--- a/2.Hardware/1.PCB/BOMTotal.xlsx
+++ b/2.Hardware/1.PCB/BOMTotal.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="8280" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="MainBoard" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="328">
   <si>
     <t>Name</t>
   </si>
@@ -513,6 +513,9 @@
     <t>Y2</t>
   </si>
   <si>
+    <t>PCB</t>
+  </si>
+  <si>
     <t>CAP, size 0603, 22 uF, 6.3 VDC</t>
   </si>
   <si>
@@ -595,6 +598,9 @@
   </si>
   <si>
     <t>U2, U3</t>
+  </si>
+  <si>
+    <t>PCB-Pannel</t>
   </si>
   <si>
     <t>C1, C4, C5, C6, C7, C8, C10</t>
@@ -1015,11 +1021,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="[$VND]\ #,##0.00;[$VND]\ \-#,##0.00"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1624,8 +1631,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
@@ -2164,12 +2174,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="23.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="129.222222222222" customWidth="1"/>
     <col min="3" max="3" width="59.2222222222222" customWidth="1"/>
+    <col min="5" max="6" width="15.4444444444444"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2196,7 +2207,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
@@ -2210,7 +2221,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
@@ -2224,7 +2235,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
@@ -2238,7 +2249,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B5" t="s">
@@ -2252,7 +2263,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
@@ -2266,7 +2277,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B7" t="s">
@@ -2280,7 +2291,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
@@ -2294,7 +2305,7 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B9" t="s">
@@ -2308,7 +2319,7 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B10" t="s">
@@ -2322,7 +2333,7 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B11" t="s">
@@ -2663,7 +2674,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B36" t="s">
@@ -2677,7 +2688,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B37" t="s">
@@ -2691,7 +2702,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B38" t="s">
@@ -2747,7 +2758,7 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>116</v>
       </c>
       <c r="B42" t="s">
@@ -2761,7 +2772,7 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B43" t="s">
@@ -2775,7 +2786,7 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B44" t="s">
@@ -2789,7 +2800,7 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B45" t="s">
@@ -2803,7 +2814,7 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B46" t="s">
@@ -2817,7 +2828,7 @@
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B47" t="s">
@@ -2831,7 +2842,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>134</v>
       </c>
       <c r="B48" t="s">
@@ -2856,7 +2867,7 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B50" t="s">
@@ -2951,6 +2962,24 @@
       </c>
       <c r="D56">
         <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
+        <v>160</v>
+      </c>
+      <c r="B57" t="s">
+        <v>160</v>
+      </c>
+      <c r="D57">
+        <v>5</v>
+      </c>
+      <c r="E57" s="1">
+        <v>26400</v>
+      </c>
+      <c r="F57" s="1">
+        <f>E57*D57</f>
+        <v>132000</v>
       </c>
     </row>
   </sheetData>
@@ -2962,13 +2991,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="17.6666666666667" customWidth="1"/>
     <col min="2" max="2" width="74.4444444444444" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="6" max="6" width="10.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="14.2222222222222"/>
+    <col min="6" max="6" width="15.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2994,60 +3024,64 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>10603226106.3</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>162</v>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -3055,13 +3089,14 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -3074,125 +3109,153 @@
       <c r="D7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D10">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B11" t="s">
         <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D11">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B12" t="s">
         <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B13" t="s">
         <v>123</v>
       </c>
       <c r="C13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>137</v>
       </c>
       <c r="C14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D16">
         <v>2</v>
+      </c>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>160</v>
+      </c>
+      <c r="B17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17" s="1">
+        <v>62000</v>
+      </c>
+      <c r="F17" s="1">
+        <f>E17*D17</f>
+        <v>310000</v>
       </c>
     </row>
   </sheetData>
@@ -3204,13 +3267,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="21.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="96.2222222222222" customWidth="1"/>
     <col min="3" max="3" width="139.111111111111" customWidth="1"/>
-    <col min="6" max="6" width="10.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="14.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="15.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3237,98 +3301,98 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D2">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
         <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B4" t="s">
         <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>191</v>
+      <c r="A5" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>194</v>
+      <c r="A6" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>197</v>
+      <c r="A7" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="B7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -3342,7 +3406,7 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -3356,7 +3420,7 @@
         <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -3370,7 +3434,7 @@
         <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -3381,7 +3445,7 @@
         <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -3395,7 +3459,7 @@
         <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -3403,10 +3467,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -3414,10 +3478,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C15" t="s">
         <v>60</v>
@@ -3427,22 +3491,22 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>208</v>
+      <c r="A16" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C16" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
-        <v>211</v>
+      <c r="A17" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="B17" t="s">
         <v>68</v>
@@ -3470,10 +3534,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C19" t="s">
         <v>78</v>
@@ -3487,24 +3551,24 @@
         <v>61031221821</v>
       </c>
       <c r="B20" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C20" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B21" t="s">
         <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -3515,24 +3579,24 @@
         <v>61300411021</v>
       </c>
       <c r="B22" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C22" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B23" t="s">
         <v>101</v>
       </c>
       <c r="C23" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -3546,7 +3610,7 @@
         <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -3568,83 +3632,83 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C26" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B27" t="s">
         <v>132</v>
       </c>
       <c r="C27" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B28" t="s">
         <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D28">
         <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B29" t="s">
         <v>123</v>
       </c>
       <c r="C29" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D29">
         <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="1" t="s">
-        <v>227</v>
+      <c r="A30" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="B30" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C30" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="1" t="s">
-        <v>230</v>
+      <c r="A31" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="B31" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C31" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -3662,14 +3726,14 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="1" t="s">
-        <v>233</v>
+      <c r="A33" s="2" t="s">
+        <v>235</v>
       </c>
       <c r="B33" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C33" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -3677,10 +3741,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B34" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C34" t="s">
         <v>144</v>
@@ -3691,10 +3755,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B35" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C35" t="s">
         <v>147</v>
@@ -3719,16 +3783,34 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B37" t="s">
         <v>155</v>
       </c>
       <c r="C37" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D37">
         <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>160</v>
+      </c>
+      <c r="B38" t="s">
+        <v>189</v>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38" s="1">
+        <v>62000</v>
+      </c>
+      <c r="F38" s="1">
+        <f>E38*D38</f>
+        <v>310000</v>
       </c>
     </row>
   </sheetData>
@@ -3740,13 +3822,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="27.6666666666667" customWidth="1"/>
     <col min="2" max="2" width="99.7777777777778" customWidth="1"/>
     <col min="3" max="3" width="255.777777777778" customWidth="1"/>
-    <col min="4" max="4" width="8.66666666666667" customWidth="1"/>
+    <col min="5" max="5" width="15.4444444444444"/>
+    <col min="6" max="6" width="17.1111111111111" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3774,13 +3858,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D2">
         <v>36</v>
@@ -3788,13 +3872,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -3802,13 +3886,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -3816,13 +3900,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -3830,13 +3914,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3844,7 +3928,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -3858,13 +3942,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B8" t="s">
         <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -3872,13 +3956,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -3886,13 +3970,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -3900,13 +3984,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -3914,13 +3998,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -3928,13 +4012,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -3942,13 +4026,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B14" t="s">
         <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -3956,13 +4040,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -3970,10 +4054,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B16" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C16" t="s">
         <v>72</v>
@@ -3984,7 +4068,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C17" t="s">
         <v>78</v>
@@ -3998,10 +4082,10 @@
         <v>61300621121</v>
       </c>
       <c r="B18" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C18" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -4012,38 +4096,38 @@
         <v>61300411121</v>
       </c>
       <c r="B19" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C19" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B20" t="s">
         <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B21" t="s">
         <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -4051,13 +4135,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B22" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C22" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -4065,13 +4149,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B23" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D23">
         <v>9</v>
@@ -4079,13 +4163,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B24" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C24" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -4093,13 +4177,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B25" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C25" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D25">
         <v>9</v>
@@ -4107,13 +4191,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D26">
         <v>23</v>
@@ -4121,13 +4205,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C27" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -4135,13 +4219,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B28" t="s">
         <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -4149,13 +4233,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s">
         <v>123</v>
       </c>
       <c r="C29" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -4163,13 +4247,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C30" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -4177,13 +4261,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s">
         <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -4191,13 +4275,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C32" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4205,13 +4289,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B33" t="s">
         <v>132</v>
       </c>
       <c r="C33" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -4219,7 +4303,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C34" t="s">
         <v>138</v>
@@ -4229,11 +4313,11 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="1" t="s">
-        <v>306</v>
+      <c r="A35" s="2" t="s">
+        <v>308</v>
       </c>
       <c r="B35" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C35" t="s">
         <v>141</v>
@@ -4258,7 +4342,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s">
         <v>149</v>
@@ -4272,10 +4356,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C38" t="s">
         <v>153</v>
@@ -4286,16 +4370,31 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C39" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D39">
         <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>160</v>
+      </c>
+      <c r="B40" t="s">
+        <v>160</v>
+      </c>
+      <c r="E40" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F40" s="1">
+        <f>E40*D40</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4307,12 +4406,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="70.8888888888889" customWidth="1"/>
     <col min="3" max="3" width="64" customWidth="1"/>
+    <col min="5" max="5" width="14.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="15.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -4339,14 +4440,14 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -4360,7 +4461,7 @@
         <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -4368,7 +4469,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C4" t="s">
         <v>42</v>
@@ -4385,18 +4486,18 @@
         <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>315</v>
+      <c r="A6" s="2" t="s">
+        <v>317</v>
       </c>
       <c r="B6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C6" t="s">
         <v>60</v>
@@ -4427,7 +4528,7 @@
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -4438,10 +4539,10 @@
         <v>61030821821</v>
       </c>
       <c r="B9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D9">
         <v>16</v>
@@ -4455,7 +4556,7 @@
         <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -4469,7 +4570,7 @@
         <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -4483,7 +4584,7 @@
         <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -4494,10 +4595,10 @@
         <v>61300311121</v>
       </c>
       <c r="B13" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C13" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -4505,10 +4606,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B14" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C14" t="s">
         <v>115</v>
@@ -4518,28 +4619,28 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>230</v>
+      <c r="A15" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="B15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B16" t="s">
         <v>132</v>
       </c>
       <c r="C16" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -4554,6 +4655,24 @@
       </c>
       <c r="D17">
         <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18" s="1">
+        <v>26400</v>
+      </c>
+      <c r="F18" s="1">
+        <f>E18*D18</f>
+        <v>132000</v>
       </c>
     </row>
   </sheetData>

--- a/2.Hardware/1.PCB/BOMTotal.xlsx
+++ b/2.Hardware/1.PCB/BOMTotal.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
-    <sheet name="MainBoard" sheetId="1" r:id="rId1"/>
+    <sheet name="MainBoard" sheetId="7" r:id="rId1"/>
     <sheet name="HBridgeDriver" sheetId="2" r:id="rId2"/>
     <sheet name="HBridgeMCU" sheetId="3" r:id="rId3"/>
     <sheet name="MainSensor" sheetId="4" r:id="rId4"/>
     <sheet name="ServoShield" sheetId="5" r:id="rId5"/>
+    <sheet name="PCB" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,779 +32,1004 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="417">
   <si>
     <t>Name</t>
   </si>
   <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Designator</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Price Total</t>
+  </si>
+  <si>
+    <t>Supplier</t>
+  </si>
+  <si>
+    <t>0106031010550</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 100 pF, 50 VDC</t>
+  </si>
+  <si>
+    <t>C1, C2, C3, C5, C6, C7, C12, C15, C28</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-gom-0603-100nf-0-1uf-50v</t>
+  </si>
+  <si>
+    <t>0106034751010</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 4.7 uF, 10 VDC</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-gom-0603-4-7uf-25v</t>
+  </si>
+  <si>
+    <t>0106032251010</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 2.2 uF, 10 VDC</t>
+  </si>
+  <si>
+    <t>C8, C13</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-gom-0603-2-2uf-50v</t>
+  </si>
+  <si>
+    <t>0106031030550</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 10 nF, 50 VDC</t>
+  </si>
+  <si>
+    <t>C9, C10, C36</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-gom-0603-10nf-50v</t>
+  </si>
+  <si>
+    <t>0106031051035</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 1 uF, 35 VDC</t>
+  </si>
+  <si>
+    <t>C11, C14</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-gom-0603-1uf-50v</t>
+  </si>
+  <si>
+    <t>0106031000550</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 10 pF, 50 VDC</t>
+  </si>
+  <si>
+    <t>C16, C17, C18, C19, C37, C38</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-gom-0603-8pf-50v</t>
+  </si>
+  <si>
+    <t>0108051041050</t>
+  </si>
+  <si>
+    <t>CAP, size 0805, 0.1 nF, 50 VDC</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-gom-0603-100pf-50v</t>
+  </si>
+  <si>
+    <t>0106032241050</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 220 nF, 50 VDC</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-gom-0603-220nf-50v</t>
+  </si>
+  <si>
+    <t>0106031041050</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 100 nF, 50 VDC</t>
+  </si>
+  <si>
+    <t>C22, C30, C32, C34</t>
+  </si>
+  <si>
+    <t>865080340001</t>
+  </si>
+  <si>
+    <t>V-Chip, D4 x H5.5mm, 10uF, 16V</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-nhom-smd-10uf-25v-4x5-4mm</t>
+  </si>
+  <si>
+    <t>865080745011</t>
+  </si>
+  <si>
+    <t>V-Chip, D6.3 x H7.7mm, 22uF, 63V</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-nhom-smd-22uf-16v-4x5-4mm</t>
+  </si>
+  <si>
+    <t>0106031061010</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 10 uF, 10 VDC</t>
+  </si>
+  <si>
+    <t>C25, C26, C27, C29, C31, C33</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-gom-0603-10uf-16v</t>
+  </si>
+  <si>
+    <t>0106031051016</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 1 uF, 16 VDC</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-gom-0603-1uf-25v</t>
+  </si>
+  <si>
+    <t>160603RedClear</t>
+  </si>
+  <si>
+    <t>WL-SMCW SMT Mono-color Chip LED Waterclear, size 0603, Red, 2V, 140deg</t>
+  </si>
+  <si>
+    <t>D1, D6, D7, D9</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/led-do-0603-dan-smd-trong-suot</t>
+  </si>
+  <si>
+    <t>SMAJ18A</t>
+  </si>
+  <si>
+    <t>400W, 21.1V, 5%, Unidirectional, TVS</t>
+  </si>
+  <si>
+    <t>D2, D4</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/smaj18a</t>
+  </si>
+  <si>
+    <t>ZMM18</t>
+  </si>
+  <si>
+    <t>18V Diode zenner</t>
+  </si>
+  <si>
+    <t>D3, D5</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/zmm18-diode-zener-18v-500mw-smd</t>
+  </si>
+  <si>
+    <t>CMP-1431-00001-2</t>
+  </si>
+  <si>
+    <t>RGB LED 3225</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/led-rgb-3528-dan-smd-trong-suot</t>
+  </si>
+  <si>
+    <t>1N5819W</t>
+  </si>
+  <si>
+    <t>Schottky Diode SOD-123</t>
+  </si>
+  <si>
+    <t>D10, D11</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/1n5819w-diode-schottky-1a-40v-sod-123</t>
+  </si>
+  <si>
+    <t>160603BlueClear</t>
+  </si>
+  <si>
+    <t>WL-SMCW SMT Mono-color Chip LED Waterclear, size 0603, Blue, 3.2V, 140deg</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/led-xanh-duong-0603-dan-smd-trong-suot</t>
+  </si>
+  <si>
+    <t>160603WhiteBlur</t>
+  </si>
+  <si>
+    <t>WL-SMCW SMT Mono-color Chip LED Blur, size 0603, White</t>
+  </si>
+  <si>
+    <t>D13</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/led-trang-0603-dan-smd-trong-suot</t>
+  </si>
+  <si>
+    <t>160603RedBlur</t>
+  </si>
+  <si>
+    <t>WL-SMCW SMT Mono-color Chip LED Blur, size 0603, Red, 2V, 140deg</t>
+  </si>
+  <si>
+    <t>D14</t>
+  </si>
+  <si>
+    <t>061812110016</t>
+  </si>
+  <si>
+    <t>Resettable Fuse, Size 1812, 16V, 1.1A</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/mf-msmf110-16-2-cau-chi-tu-phuc-hoi-1812-16v-1-1a</t>
+  </si>
+  <si>
+    <t>061812050015</t>
+  </si>
+  <si>
+    <t>Resettable Fuse, Size 1812, 15V, 0.5A</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/mf-msmf050-2-cau-chi-tu-phuc-hoi-1812-15v-0-5a</t>
+  </si>
+  <si>
+    <t>061206035006</t>
+  </si>
+  <si>
+    <t>Resettable Fuse, Size 1206, 6V, 0.35A</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/mf-nsmf035-2-cau-chi-tu-phuc-hoi-1206-6v-0-35a</t>
+  </si>
+  <si>
+    <t>061812020030</t>
+  </si>
+  <si>
+    <t>Resettable Fuse, Size 1812, 30V, 0.2A</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/minismdc020f-2-cau-chi-tu-phuc-hoi-1812-30v-200ma</t>
+  </si>
+  <si>
+    <t>BLM18PG121SN1D</t>
+  </si>
+  <si>
+    <t>Ferrite Chip, 1 Function(s), 2A, 2 Pin(s)</t>
+  </si>
+  <si>
+    <t>FB1</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/cbw201209u121t-ferrite-beads-2a-120-ohm-0805</t>
+  </si>
+  <si>
+    <t>KF301-2P</t>
+  </si>
+  <si>
+    <t>2 Pin Terminal Block 5mm Pitch</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/kf301-2-v-domino-2-chan-thang-5-08mm-300v-10a-han-pcb</t>
+  </si>
+  <si>
+    <t>S8411-45R</t>
+  </si>
+  <si>
+    <t>Coin Cell Battery Retainer, Horizontal SMT, for CR1220 Coin Cell Batteries, Tape &amp; Reeled</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/de-pin-cr1220-dan-smd</t>
+  </si>
+  <si>
+    <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 24p</t>
+  </si>
+  <si>
+    <t>J3, J4, J6</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-24-chan-2-hang-smd</t>
+  </si>
+  <si>
+    <t>MSD-4-A</t>
+  </si>
+  <si>
+    <t>Micro SD Card Connector, 9 Positions, Connector and Ejector, Push In, Auto Eject Out, Surface Mount, 1.8 mm Height Above Board, Gold Flash</t>
+  </si>
+  <si>
+    <t>J5</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/misd-pp-9p-v1-khay-the-nho-microsd-9-chan-push-push</t>
+  </si>
+  <si>
+    <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 20p</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-20-chan-2-hang-smd</t>
+  </si>
+  <si>
+    <t>Mini USB 2.0 Type B Receptacle WR-COM, Horizontal, SMT, with Pads and Pegs</t>
+  </si>
+  <si>
+    <t>J8</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/cong-usb-mini-b-dau-cai-5-chan-smd-v1</t>
+  </si>
+  <si>
+    <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 4p</t>
+  </si>
+  <si>
+    <t>J9, J10</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-4-chan-2-hang-smd</t>
+  </si>
+  <si>
+    <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 6p</t>
+  </si>
+  <si>
+    <t>J11</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-smd</t>
+  </si>
+  <si>
+    <t>WR-PHD Pin Header, SMT, pitch 2.54mm, Dual Row, Vertical, 4p</t>
+  </si>
+  <si>
+    <t>J12</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-6-chan-2-hang-smd</t>
+  </si>
+  <si>
+    <t>WR-PHD Pin Header, SMT, pitch 2.54mm, Dual Row, Vertical, 6p</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>WR-PHD Pin Header, SMT, pitch 2.54mm, Dual Row, Vertical, 24p</t>
+  </si>
+  <si>
+    <t>P2, P3, P15</t>
+  </si>
+  <si>
+    <t>665304124022</t>
+  </si>
+  <si>
+    <t>WR-WTB SMT Male Vertical Shrouded Header, pitch 1mm, 4p</t>
+  </si>
+  <si>
+    <t>P4, P5, P6</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dau-sh1-0mm-4-chan-dan-smd-thang-dung</t>
+  </si>
+  <si>
+    <t>665305124022</t>
+  </si>
+  <si>
+    <t>WR-WTB SMT Male Vertical Shrouded Header, pitch 1mm, 5p</t>
+  </si>
+  <si>
+    <t>P7, P8, P9</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dau-sh1-0mm-6-chan-dan-smd-thang-dung</t>
+  </si>
+  <si>
+    <t>665303124022</t>
+  </si>
+  <si>
+    <t>WR-WTB SMT Male Vertical Shrouded Header, pitch 1mm, 3p</t>
+  </si>
+  <si>
+    <t>P10, P11, P12, P13, P14</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dau-sh1-0mm-3-chan-dan-smd-nam-ngang</t>
+  </si>
+  <si>
+    <t>WR-PHD Pin Header, SMT, pitch 2.54mm, Dual Row, Vertical, 20p</t>
+  </si>
+  <si>
+    <t>P16</t>
+  </si>
+  <si>
+    <t>WR-PHD Pin Header, SMT, pitch 2.54mm, Dual Row, Vertical, 8p</t>
+  </si>
+  <si>
+    <t>P17, P18</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-8-chan-2-hang-smd</t>
+  </si>
+  <si>
+    <t>AO3407A</t>
+  </si>
+  <si>
+    <t>P-Channel 30 V 4.3A (Ta) 1.4W (Ta) Surface Mount SOT-23-3</t>
+  </si>
+  <si>
+    <t>Q1, Q2, Q3</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/ao3407a-mosfet-kenh-p-30v-4-3a-sot-23-3</t>
+  </si>
+  <si>
+    <t>0006031031</t>
+  </si>
+  <si>
+    <t>RES, size 0603, 10 KOhm, 1/4 W</t>
+  </si>
+  <si>
+    <t>R1, R2, R4, R5, R7, R8, R11, R14, R18, R19, R20, R21, R22, R23, R26, R34, R35, R39</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-10-kohm-0603-1-</t>
+  </si>
+  <si>
+    <t>0006031221</t>
+  </si>
+  <si>
+    <t>RES, size 0603, 1.2 KOhm, 1/4 W</t>
+  </si>
+  <si>
+    <t>R3, R24, R25, R27, R28</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-1-2-kohm-0603-1-</t>
+  </si>
+  <si>
+    <t>0006030001</t>
+  </si>
+  <si>
+    <t>RES, size 0603, 0 Ohm, 1/4 W</t>
+  </si>
+  <si>
+    <t>R6, R9, R10, R12, R13, R31, R32</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-0-ohm-0603-1-</t>
+  </si>
+  <si>
+    <t>0008051531</t>
+  </si>
+  <si>
+    <t>RES, size 0805, 15 KOhm, 1/8 W</t>
+  </si>
+  <si>
+    <t>R15, R16, R17</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-15-kohm-0805-5-</t>
+  </si>
+  <si>
+    <t>0006031041</t>
+  </si>
+  <si>
+    <t>RES, size 0603, 100 KOhm, 1/4 W</t>
+  </si>
+  <si>
+    <t>R29</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-100-kohm-0603-5-</t>
+  </si>
+  <si>
+    <t>0006031521</t>
+  </si>
+  <si>
+    <t>RES, size 0603, 1.5  KOhm, 1/4 W</t>
+  </si>
+  <si>
+    <t>R30</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-1-5-kohm-0603-1-</t>
+  </si>
+  <si>
+    <t>0006031011</t>
+  </si>
+  <si>
+    <t>RES, size 0603, 100 Ohm, 1/4 W</t>
+  </si>
+  <si>
+    <t>R33</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-100-ohm-0603-5-</t>
+  </si>
+  <si>
+    <t>0006032001</t>
+  </si>
+  <si>
+    <t>RES, size 0603, 20 Ohm, 1/4 W</t>
+  </si>
+  <si>
+    <t>R36, R37</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-20-ohm-0603-5-</t>
+  </si>
+  <si>
+    <t>0006031021</t>
+  </si>
+  <si>
+    <t>RES, size 0603, 1 KOhm, 1/4 W</t>
+  </si>
+  <si>
+    <t>R38, R40, R41</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-1-kohm-0603-5-</t>
+  </si>
+  <si>
+    <t>MP3.2</t>
+  </si>
+  <si>
+    <t>Screw M3</t>
+  </si>
+  <si>
+    <t>Scr1, Scr2, Scr3, Scr4</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/vit-nhua-m3-dai-5mm</t>
+  </si>
+  <si>
+    <t>434111050826</t>
+  </si>
+  <si>
+    <t>WS-TASV SMT Tact Switch, L6 x W3.5 x H5mm, 260g, SPST-NO, 12V, 50mA</t>
+  </si>
+  <si>
+    <t>SW1, SW2, SW3</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/nut-nhan-3x6mm-cao-5mm-2-chan-smd-dau-trang</t>
+  </si>
+  <si>
+    <t>STM32F407VGTx</t>
+  </si>
+  <si>
+    <t>ARM Microcontrollers - MCU ARM M4 1024 FLASH 168 Mhz 192kB SRAM</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/stm32f407vet6-32-bit-arm-cortex-m4-microcontroller-168mhz-512kb-flash-100-lqfp</t>
+  </si>
+  <si>
+    <t>L7805ACD2T_TO-263</t>
+  </si>
+  <si>
+    <t>Out: 5V, 1.5A; In: 7V to 35V; Pacakge: TO-263</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/l7805acd2t-ic-on-ap-5v-1-5a</t>
+  </si>
+  <si>
+    <t>AMS1117-3.3V</t>
+  </si>
+  <si>
+    <t>AMS1117-3.3V, OUT 3.3V 1A.</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/ams1117-3-3v-ic-on-ap-3-3v-1a-sot-223</t>
+  </si>
+  <si>
+    <t>STM32F103C8T6</t>
+  </si>
+  <si>
+    <t>ARM Microcontrollers - MCU 32BIT Cortex M3 64KB 20KB RAM 2X12 ADC</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/stm32f103c8t6-32-bit-arm-cortex-m3-microcontroller-72mhz-64kb-flash-48-lqfp</t>
+  </si>
+  <si>
+    <t>CMP-200220-000002-1</t>
+  </si>
+  <si>
+    <t>CRYSTAL 25.0000MHZ 8PF SMD</t>
+  </si>
+  <si>
+    <t>Y1</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/thach-anh-25mhz-3225-4-chan-smd</t>
+  </si>
+  <si>
+    <t>CRYSTAL 8.0000MHZ 8PF SMD</t>
+  </si>
+  <si>
+    <t>Y3</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/thach-anh-8mhz-3225-4-chan-smd</t>
+  </si>
+  <si>
+    <t>FC-13532.7680KA-A0</t>
+  </si>
+  <si>
+    <t>Parallel - Fundamental Quartz Crystal, 0.032768MHz Nom</t>
+  </si>
+  <si>
+    <t>Y2</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/thach-anh-fc-135-32-768khz-3215</t>
+  </si>
+  <si>
+    <t>PCB</t>
+  </si>
+  <si>
+    <t>https://shopee.vn/S%E1%BA%A3n-xu%E1%BA%A5t-PCB-ch%E1%BA%A5t-l%C6%B0%E1%BB%A3ng-cao-%E2%80%93-MOQ-5-T%C3%B9y-ch%E1%BB%89nh-m%C3%A0u-mi%E1%BB%85n-ph%C3%AD-B%E1%BA%A3ng-%C4%91%C6%A1n-%C4%91%C3%B4i-v%C3%A0-nhi%E1%BB%81u-l%E1%BB%9Bp-i.1135296432.28315488514</t>
+  </si>
+  <si>
+    <t>Tổng tiền</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Designator</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
     <t>Total Price</t>
   </si>
   <si>
     <t>Supplier 1</t>
   </si>
   <si>
-    <t>0106031010550</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 100 pF, 50 VDC</t>
-  </si>
-  <si>
-    <t>C1, C2, C3, C5, C6, C7, C12, C15, C22</t>
-  </si>
-  <si>
-    <t>0106034751010</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 4.7 uF, 10 VDC</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>0106032251010</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 2.2 uF, 10 VDC</t>
-  </si>
-  <si>
-    <t>C8, C13</t>
-  </si>
-  <si>
-    <t>0106031030550</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 10 nF, 50 VDC</t>
-  </si>
-  <si>
-    <t>C9, C10, C30</t>
-  </si>
-  <si>
-    <t>0106031051035</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 1 uF, 35 VDC</t>
-  </si>
-  <si>
-    <t>C11, C14</t>
-  </si>
-  <si>
-    <t>0106031000550</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 10 pF, 50 VDC</t>
-  </si>
-  <si>
-    <t>C16, C17, C18, C19, C31, C32</t>
-  </si>
-  <si>
-    <t>0108051041050</t>
-  </si>
-  <si>
-    <t>CAP, size 0805, 0.1 nF, 50 VDC</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>0106031061010</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 10 uF, 10 VDC</t>
-  </si>
-  <si>
-    <t>C21, C23, C25, C27</t>
-  </si>
-  <si>
-    <t>0106031041050</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 100 nF, 50 VDC</t>
-  </si>
-  <si>
-    <t>C24, C26, C28</t>
-  </si>
-  <si>
-    <t>0106031051016</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 1 uF, 16 VDC</t>
+    <t>CAP, size 0603, 22 uF, 6.3 VDC</t>
+  </si>
+  <si>
+    <t>C1, C2</t>
+  </si>
+  <si>
+    <t>0108051031050</t>
+  </si>
+  <si>
+    <t>CAP, size 0805, 10 nF, 50 VDC</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>D1, D2</t>
+  </si>
+  <si>
+    <t>160603GreenClear</t>
+  </si>
+  <si>
+    <t>WL-SMCW SMT Mono-color Chip LED Waterclear, size 0603, Green, 3.2V, 140deg</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>KF120-2</t>
+  </si>
+  <si>
+    <t>2.54mm Terminal</t>
+  </si>
+  <si>
+    <t>J2, J3</t>
+  </si>
+  <si>
+    <t>90StraightHeader</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>IRLR7843TRPBF</t>
+  </si>
+  <si>
+    <t>RoHS Compliant</t>
+  </si>
+  <si>
+    <t>Q1, Q2, Q3, Q4</t>
+  </si>
+  <si>
+    <t>R1, R4, R5, R6, R9, R10</t>
+  </si>
+  <si>
+    <t>R2, R3, R13</t>
+  </si>
+  <si>
+    <t>R7, R8, R11, R12</t>
+  </si>
+  <si>
+    <t>Scr1</t>
+  </si>
+  <si>
+    <t>PC817X2NIP1B</t>
+  </si>
+  <si>
+    <t>Optocoupler DC-IN 1-CH Transistor DC-OUT 4-Pin DIP SMD T/R</t>
+  </si>
+  <si>
+    <t>U1, U4</t>
+  </si>
+  <si>
+    <t>IR2104SPBF</t>
+  </si>
+  <si>
+    <t>Half-Bridge Gate Driver IC Non-Inverting 8-SOIC</t>
+  </si>
+  <si>
+    <t>U2, U3</t>
+  </si>
+  <si>
+    <t>PCB-Pannel</t>
+  </si>
+  <si>
+    <t>C1, C4, C5, C6, C7, C8, C10</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3, C9</t>
+  </si>
+  <si>
+    <t>0106030600550</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 6 pF, 50 VDC</t>
+  </si>
+  <si>
+    <t>C11, C12</t>
+  </si>
+  <si>
+    <t>0106033300550</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 33 pF, 50 VDC</t>
+  </si>
+  <si>
+    <t>C13, C14</t>
+  </si>
+  <si>
+    <t>865080340003</t>
+  </si>
+  <si>
+    <t>V-Chip, D4 x H5.5mm, 22uF, 16V</t>
+  </si>
+  <si>
+    <t>C15, C16</t>
+  </si>
+  <si>
+    <t>C17, C18</t>
+  </si>
+  <si>
+    <t>D3, D7</t>
+  </si>
+  <si>
+    <t>D5, D6</t>
+  </si>
+  <si>
+    <t>D8, D10, D12, D14</t>
+  </si>
+  <si>
+    <t>Schottky-Diode</t>
+  </si>
+  <si>
+    <t>D9, D11, D13, D15</t>
+  </si>
+  <si>
+    <t>0605201000250F</t>
+  </si>
+  <si>
+    <t>Glass Fuse, Size 0520, 250 VAC, 10A, F</t>
+  </si>
+  <si>
+    <t>061812110024</t>
+  </si>
+  <si>
+    <t>Resettable Fuse, Size 1812, 24V, 1.1A</t>
+  </si>
+  <si>
+    <t>F2, F3</t>
+  </si>
+  <si>
+    <t>796683-3</t>
+  </si>
+  <si>
+    <t>Wire to Board 3 Position 5 mm Pitch 30-12 AWG Euro Style Terminal Block</t>
+  </si>
+  <si>
+    <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 12p</t>
+  </si>
+  <si>
+    <t>J3_U_MotorDriverConnector1, J3_U_MotorDriverConnector2, J3_U_MotorDriverConnector3, J3_U_MotorDriverConnector4</t>
+  </si>
+  <si>
+    <t>WR-PHD Pin Header, THT, pitch 2.54mm, Single Row, Angled, 4p</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>AOD4185</t>
+  </si>
+  <si>
+    <t>P-Channel 40V 40A (Tc) 2.5W (Ta), 62.5W (Tc) Surface Mount TO-252, (D-Pak)</t>
+  </si>
+  <si>
+    <t>Q4, Q5, Q6</t>
+  </si>
+  <si>
+    <t>R1, R2, R3, R15</t>
+  </si>
+  <si>
+    <t>R4, R8, R12, R14</t>
+  </si>
+  <si>
+    <t>R5, R6, R7, R9, R10, R11_U_MotorDriverConnector1, R11_U_MotorDriverConnector2, R11_U_MotorDriverConnector3, R11_U_MotorDriverConnector4</t>
+  </si>
+  <si>
+    <t>0006031211</t>
+  </si>
+  <si>
+    <t>RES, size 0603, 120 Ohm, 1/4 W</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>R16, R17, R18, R19, R20, R21</t>
+  </si>
+  <si>
+    <t>434111043826</t>
+  </si>
+  <si>
+    <t>WS-TASV SMT Tact Switch, L6 x W3.5 x H4.3mm, 260g, SPST-NO, 12V, 50mA</t>
+  </si>
+  <si>
+    <t>SW1, SW2_U_MotorDriverConnector1, SW2_U_MotorDriverConnector2, SW2_U_MotorDriverConnector3, SW2_U_MotorDriverConnector4</t>
+  </si>
+  <si>
+    <t>STM32F103RCT6</t>
+  </si>
+  <si>
+    <t>ARMÂ® CortexÂ®-M3 STM32F1 Microcontroller IC 32-Bit 72MHz 256KB (256K x 8) FLASH 64-LQFP (10x10)</t>
+  </si>
+  <si>
+    <t>TJA1050</t>
+  </si>
+  <si>
+    <t>1/1 Transceiver Half CANbus 8-SO</t>
+  </si>
+  <si>
+    <t>C0603C200J5GACTU</t>
+  </si>
+  <si>
+    <t>CAP CER 20PF 50V 5% NP0 0603</t>
+  </si>
+  <si>
+    <t>C1_DS1, C1_DS2, C1_DS3, C1_DS4, C2_DS1, C2_DS2, C2_DS3, C2_DS4, C3_DS1, C3_DS2, C3_DS3, C3_DS4, C4_DS1, C4_DS2, C4_DS3, C4_DS4, C6_LS1, C6_LS2, C6_LS3, C6_LS4, C6_LS5, C7_LS1, C7_LS2, C7_LS3, C7_LS4, C7_LS5, C8_LS1, C8_LS2, C8_LS3, C8_LS4, C8_LS5, C9_LS1, C9_LS2, C9_LS3, C9_LS4, C9_LS5</t>
+  </si>
+  <si>
+    <t>GRM155R71C104KA88D</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 16V X7R 0402</t>
+  </si>
+  <si>
+    <t>C5_DS1, C5_DS2, C5_DS3, C5_DS4, C10_LS1, C10_LS2, C10_LS3, C10_LS4, C10_LS5</t>
+  </si>
+  <si>
+    <t>100 nF</t>
+  </si>
+  <si>
+    <t>C16, C18, C19, C20, C21, C22, C23, C24, C26, C27, C28, C38</t>
+  </si>
+  <si>
+    <t>10 uF</t>
+  </si>
+  <si>
+    <t>C17, C31, C34</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 100 nF</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>10 nF</t>
   </si>
   <si>
     <t>C29</t>
   </si>
   <si>
-    <t>160603RedClear</t>
-  </si>
-  <si>
-    <t>WL-SMCW SMT Mono-color Chip LED Waterclear, size 0603, Red, 2V, 140deg</t>
-  </si>
-  <si>
-    <t>D1, D6, D7, D9</t>
-  </si>
-  <si>
-    <t>SMAJ18A</t>
-  </si>
-  <si>
-    <t>400W, 21.1V, 5%, Unidirectional, TVS</t>
-  </si>
-  <si>
-    <t>D2, D4</t>
-  </si>
-  <si>
-    <t>ZMM18</t>
-  </si>
-  <si>
-    <t>D3, D5</t>
-  </si>
-  <si>
-    <t>CMP-1431-00001-2</t>
-  </si>
-  <si>
-    <t>D8</t>
-  </si>
-  <si>
-    <t>1N5819W</t>
-  </si>
-  <si>
-    <t>D10, D11, D12</t>
-  </si>
-  <si>
-    <t>160603BlueClear</t>
-  </si>
-  <si>
-    <t>WL-SMCW SMT Mono-color Chip LED Waterclear, size 0603, Blue, 3.2V, 140deg</t>
-  </si>
-  <si>
-    <t>D13</t>
-  </si>
-  <si>
-    <t>160603WhiteBlur</t>
-  </si>
-  <si>
-    <t>WL-SMCW SMT Mono-color Chip LED Blur, size 0603, White</t>
-  </si>
-  <si>
-    <t>D14</t>
-  </si>
-  <si>
-    <t>160603RedBlur</t>
-  </si>
-  <si>
-    <t>WL-SMCW SMT Mono-color Chip LED Blur, size 0603, Red, 2V, 140deg</t>
-  </si>
-  <si>
-    <t>D15</t>
-  </si>
-  <si>
-    <t>MF-MSMF110/16-2</t>
-  </si>
-  <si>
-    <t>Resettable Fuse, Size 1812, 16V, 1.1A</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>MF-MSMF050-2</t>
-  </si>
-  <si>
-    <t>Resettable Fuse, Size 1812, 15V, 0.5A</t>
-  </si>
-  <si>
-    <t>F2</t>
-  </si>
-  <si>
-    <t>MF-NSMF035-2</t>
-  </si>
-  <si>
-    <t>Resettable Fuse, Size 1206, 6V, 0.35A</t>
-  </si>
-  <si>
-    <t>F3</t>
-  </si>
-  <si>
-    <t>MINISMDC020F</t>
-  </si>
-  <si>
-    <t>Resettable Fuse, Size 1812, 30V, 0.2A</t>
-  </si>
-  <si>
-    <t>F4</t>
-  </si>
-  <si>
-    <t>120R , 0805</t>
-  </si>
-  <si>
-    <t>Ferrite Chip, 1 Function(s), 2A, 2 Pin(s)</t>
-  </si>
-  <si>
-    <t>FB1</t>
-  </si>
-  <si>
-    <t>KF301-2P</t>
-  </si>
-  <si>
-    <t>2 Pin Terminal Block 5mm Pitch</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>S8411-45R</t>
-  </si>
-  <si>
-    <t>Coin Cell Battery Retainer, Horizontal SMT, for CR1220 Coin Cell Batteries, Tape &amp; Reeled</t>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 24p</t>
-  </si>
-  <si>
-    <t>J3, J4, J6</t>
-  </si>
-  <si>
-    <t>MSD-4-A</t>
-  </si>
-  <si>
-    <t>Micro SD Card Connector, 9 Positions, Connector and Ejector, Push In, Auto Eject Out, Surface Mount, 1.8 mm Height Above Board, Gold Flash</t>
-  </si>
-  <si>
-    <t>J5</t>
-  </si>
-  <si>
-    <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 20p</t>
-  </si>
-  <si>
-    <t>J7</t>
-  </si>
-  <si>
-    <t>Mini USB 2.0 Type B Receptacle WR-COM, Horizontal, SMT, with Pads and Pegs</t>
-  </si>
-  <si>
-    <t>J8</t>
-  </si>
-  <si>
-    <t>FEMALE,SMT</t>
-  </si>
-  <si>
-    <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 4p</t>
-  </si>
-  <si>
-    <t>J9, J10, J11</t>
-  </si>
-  <si>
-    <t>WR-PHD Pin Header, SMT, pitch 2.54mm, Dual Row, Vertical, 4p</t>
-  </si>
-  <si>
-    <t>J12</t>
-  </si>
-  <si>
-    <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 6p</t>
-  </si>
-  <si>
-    <t>J13</t>
-  </si>
-  <si>
-    <t>MALE,SMT, 61030621121</t>
-  </si>
-  <si>
-    <t>WR-PHD Pin Header, SMT, pitch 2.54mm, Dual Row, Vertical, 6p</t>
-  </si>
-  <si>
-    <t>P1, P19</t>
-  </si>
-  <si>
-    <t>WR-PHD Pin Header, SMT, pitch 2.54mm, Dual Row, Vertical, 24p</t>
-  </si>
-  <si>
-    <t>P2, P3, P15</t>
-  </si>
-  <si>
-    <t>665304124022</t>
-  </si>
-  <si>
-    <t>WR-WTB SMT Male Vertical Shrouded Header, pitch 1mm, 4p</t>
-  </si>
-  <si>
-    <t>P4, P5, P6</t>
-  </si>
-  <si>
-    <t>665305124022</t>
-  </si>
-  <si>
-    <t>WR-WTB SMT Male Vertical Shrouded Header, pitch 1mm, 5p</t>
-  </si>
-  <si>
-    <t>P7, P8, P9</t>
-  </si>
-  <si>
-    <t>665303124022</t>
-  </si>
-  <si>
-    <t>WR-WTB SMT Male Vertical Shrouded Header, pitch 1mm, 3p</t>
-  </si>
-  <si>
-    <t>P10, P11, P12, P13, P14</t>
-  </si>
-  <si>
-    <t>WR-PHD Pin Header, SMT, pitch 2.54mm, Dual Row, Vertical, 20p</t>
-  </si>
-  <si>
-    <t>P16</t>
-  </si>
-  <si>
-    <t>WR-PHD Pin Header, SMT, pitch 2.54mm, Dual Row, Vertical, 8p</t>
-  </si>
-  <si>
-    <t>P17, P18</t>
-  </si>
-  <si>
-    <t>AO3407A</t>
-  </si>
-  <si>
-    <t>P-Channel 30 V 4.3A (Ta) 1.4W (Ta) Surface Mount SOT-23-3</t>
-  </si>
-  <si>
-    <t>Q1, Q2, Q3</t>
-  </si>
-  <si>
-    <t>0006031221</t>
-  </si>
-  <si>
-    <t>RES, size 0603, 1.2 KOhm, 1/4 W</t>
-  </si>
-  <si>
-    <t>R1, R20, R21, R23, R24</t>
-  </si>
-  <si>
-    <t>0006030001</t>
-  </si>
-  <si>
-    <t>RES, size 0603, 0 Ohm, 1/4 W</t>
-  </si>
-  <si>
-    <t>R2, R5, R6, R8, R9</t>
-  </si>
-  <si>
-    <t>0006031031</t>
-  </si>
-  <si>
-    <t>RES, size 0603, 10 KOhm, 1/4 W</t>
-  </si>
-  <si>
-    <t>R3, R4, R7, R10, R14, R15, R16, R17, R18, R19, R22, R26, R28, R31</t>
-  </si>
-  <si>
-    <t>0008051031</t>
-  </si>
-  <si>
-    <t>RES, size 0805, 10 KOhm, 1/8 W</t>
-  </si>
-  <si>
-    <t>R11, R12, R13</t>
-  </si>
-  <si>
-    <t>0006031011</t>
-  </si>
-  <si>
-    <t>RES, size 0603, 100 Ohm, 1/4 W</t>
-  </si>
-  <si>
-    <t>R25</t>
-  </si>
-  <si>
-    <t>0006031021</t>
-  </si>
-  <si>
-    <t>RES, size 0603, 1 KOhm, 1/4 W</t>
-  </si>
-  <si>
-    <t>R27, R29, R30</t>
-  </si>
-  <si>
-    <t>0006032001</t>
-  </si>
-  <si>
-    <t>RES, size 0603, 20 Ohm, 1/4 W</t>
-  </si>
-  <si>
-    <t>R32, R33</t>
-  </si>
-  <si>
-    <t>MP3.2</t>
-  </si>
-  <si>
-    <t>Scr1, Scr2, Scr3, Scr4</t>
-  </si>
-  <si>
-    <t>434111050826</t>
-  </si>
-  <si>
-    <t>WS-TASV SMT Tact Switch, L6 x W3.5 x H5mm, 260g, SPST-NO, 12V, 50mA</t>
-  </si>
-  <si>
-    <t>SW1, SW2, SW3</t>
-  </si>
-  <si>
-    <t>STM32F407VxTx</t>
-  </si>
-  <si>
-    <t>ARM Microcontrollers - MCU ARM M4 1024 FLASH 168 Mhz 192kB SRAM</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>L7805ACD2T_TO-263</t>
-  </si>
-  <si>
-    <t>Out: 5V, 1.5A; In: 7V to 35V; Pacakge: TO-263</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>AMS1117-3.3V</t>
-  </si>
-  <si>
-    <t>AMS1117-3.3V, OUT 3.3V 1A.</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>STM32F103C8T6</t>
-  </si>
-  <si>
-    <t>ARM Microcontrollers - MCU 32BIT Cortex M3 64KB 20KB RAM 2X12 ADC</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>25Mhz, 3225, 8Mhz, 3225</t>
-  </si>
-  <si>
-    <t>CRYSTAL 25.0000MHZ 8PF SMD</t>
-  </si>
-  <si>
-    <t>Y1, Y3</t>
-  </si>
-  <si>
-    <t>32.7680Khz , 3215</t>
-  </si>
-  <si>
-    <t>Parallel - Fundamental Quartz Crystal, 0.032768MHz Nom</t>
-  </si>
-  <si>
-    <t>Y2</t>
-  </si>
-  <si>
-    <t>PCB</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 22 uF, 6.3 VDC</t>
-  </si>
-  <si>
-    <t>C1, C2</t>
-  </si>
-  <si>
-    <t>0108051031050</t>
-  </si>
-  <si>
-    <t>CAP, size 0805, 10 nF, 50 VDC</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>D1, D2</t>
-  </si>
-  <si>
-    <t>160603GreenClear</t>
-  </si>
-  <si>
-    <t>WL-SMCW SMT Mono-color Chip LED Waterclear, size 0603, Green, 3.2V, 140deg</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>KF120-2</t>
-  </si>
-  <si>
-    <t>2.54mm Terminal</t>
-  </si>
-  <si>
-    <t>J2, J3</t>
-  </si>
-  <si>
-    <t>90StraightHeader</t>
-  </si>
-  <si>
-    <t>J4</t>
-  </si>
-  <si>
-    <t>IRLR7843TRPBF</t>
-  </si>
-  <si>
-    <t>RoHS Compliant</t>
-  </si>
-  <si>
-    <t>Q1, Q2, Q3, Q4</t>
-  </si>
-  <si>
-    <t>R1, R4, R5, R6, R9, R10</t>
-  </si>
-  <si>
-    <t>R2, R3, R13</t>
-  </si>
-  <si>
-    <t>R7, R8, R11, R12</t>
-  </si>
-  <si>
-    <t>Scr1</t>
-  </si>
-  <si>
-    <t>PC817X2NIP1B</t>
-  </si>
-  <si>
-    <t>Optocoupler DC-IN 1-CH Transistor DC-OUT 4-Pin DIP SMD T/R</t>
-  </si>
-  <si>
-    <t>U1, U4</t>
-  </si>
-  <si>
-    <t>IR2104SPBF</t>
-  </si>
-  <si>
-    <t>Half-Bridge Gate Driver IC Non-Inverting 8-SOIC</t>
-  </si>
-  <si>
-    <t>U2, U3</t>
-  </si>
-  <si>
-    <t>PCB-Pannel</t>
-  </si>
-  <si>
-    <t>C1, C4, C5, C6, C7, C8, C10</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3, C9</t>
-  </si>
-  <si>
-    <t>0106030600550</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 6 pF, 50 VDC</t>
-  </si>
-  <si>
-    <t>C11, C12</t>
-  </si>
-  <si>
-    <t>0106033300550</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 33 pF, 50 VDC</t>
-  </si>
-  <si>
-    <t>C13, C14</t>
-  </si>
-  <si>
-    <t>865080340003</t>
-  </si>
-  <si>
-    <t>V-Chip, D4 x H5.5mm, 22uF, 16V</t>
-  </si>
-  <si>
-    <t>C15, C16</t>
-  </si>
-  <si>
-    <t>C17, C18</t>
-  </si>
-  <si>
-    <t>D3, D7</t>
-  </si>
-  <si>
-    <t>D5, D6</t>
-  </si>
-  <si>
-    <t>D8, D10, D12, D14</t>
-  </si>
-  <si>
-    <t>Schottky-Diode</t>
-  </si>
-  <si>
-    <t>D9, D11, D13, D15</t>
-  </si>
-  <si>
-    <t>0605201000250F</t>
-  </si>
-  <si>
-    <t>Glass Fuse, Size 0520, 250 VAC, 10A, F</t>
-  </si>
-  <si>
-    <t>061812110024</t>
-  </si>
-  <si>
-    <t>Resettable Fuse, Size 1812, 24V, 1.1A</t>
-  </si>
-  <si>
-    <t>F2, F3</t>
-  </si>
-  <si>
-    <t>061812020030</t>
-  </si>
-  <si>
-    <t>796683-3</t>
-  </si>
-  <si>
-    <t>Wire to Board 3 Position 5 mm Pitch 30-12 AWG Euro Style Terminal Block</t>
-  </si>
-  <si>
-    <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 12p</t>
-  </si>
-  <si>
-    <t>J3_U_MotorDriverConnector1, J3_U_MotorDriverConnector2, J3_U_MotorDriverConnector3, J3_U_MotorDriverConnector4</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>WR-PHD Pin Header, THT, pitch 2.54mm, Single Row, Angled, 4p</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t>AOD4185</t>
-  </si>
-  <si>
-    <t>P-Channel 40V 40A (Tc) 2.5W (Ta), 62.5W (Tc) Surface Mount TO-252, (D-Pak)</t>
-  </si>
-  <si>
-    <t>Q4, Q5, Q6</t>
-  </si>
-  <si>
-    <t>R1, R2, R3, R15</t>
-  </si>
-  <si>
-    <t>R4, R8, R12, R14</t>
-  </si>
-  <si>
-    <t>R5, R6, R7, R9, R10, R11_U_MotorDriverConnector1, R11_U_MotorDriverConnector2, R11_U_MotorDriverConnector3, R11_U_MotorDriverConnector4</t>
-  </si>
-  <si>
-    <t>0006031211</t>
-  </si>
-  <si>
-    <t>RES, size 0603, 120 Ohm, 1/4 W</t>
-  </si>
-  <si>
-    <t>R13</t>
-  </si>
-  <si>
-    <t>0008051531</t>
-  </si>
-  <si>
-    <t>RES, size 0805, 15 KOhm, 1/8 W</t>
-  </si>
-  <si>
-    <t>R16, R17, R18, R19, R20, R21</t>
-  </si>
-  <si>
-    <t>434111043826</t>
-  </si>
-  <si>
-    <t>WS-TASV SMT Tact Switch, L6 x W3.5 x H4.3mm, 260g, SPST-NO, 12V, 50mA</t>
-  </si>
-  <si>
-    <t>SW1, SW2_U_MotorDriverConnector1, SW2_U_MotorDriverConnector2, SW2_U_MotorDriverConnector3, SW2_U_MotorDriverConnector4</t>
-  </si>
-  <si>
-    <t>STM32F103RCT6</t>
-  </si>
-  <si>
-    <t>ARMÂ® CortexÂ®-M3 STM32F1 Microcontroller IC 32-Bit 72MHz 256KB (256K x 8) FLASH 64-LQFP (10x10)</t>
-  </si>
-  <si>
-    <t>TJA1050</t>
-  </si>
-  <si>
-    <t>1/1 Transceiver Half CANbus 8-SO</t>
-  </si>
-  <si>
-    <t>CMP-200220-000002-1</t>
-  </si>
-  <si>
-    <t>Y1</t>
-  </si>
-  <si>
-    <t>C0603C200J5GACTU</t>
-  </si>
-  <si>
-    <t>CAP CER 20PF 50V 5% NP0 0603</t>
-  </si>
-  <si>
-    <t>C1_DS1, C1_DS2, C1_DS3, C1_DS4, C2_DS1, C2_DS2, C2_DS3, C2_DS4, C3_DS1, C3_DS2, C3_DS3, C3_DS4, C4_DS1, C4_DS2, C4_DS3, C4_DS4, C6_LS1, C6_LS2, C6_LS3, C6_LS4, C6_LS5, C7_LS1, C7_LS2, C7_LS3, C7_LS4, C7_LS5, C8_LS1, C8_LS2, C8_LS3, C8_LS4, C8_LS5, C9_LS1, C9_LS2, C9_LS3, C9_LS4, C9_LS5</t>
-  </si>
-  <si>
-    <t>GRM155R71C104KA88D</t>
-  </si>
-  <si>
-    <t>CAP CER 0.1UF 16V X7R 0402</t>
-  </si>
-  <si>
-    <t>C5_DS1, C5_DS2, C5_DS3, C5_DS4, C10_LS1, C10_LS2, C10_LS3, C10_LS4, C10_LS5</t>
-  </si>
-  <si>
-    <t>100 nF</t>
-  </si>
-  <si>
-    <t>C16, C18, C19, C20, C21, C22, C23, C24, C26, C27, C28, C38</t>
-  </si>
-  <si>
-    <t>10 uF</t>
-  </si>
-  <si>
-    <t>C17, C31, C34</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 100 nF</t>
-  </si>
-  <si>
-    <t>C25</t>
-  </si>
-  <si>
-    <t>10 nF</t>
-  </si>
-  <si>
     <t>1 uF</t>
   </si>
   <si>
@@ -909,9 +1135,6 @@
     <t>100 kOhm</t>
   </si>
   <si>
-    <t>RES, size 0603, 100 KOhm, 1/4 W</t>
-  </si>
-  <si>
     <t>R14, R15</t>
   </si>
   <si>
@@ -1015,6 +1238,51 @@
   </si>
   <si>
     <t>R4</t>
+  </si>
+  <si>
+    <t>PCB Price</t>
+  </si>
+  <si>
+    <t>Project related</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>MainBoard</t>
+  </si>
+  <si>
+    <t>Shopee , 6 - 8 days shipping</t>
+  </si>
+  <si>
+    <t>HBridge-MCU</t>
+  </si>
+  <si>
+    <t>HBridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CXT , 12 - 14 days shipping , PCB Pannel </t>
+  </si>
+  <si>
+    <t>HBridge-Driver</t>
+  </si>
+  <si>
+    <t>MainSensor</t>
+  </si>
+  <si>
+    <t>Sensor</t>
+  </si>
+  <si>
+    <t>CXT , 12 - 14 days shipping</t>
+  </si>
+  <si>
+    <t>ServoShield</t>
+  </si>
+  <si>
+    <t>MainBoard Sheild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total: </t>
   </si>
 </sst>
 </file>
@@ -1631,11 +1899,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
@@ -2174,13 +2448,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G57"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:G64"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="23.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="21.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="129.222222222222" customWidth="1"/>
-    <col min="3" max="3" width="59.2222222222222" customWidth="1"/>
-    <col min="5" max="6" width="15.4444444444444"/>
+    <col min="3" max="3" width="73.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="8.66666666666667" customWidth="1"/>
+    <col min="5" max="5" width="14.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="15.4444444444444" customWidth="1"/>
+    <col min="7" max="7" width="255.777777777778" customWidth="1"/>
+    <col min="8" max="8" width="76" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2206,8 +2484,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
@@ -2219,770 +2497,1549 @@
       <c r="D2">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="1">
+        <v>190</v>
+      </c>
+      <c r="F2" s="1">
+        <f t="shared" ref="F2:F11" si="0">E2*D2</f>
+        <v>1710</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
+      <c r="E3" s="1">
+        <v>400</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>16</v>
+      <c r="E4" s="1">
+        <v>1500</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>19</v>
+      <c r="E5" s="1">
+        <v>190</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>22</v>
+      <c r="E6" s="1">
+        <v>350</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
+      <c r="E7" s="1">
+        <v>190</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>28</v>
+      <c r="E8" s="1">
+        <v>190</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>500</v>
+      </c>
+      <c r="F9" s="1">
+        <f>E9*D9</f>
+        <v>500</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10">
+      <c r="E10" s="1">
+        <v>192</v>
+      </c>
+      <c r="F10" s="1">
+        <f t="shared" si="0"/>
+        <v>768</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>800</v>
+      </c>
+      <c r="F11" s="1">
+        <f>E11*D11</f>
+        <v>800</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>800</v>
+      </c>
+      <c r="F12" s="1">
+        <f>E12*D12</f>
+        <v>800</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13" s="1">
+        <v>600</v>
+      </c>
+      <c r="F13" s="1">
+        <f>E13*D9</f>
+        <v>600</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>400</v>
+      </c>
+      <c r="F14" s="1">
+        <f>E14*D11</f>
+        <v>400</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1">
+        <v>180</v>
+      </c>
+      <c r="F15" s="1">
+        <f t="shared" ref="F15:F47" si="1">E15*D15</f>
+        <v>720</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1">
+        <v>500</v>
+      </c>
+      <c r="F16" s="1">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>200</v>
+      </c>
+      <c r="F17" s="1">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>600</v>
+      </c>
+      <c r="F18" s="1">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1">
+        <v>350</v>
+      </c>
+      <c r="F19" s="1">
+        <f t="shared" si="1"/>
+        <v>700</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>170</v>
+      </c>
+      <c r="F20" s="1">
+        <f t="shared" si="1"/>
+        <v>170</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>210</v>
+      </c>
+      <c r="F21" s="1">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>180</v>
+      </c>
+      <c r="F22" s="1">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1500</v>
+      </c>
+      <c r="F23" s="1">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1700</v>
+      </c>
+      <c r="F24" s="1">
+        <f t="shared" si="1"/>
+        <v>1700</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1500</v>
+      </c>
+      <c r="F25" s="1">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F26" s="1">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>600</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1500</v>
+      </c>
+      <c r="F28" s="1">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>61032421821</v>
+      </c>
+      <c r="B30" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:4">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" spans="1:4">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" spans="1:4">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27">
-        <v>61032421821</v>
-      </c>
-      <c r="B27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29">
+      <c r="E30" s="1">
+        <v>4200</v>
+      </c>
+      <c r="F30" s="1">
+        <f t="shared" si="1"/>
+        <v>12600</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
+        <v>3500</v>
+      </c>
+      <c r="F31" s="1">
+        <f t="shared" si="1"/>
+        <v>3500</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
         <v>61032021821</v>
       </c>
-      <c r="B29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30">
+      <c r="B32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" t="s">
+        <v>125</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3700</v>
+      </c>
+      <c r="F32" s="1">
+        <f t="shared" si="1"/>
+        <v>3700</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
         <v>65100516121</v>
       </c>
-      <c r="B30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32">
-        <v>61030421121</v>
-      </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>88</v>
-      </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>95</v>
+      <c r="E33" s="1">
+        <v>800</v>
+      </c>
+      <c r="F33" s="1">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>61000421821</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="D34">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34" s="1">
+        <v>1200</v>
+      </c>
+      <c r="F34" s="1">
+        <f t="shared" si="1"/>
+        <v>2400</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
+        <v>61030621821</v>
+      </c>
+      <c r="B35" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" t="s">
+        <v>134</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F35" s="1">
+        <f t="shared" si="1"/>
+        <v>4500</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>61030421121</v>
+      </c>
+      <c r="B36" t="s">
+        <v>136</v>
+      </c>
+      <c r="C36" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1300</v>
+      </c>
+      <c r="F36" s="1">
+        <f t="shared" si="1"/>
+        <v>1300</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>61030621121</v>
+      </c>
+      <c r="B37" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" t="s">
+        <v>140</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F37" s="1">
+        <f t="shared" si="1"/>
+        <v>4500</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
         <v>61002421121</v>
       </c>
-      <c r="B35" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35">
+      <c r="B38" t="s">
+        <v>141</v>
+      </c>
+      <c r="C38" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B36" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" t="s">
-        <v>102</v>
-      </c>
-      <c r="D36">
+      <c r="E38" s="1">
+        <v>1200</v>
+      </c>
+      <c r="F38" s="1">
+        <f t="shared" si="1"/>
+        <v>3600</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C39" t="s">
+        <v>145</v>
+      </c>
+      <c r="D39">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B37" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" t="s">
-        <v>105</v>
-      </c>
-      <c r="D37">
+      <c r="E39" s="1">
+        <v>900</v>
+      </c>
+      <c r="F39" s="1">
+        <f t="shared" si="1"/>
+        <v>2700</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40">
         <v>3</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B38" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D38">
+      <c r="E40" s="1">
+        <v>1200</v>
+      </c>
+      <c r="F40" s="1">
+        <f t="shared" si="1"/>
+        <v>3600</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" t="s">
+        <v>152</v>
+      </c>
+      <c r="C41" t="s">
+        <v>153</v>
+      </c>
+      <c r="D41">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39">
+      <c r="E41" s="1">
+        <v>680</v>
+      </c>
+      <c r="F41" s="1">
+        <f t="shared" si="1"/>
+        <v>3400</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
         <v>61032021121</v>
       </c>
-      <c r="B39" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" t="s">
-        <v>110</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40">
+      <c r="B42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C42" t="s">
+        <v>156</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>4500</v>
+      </c>
+      <c r="F42" s="1">
+        <f t="shared" si="1"/>
+        <v>4500</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
         <v>61030821121</v>
       </c>
-      <c r="B40" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" t="s">
-        <v>112</v>
-      </c>
-      <c r="D40">
+      <c r="B43" t="s">
+        <v>157</v>
+      </c>
+      <c r="C43" t="s">
+        <v>158</v>
+      </c>
+      <c r="D43">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>113</v>
-      </c>
-      <c r="B41" t="s">
-        <v>114</v>
-      </c>
-      <c r="C41" t="s">
-        <v>115</v>
-      </c>
-      <c r="D41">
+      <c r="E43" s="1">
+        <v>1500</v>
+      </c>
+      <c r="F43" s="1">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>160</v>
+      </c>
+      <c r="B44" t="s">
+        <v>161</v>
+      </c>
+      <c r="C44" t="s">
+        <v>162</v>
+      </c>
+      <c r="D44">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B42" t="s">
-        <v>117</v>
-      </c>
-      <c r="C42" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42">
+      <c r="E44" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F44" s="1">
+        <f t="shared" si="1"/>
+        <v>6000</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B45" t="s">
+        <v>165</v>
+      </c>
+      <c r="C45" t="s">
+        <v>166</v>
+      </c>
+      <c r="D45">
+        <v>18</v>
+      </c>
+      <c r="E45" s="1">
+        <v>38</v>
+      </c>
+      <c r="F45" s="1">
+        <f t="shared" si="1"/>
+        <v>684</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B46" t="s">
+        <v>169</v>
+      </c>
+      <c r="C46" t="s">
+        <v>170</v>
+      </c>
+      <c r="D46">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B43" t="s">
-        <v>120</v>
-      </c>
-      <c r="C43" t="s">
-        <v>121</v>
-      </c>
-      <c r="D43">
+      <c r="E46" s="1">
+        <v>38</v>
+      </c>
+      <c r="F46" s="1">
+        <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B47" t="s">
+        <v>173</v>
+      </c>
+      <c r="C47" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47">
+        <v>7</v>
+      </c>
+      <c r="E47" s="1">
+        <v>38</v>
+      </c>
+      <c r="F47" s="1">
+        <f t="shared" si="1"/>
+        <v>266</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B48" t="s">
+        <v>177</v>
+      </c>
+      <c r="C48" t="s">
+        <v>178</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48" s="1">
+        <v>50</v>
+      </c>
+      <c r="F48" s="1">
+        <f>E48*D48</f>
+        <v>150</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B49" t="s">
+        <v>181</v>
+      </c>
+      <c r="C49" t="s">
+        <v>182</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49" s="1">
+        <v>32</v>
+      </c>
+      <c r="F49" s="1">
+        <f>E49*D49</f>
+        <v>32</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B50" t="s">
+        <v>185</v>
+      </c>
+      <c r="C50" t="s">
+        <v>186</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" s="1">
+        <v>38</v>
+      </c>
+      <c r="F50" s="1">
+        <f>E50*D50</f>
+        <v>38</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B51" t="s">
+        <v>189</v>
+      </c>
+      <c r="C51" t="s">
+        <v>190</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1">
+        <v>32</v>
+      </c>
+      <c r="F51" s="1">
+        <f>E51*D51</f>
+        <v>32</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B52" t="s">
+        <v>193</v>
+      </c>
+      <c r="C52" t="s">
+        <v>194</v>
+      </c>
+      <c r="D52">
+        <v>2</v>
+      </c>
+      <c r="E52" s="1">
+        <v>32</v>
+      </c>
+      <c r="F52" s="1">
+        <f>E52*D52</f>
+        <v>64</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B53" t="s">
+        <v>197</v>
+      </c>
+      <c r="C53" t="s">
+        <v>198</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53" s="1">
+        <v>32</v>
+      </c>
+      <c r="F53" s="1">
+        <f t="shared" ref="F53:F62" si="2">E53*D53</f>
+        <v>96</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>200</v>
+      </c>
+      <c r="B54" t="s">
+        <v>201</v>
+      </c>
+      <c r="C54" t="s">
+        <v>202</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+      <c r="E54" s="1">
+        <v>380</v>
+      </c>
+      <c r="F54" s="1">
+        <f t="shared" si="2"/>
+        <v>1520</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B55" t="s">
+        <v>205</v>
+      </c>
+      <c r="C55" t="s">
+        <v>206</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55" s="1">
+        <v>500</v>
+      </c>
+      <c r="F55" s="1">
+        <f t="shared" si="2"/>
+        <v>1500</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>208</v>
+      </c>
+      <c r="B56" t="s">
+        <v>209</v>
+      </c>
+      <c r="C56" t="s">
+        <v>210</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56" s="1">
+        <v>85000</v>
+      </c>
+      <c r="F56" s="1">
+        <f t="shared" si="2"/>
+        <v>85000</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>212</v>
+      </c>
+      <c r="B57" t="s">
+        <v>213</v>
+      </c>
+      <c r="C57" t="s">
+        <v>214</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57" s="1">
+        <v>13000</v>
+      </c>
+      <c r="F57" s="1">
+        <f t="shared" si="2"/>
+        <v>13000</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>216</v>
+      </c>
+      <c r="B58" t="s">
+        <v>217</v>
+      </c>
+      <c r="C58" t="s">
+        <v>218</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58" s="1">
+        <v>3500</v>
+      </c>
+      <c r="F58" s="1">
+        <f t="shared" si="2"/>
+        <v>3500</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>220</v>
+      </c>
+      <c r="B59" t="s">
+        <v>221</v>
+      </c>
+      <c r="C59" t="s">
+        <v>222</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59" s="1">
+        <v>33000</v>
+      </c>
+      <c r="F59" s="1">
+        <f t="shared" si="2"/>
+        <v>33000</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>224</v>
+      </c>
+      <c r="B60" t="s">
+        <v>225</v>
+      </c>
+      <c r="C60" t="s">
+        <v>226</v>
+      </c>
+      <c r="D60">
+        <v>2</v>
+      </c>
+      <c r="E60" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F60" s="1">
+        <f t="shared" si="2"/>
+        <v>8000</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7">
+      <c r="B61" t="s">
+        <v>228</v>
+      </c>
+      <c r="C61" t="s">
+        <v>229</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F61" s="1">
+        <f>E61*D62</f>
+        <v>4000</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>231</v>
+      </c>
+      <c r="B62" t="s">
+        <v>232</v>
+      </c>
+      <c r="C62" t="s">
+        <v>233</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F62" s="1">
+        <f>E62*D62</f>
+        <v>4000</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>235</v>
+      </c>
+      <c r="B63" t="s">
+        <v>235</v>
+      </c>
+      <c r="D63">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B44" t="s">
-        <v>123</v>
-      </c>
-      <c r="C44" t="s">
-        <v>124</v>
-      </c>
-      <c r="D44">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B45" t="s">
-        <v>126</v>
-      </c>
-      <c r="C45" t="s">
-        <v>127</v>
-      </c>
-      <c r="D45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B46" t="s">
-        <v>129</v>
-      </c>
-      <c r="C46" t="s">
-        <v>130</v>
-      </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B47" t="s">
-        <v>132</v>
-      </c>
-      <c r="C47" t="s">
-        <v>133</v>
-      </c>
-      <c r="D47">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B48" t="s">
-        <v>135</v>
-      </c>
-      <c r="C48" t="s">
-        <v>136</v>
-      </c>
-      <c r="D48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" spans="1:4">
-      <c r="A49" t="s">
-        <v>137</v>
-      </c>
-      <c r="C49" t="s">
-        <v>138</v>
-      </c>
-      <c r="D49">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B50" t="s">
-        <v>140</v>
-      </c>
-      <c r="C50" t="s">
-        <v>141</v>
-      </c>
-      <c r="D50">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>142</v>
-      </c>
-      <c r="B51" t="s">
-        <v>143</v>
-      </c>
-      <c r="C51" t="s">
-        <v>144</v>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
-        <v>145</v>
-      </c>
-      <c r="B52" t="s">
-        <v>146</v>
-      </c>
-      <c r="C52" t="s">
-        <v>147</v>
-      </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" t="s">
-        <v>148</v>
-      </c>
-      <c r="B53" t="s">
-        <v>149</v>
-      </c>
-      <c r="C53" t="s">
-        <v>150</v>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" t="s">
-        <v>151</v>
-      </c>
-      <c r="B54" t="s">
-        <v>152</v>
-      </c>
-      <c r="C54" t="s">
-        <v>153</v>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" t="s">
-        <v>154</v>
-      </c>
-      <c r="B55" t="s">
-        <v>155</v>
-      </c>
-      <c r="C55" t="s">
-        <v>156</v>
-      </c>
-      <c r="D55">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" t="s">
-        <v>157</v>
-      </c>
-      <c r="B56" t="s">
-        <v>158</v>
-      </c>
-      <c r="C56" t="s">
-        <v>159</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" t="s">
-        <v>160</v>
-      </c>
-      <c r="B57" t="s">
-        <v>160</v>
-      </c>
-      <c r="D57">
-        <v>5</v>
-      </c>
-      <c r="E57" s="1">
+      <c r="E63" s="1">
         <v>26400</v>
       </c>
-      <c r="F57" s="1">
-        <f>E57*D57</f>
+      <c r="F63" s="1">
+        <f>E63*D63</f>
         <v>132000</v>
       </c>
+      <c r="G63" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="64" spans="5:6">
+      <c r="E64" t="s">
+        <v>237</v>
+      </c>
+      <c r="F64" s="1">
+        <f>SUM(F2:F63)</f>
+        <v>375530</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="https://www.thegioiic.com/tu-gom-0603-100nf-0-1uf-50v" tooltip="https://www.thegioiic.com/tu-gom-0603-100nf-0-1uf-50v"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://www.thegioiic.com/tu-gom-0603-4-7uf-25v"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://www.thegioiic.com/tu-gom-0603-2-2uf-50v"/>
+    <hyperlink ref="G5" r:id="rId4" display="https://www.thegioiic.com/tu-gom-0603-10nf-50v" tooltip="https://www.thegioiic.com/tu-gom-0603-10nf-50v"/>
+    <hyperlink ref="G6" r:id="rId5" display="https://www.thegioiic.com/tu-gom-0603-1uf-50v"/>
+    <hyperlink ref="G7" r:id="rId6" display="https://www.thegioiic.com/tu-gom-0603-8pf-50v" tooltip="https://www.thegioiic.com/tu-gom-0603-8pf-50v"/>
+    <hyperlink ref="G8" r:id="rId7" display="https://www.thegioiic.com/tu-gom-0603-100pf-50v"/>
+    <hyperlink ref="G13" r:id="rId8" display="https://www.thegioiic.com/tu-gom-0603-10uf-16v"/>
+    <hyperlink ref="G10" r:id="rId1" display="https://www.thegioiic.com/tu-gom-0603-100nf-0-1uf-50v"/>
+    <hyperlink ref="G14" r:id="rId9" display="https://www.thegioiic.com/tu-gom-0603-1uf-25v" tooltip="https://www.thegioiic.com/tu-gom-0603-1uf-25v"/>
+    <hyperlink ref="G9" r:id="rId10" display="https://www.thegioiic.com/tu-gom-0603-220nf-50v"/>
+    <hyperlink ref="G15" r:id="rId11" display="https://www.thegioiic.com/led-do-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G16" r:id="rId12" display="https://www.thegioiic.com/smaj18a"/>
+    <hyperlink ref="G17" r:id="rId13" display="https://www.thegioiic.com/zmm18-diode-zener-18v-500mw-smd"/>
+    <hyperlink ref="G19" r:id="rId14" display="https://www.thegioiic.com/1n5819w-diode-schottky-1a-40v-sod-123"/>
+    <hyperlink ref="G20" r:id="rId15" display="https://www.thegioiic.com/led-xanh-duong-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G21" r:id="rId16" display="https://www.thegioiic.com/led-trang-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G18" r:id="rId17" display="https://www.thegioiic.com/led-rgb-3528-dan-smd-trong-suot"/>
+    <hyperlink ref="G22" r:id="rId11" display="https://www.thegioiic.com/led-do-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G23" r:id="rId18" display="https://www.thegioiic.com/mf-msmf110-16-2-cau-chi-tu-phuc-hoi-1812-16v-1-1a"/>
+    <hyperlink ref="G24" r:id="rId19" display="https://www.thegioiic.com/mf-msmf050-2-cau-chi-tu-phuc-hoi-1812-15v-0-5a"/>
+    <hyperlink ref="G25" r:id="rId20" display="https://www.thegioiic.com/mf-nsmf035-2-cau-chi-tu-phuc-hoi-1206-6v-0-35a"/>
+    <hyperlink ref="G26" r:id="rId21" display="https://www.thegioiic.com/minismdc020f-2-cau-chi-tu-phuc-hoi-1812-30v-200ma"/>
+    <hyperlink ref="G27" r:id="rId22" display="https://www.thegioiic.com/cbw201209u121t-ferrite-beads-2a-120-ohm-0805"/>
+    <hyperlink ref="G28" r:id="rId23" display="https://www.thegioiic.com/kf301-2-v-domino-2-chan-thang-5-08mm-300v-10a-han-pcb"/>
+    <hyperlink ref="G29" r:id="rId24" display="https://www.thegioiic.com/de-pin-cr1220-dan-smd"/>
+    <hyperlink ref="G30" r:id="rId25" display="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-24-chan-2-hang-smd"/>
+    <hyperlink ref="G31" r:id="rId26" display="https://www.thegioiic.com/misd-pp-9p-v1-khay-the-nho-microsd-9-chan-push-push"/>
+    <hyperlink ref="G32" r:id="rId27" display="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-20-chan-2-hang-smd"/>
+    <hyperlink ref="G33" r:id="rId28" display="https://www.thegioiic.com/cong-usb-mini-b-dau-cai-5-chan-smd-v1"/>
+    <hyperlink ref="G34" r:id="rId29" display="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-4-chan-2-hang-smd"/>
+    <hyperlink ref="G35" r:id="rId30" display="https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-smd"/>
+    <hyperlink ref="G37" r:id="rId30" display="https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-smd"/>
+    <hyperlink ref="G39" r:id="rId31" display="https://www.thegioiic.com/dau-sh1-0mm-4-chan-dan-smd-thang-dung"/>
+    <hyperlink ref="G38" r:id="rId29" display="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-4-chan-2-hang-smd"/>
+    <hyperlink ref="G36" r:id="rId32" display="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-6-chan-2-hang-smd"/>
+    <hyperlink ref="G40" r:id="rId33" display="https://www.thegioiic.com/dau-sh1-0mm-6-chan-dan-smd-thang-dung"/>
+    <hyperlink ref="G41" r:id="rId34" display="https://www.thegioiic.com/dau-sh1-0mm-3-chan-dan-smd-nam-ngang"/>
+    <hyperlink ref="G42" r:id="rId30" display="https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-smd"/>
+    <hyperlink ref="G43" r:id="rId35" display="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-8-chan-2-hang-smd"/>
+    <hyperlink ref="G44" r:id="rId36" display="https://www.thegioiic.com/ao3407a-mosfet-kenh-p-30v-4-3a-sot-23-3"/>
+    <hyperlink ref="G45" r:id="rId37" display="https://www.thegioiic.com/dien-tro-10-kohm-0603-1-"/>
+    <hyperlink ref="G46" r:id="rId38" display="https://www.thegioiic.com/dien-tro-1-2-kohm-0603-1-"/>
+    <hyperlink ref="G47" r:id="rId39" display="https://www.thegioiic.com/dien-tro-0-ohm-0603-1-"/>
+    <hyperlink ref="G53" r:id="rId40" display="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-"/>
+    <hyperlink ref="G54" r:id="rId41" display="https://www.thegioiic.com/vit-nhua-m3-dai-5mm"/>
+    <hyperlink ref="G55" r:id="rId42" display="https://www.thegioiic.com/nut-nhan-3x6mm-cao-5mm-2-chan-smd-dau-trang"/>
+    <hyperlink ref="G56" r:id="rId43" display="https://www.thegioiic.com/stm32f407vet6-32-bit-arm-cortex-m4-microcontroller-168mhz-512kb-flash-100-lqfp"/>
+    <hyperlink ref="G57" r:id="rId44" display="https://www.thegioiic.com/l7805acd2t-ic-on-ap-5v-1-5a"/>
+    <hyperlink ref="G58" r:id="rId45" display="https://www.thegioiic.com/ams1117-3-3v-ic-on-ap-3-3v-1a-sot-223"/>
+    <hyperlink ref="G59" r:id="rId46" display="https://www.thegioiic.com/stm32f103c8t6-32-bit-arm-cortex-m3-microcontroller-72mhz-64kb-flash-48-lqfp"/>
+    <hyperlink ref="G60" r:id="rId47" display="https://www.thegioiic.com/thach-anh-25mhz-3225-4-chan-smd"/>
+    <hyperlink ref="G61" r:id="rId48" display="https://www.thegioiic.com/thach-anh-8mhz-3225-4-chan-smd"/>
+    <hyperlink ref="G62" r:id="rId49" display="https://www.thegioiic.com/thach-anh-fc-135-32-768khz-3215"/>
+    <hyperlink ref="G11" r:id="rId50" display="https://www.thegioiic.com/tu-nhom-smd-10uf-25v-4x5-4mm"/>
+    <hyperlink ref="G12" r:id="rId51" display="https://www.thegioiic.com/tu-nhom-smd-22uf-16v-4x5-4mm"/>
+    <hyperlink ref="G48" r:id="rId52" display="https://www.thegioiic.com/dien-tro-15-kohm-0805-5-"/>
+    <hyperlink ref="G49" r:id="rId53" display="https://www.thegioiic.com/dien-tro-100-kohm-0603-5-"/>
+    <hyperlink ref="G50" r:id="rId54" display="https://www.thegioiic.com/dien-tro-1-5-kohm-0603-1-"/>
+    <hyperlink ref="G51" r:id="rId55" display="https://www.thegioiic.com/dien-tro-100-ohm-0603-5-"/>
+    <hyperlink ref="G52" r:id="rId56" display="https://www.thegioiic.com/dien-tro-20-ohm-0603-5-"/>
+    <hyperlink ref="G63" r:id="rId57" display="https://shopee.vn/S%E1%BA%A3n-xu%E1%BA%A5t-PCB-ch%E1%BA%A5t-l%C6%B0%E1%BB%A3ng-cao-%E2%80%93-MOQ-5-T%C3%B9y-ch%E1%BB%89nh-m%C3%A0u-mi%E1%BB%85n-ph%C3%AD-B%E1%BA%A3ng-%C4%91%C6%A1n-%C4%91%C3%B4i-v%C3%A0-nhi%E1%BB%81u-l%E1%BB%9Bp-i.1135296432.28315488514"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3006,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>238</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -3018,10 +4075,10 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>239</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3029,10 +4086,10 @@
         <v>10603226106.3</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>241</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>242</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -3040,14 +4097,14 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>163</v>
+      <c r="A3" s="4" t="s">
+        <v>243</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>245</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -3056,10 +4113,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -3068,13 +4125,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>247</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>248</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -3083,13 +4140,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3098,13 +4155,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -3113,13 +4170,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>252</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>253</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -3128,10 +4185,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>254</v>
       </c>
       <c r="C9" t="s">
-        <v>175</v>
+        <v>255</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3140,13 +4197,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>256</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>257</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>258</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -3154,14 +4211,14 @@
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="2" t="s">
-        <v>128</v>
+      <c r="A11" s="4" t="s">
+        <v>188</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="C11" t="s">
-        <v>179</v>
+        <v>259</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -3169,14 +4226,14 @@
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2" t="s">
-        <v>131</v>
+      <c r="A12" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="C12" t="s">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -3184,14 +4241,14 @@
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="2" t="s">
-        <v>122</v>
+      <c r="A13" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
-        <v>181</v>
+        <v>261</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -3200,10 +4257,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="C14" t="s">
-        <v>182</v>
+        <v>262</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -3212,13 +4269,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>183</v>
+        <v>263</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>264</v>
       </c>
       <c r="C15" t="s">
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -3227,13 +4284,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>266</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>267</v>
       </c>
       <c r="C16" t="s">
-        <v>188</v>
+        <v>268</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -3242,10 +4299,10 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="B17" t="s">
-        <v>189</v>
+        <v>269</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -3282,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>238</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -3294,105 +4351,105 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>239</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>31</v>
+      <c r="A2" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="D2">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>28</v>
+      <c r="A3" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>271</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>34</v>
+      <c r="A4" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>192</v>
+        <v>272</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>193</v>
+      <c r="A5" s="4" t="s">
+        <v>273</v>
       </c>
       <c r="B5" t="s">
-        <v>194</v>
+        <v>274</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>275</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>196</v>
+      <c r="A6" s="4" t="s">
+        <v>276</v>
       </c>
       <c r="B6" t="s">
-        <v>197</v>
+        <v>277</v>
       </c>
       <c r="C6" t="s">
-        <v>198</v>
+        <v>278</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>199</v>
+      <c r="A7" s="4" t="s">
+        <v>279</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="C7" t="s">
-        <v>201</v>
+        <v>281</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
+      <c r="A8" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>202</v>
+        <v>282</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -3400,13 +4457,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -3414,13 +4471,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>203</v>
+        <v>283</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -3428,13 +4485,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -3442,10 +4499,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>204</v>
+        <v>284</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -3453,13 +4510,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -3467,10 +4524,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>286</v>
       </c>
       <c r="C14" t="s">
-        <v>207</v>
+        <v>287</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -3478,41 +4535,41 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>288</v>
       </c>
       <c r="B15" t="s">
-        <v>209</v>
+        <v>289</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>210</v>
+      <c r="A16" s="4" t="s">
+        <v>290</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>291</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>292</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>213</v>
+      <c r="A17" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -3520,13 +4577,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -3534,13 +4591,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>214</v>
+        <v>293</v>
       </c>
       <c r="B19" t="s">
-        <v>215</v>
+        <v>294</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -3551,24 +4608,24 @@
         <v>61031221821</v>
       </c>
       <c r="B20" t="s">
-        <v>216</v>
+        <v>295</v>
       </c>
       <c r="C20" t="s">
-        <v>217</v>
+        <v>296</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
-        <v>106</v>
+      <c r="A21" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>218</v>
+        <v>140</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -3579,24 +4636,24 @@
         <v>61300411021</v>
       </c>
       <c r="B22" t="s">
-        <v>219</v>
+        <v>297</v>
       </c>
       <c r="C22" t="s">
-        <v>220</v>
+        <v>298</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
-        <v>100</v>
+      <c r="A23" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="B23" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="C23" t="s">
-        <v>221</v>
+        <v>299</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -3607,10 +4664,10 @@
         <v>61030621121</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="C24" t="s">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -3618,13 +4675,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -3632,83 +4689,83 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="B26" t="s">
-        <v>224</v>
+        <v>302</v>
       </c>
       <c r="C26" t="s">
-        <v>225</v>
+        <v>303</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
-        <v>131</v>
+      <c r="A27" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="B27" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="C27" t="s">
-        <v>226</v>
+        <v>304</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
-        <v>119</v>
+      <c r="A28" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="C28" t="s">
-        <v>227</v>
+        <v>305</v>
       </c>
       <c r="D28">
         <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
-        <v>122</v>
+      <c r="A29" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="B29" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="C29" t="s">
-        <v>228</v>
+        <v>306</v>
       </c>
       <c r="D29">
         <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
-        <v>229</v>
+      <c r="A30" s="4" t="s">
+        <v>307</v>
       </c>
       <c r="B30" t="s">
-        <v>230</v>
+        <v>308</v>
       </c>
       <c r="C30" t="s">
-        <v>231</v>
+        <v>309</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2" t="s">
-        <v>232</v>
+      <c r="A31" s="4" t="s">
+        <v>176</v>
       </c>
       <c r="B31" t="s">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="C31" t="s">
-        <v>234</v>
+        <v>310</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -3716,24 +4773,24 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="C32" t="s">
-        <v>138</v>
+        <v>202</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="2" t="s">
-        <v>235</v>
+      <c r="A33" s="4" t="s">
+        <v>311</v>
       </c>
       <c r="B33" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="C33" t="s">
-        <v>237</v>
+        <v>313</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -3741,13 +4798,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>238</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s">
-        <v>239</v>
+        <v>315</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>210</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -3755,13 +4812,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>240</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s">
-        <v>241</v>
+        <v>317</v>
       </c>
       <c r="C35" t="s">
-        <v>147</v>
+        <v>214</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -3769,13 +4826,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="B36" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="C36" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -3783,13 +4840,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="B37" t="s">
-        <v>155</v>
+        <v>225</v>
       </c>
       <c r="C37" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -3797,10 +4854,10 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="B38" t="s">
-        <v>189</v>
+        <v>269</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -3838,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>238</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -3850,21 +4907,21 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>239</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>318</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>319</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>320</v>
       </c>
       <c r="D2">
         <v>36</v>
@@ -3872,13 +4929,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>247</v>
+        <v>321</v>
       </c>
       <c r="B3" t="s">
-        <v>248</v>
+        <v>322</v>
       </c>
       <c r="C3" t="s">
-        <v>249</v>
+        <v>323</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -3886,13 +4943,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>250</v>
+        <v>324</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>251</v>
+        <v>325</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -3900,13 +4957,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>252</v>
+        <v>326</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>253</v>
+        <v>327</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -3914,13 +4971,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>250</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
-        <v>254</v>
+        <v>328</v>
       </c>
       <c r="C6" t="s">
-        <v>255</v>
+        <v>329</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3928,13 +4985,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>256</v>
+        <v>330</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>331</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -3942,13 +4999,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>257</v>
+        <v>332</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>258</v>
+        <v>333</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -3956,13 +5013,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>259</v>
+        <v>334</v>
       </c>
       <c r="B9" t="s">
-        <v>260</v>
+        <v>335</v>
       </c>
       <c r="C9" t="s">
-        <v>261</v>
+        <v>336</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -3970,13 +5027,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>257</v>
+        <v>332</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>262</v>
+        <v>337</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -3984,13 +5041,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>263</v>
+        <v>338</v>
       </c>
       <c r="B11" t="s">
-        <v>197</v>
+        <v>277</v>
       </c>
       <c r="C11" t="s">
-        <v>264</v>
+        <v>339</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -3998,13 +5055,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>265</v>
+        <v>340</v>
       </c>
       <c r="B12" t="s">
-        <v>266</v>
+        <v>341</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
+        <v>342</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -4012,13 +5069,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>265</v>
+        <v>340</v>
       </c>
       <c r="B13" t="s">
-        <v>266</v>
+        <v>341</v>
       </c>
       <c r="C13" t="s">
-        <v>268</v>
+        <v>343</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -4026,13 +5083,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>269</v>
+        <v>344</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>204</v>
+        <v>284</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -4040,13 +5097,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>270</v>
+        <v>345</v>
       </c>
       <c r="B15" t="s">
-        <v>271</v>
+        <v>346</v>
       </c>
       <c r="C15" t="s">
-        <v>272</v>
+        <v>347</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -4054,13 +5111,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>273</v>
+        <v>348</v>
       </c>
       <c r="B16" t="s">
-        <v>274</v>
+        <v>349</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -4068,10 +5125,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>275</v>
+        <v>350</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -4082,10 +5139,10 @@
         <v>61300621121</v>
       </c>
       <c r="B18" t="s">
-        <v>276</v>
+        <v>351</v>
       </c>
       <c r="C18" t="s">
-        <v>218</v>
+        <v>140</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -4096,38 +5153,38 @@
         <v>61300411121</v>
       </c>
       <c r="B19" t="s">
-        <v>277</v>
+        <v>352</v>
       </c>
       <c r="C19" t="s">
-        <v>220</v>
+        <v>298</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>106</v>
+      <c r="A20" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>221</v>
+        <v>299</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
-        <v>100</v>
+      <c r="A21" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="C21" t="s">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -4135,13 +5192,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>278</v>
+        <v>353</v>
       </c>
       <c r="B22" t="s">
-        <v>279</v>
+        <v>354</v>
       </c>
       <c r="C22" t="s">
-        <v>280</v>
+        <v>355</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -4149,13 +5206,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>281</v>
+        <v>356</v>
       </c>
       <c r="B23" t="s">
-        <v>282</v>
+        <v>357</v>
       </c>
       <c r="C23" t="s">
-        <v>283</v>
+        <v>358</v>
       </c>
       <c r="D23">
         <v>9</v>
@@ -4163,13 +5220,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>278</v>
+        <v>353</v>
       </c>
       <c r="B24" t="s">
-        <v>279</v>
+        <v>354</v>
       </c>
       <c r="C24" t="s">
-        <v>284</v>
+        <v>359</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -4177,13 +5234,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>285</v>
+        <v>360</v>
       </c>
       <c r="B25" t="s">
-        <v>286</v>
+        <v>361</v>
       </c>
       <c r="C25" t="s">
-        <v>287</v>
+        <v>362</v>
       </c>
       <c r="D25">
         <v>9</v>
@@ -4191,13 +5248,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>288</v>
+        <v>363</v>
       </c>
       <c r="B26" t="s">
-        <v>289</v>
+        <v>364</v>
       </c>
       <c r="C26" t="s">
-        <v>290</v>
+        <v>365</v>
       </c>
       <c r="D26">
         <v>23</v>
@@ -4205,13 +5262,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>291</v>
+        <v>366</v>
       </c>
       <c r="B27" t="s">
-        <v>292</v>
+        <v>181</v>
       </c>
       <c r="C27" t="s">
-        <v>293</v>
+        <v>367</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -4219,13 +5276,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>294</v>
+        <v>368</v>
       </c>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="C28" t="s">
-        <v>295</v>
+        <v>369</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -4233,13 +5290,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>296</v>
+        <v>370</v>
       </c>
       <c r="B29" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="C29" t="s">
-        <v>297</v>
+        <v>371</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -4247,13 +5304,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>298</v>
+        <v>372</v>
       </c>
       <c r="B30" t="s">
-        <v>299</v>
+        <v>373</v>
       </c>
       <c r="C30" t="s">
-        <v>300</v>
+        <v>374</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -4261,13 +5318,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>301</v>
+        <v>375</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="C31" t="s">
-        <v>302</v>
+        <v>376</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -4275,13 +5332,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>303</v>
+        <v>377</v>
       </c>
       <c r="B32" t="s">
-        <v>230</v>
+        <v>308</v>
       </c>
       <c r="C32" t="s">
-        <v>304</v>
+        <v>378</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4289,13 +5346,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>305</v>
+        <v>379</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="C33" t="s">
-        <v>306</v>
+        <v>380</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -4303,24 +5360,24 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>307</v>
+        <v>381</v>
       </c>
       <c r="C34" t="s">
-        <v>138</v>
+        <v>202</v>
       </c>
       <c r="D34">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="2" t="s">
-        <v>308</v>
+      <c r="A35" s="4" t="s">
+        <v>382</v>
       </c>
       <c r="B35" t="s">
-        <v>309</v>
+        <v>383</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>206</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -4328,13 +5385,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="B36" t="s">
-        <v>152</v>
+        <v>221</v>
       </c>
       <c r="C36" t="s">
-        <v>147</v>
+        <v>214</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -4342,13 +5399,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>310</v>
+        <v>384</v>
       </c>
       <c r="B37" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="C37" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -4356,13 +5413,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="B38" t="s">
-        <v>241</v>
+        <v>317</v>
       </c>
       <c r="C38" t="s">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -4370,13 +5427,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>312</v>
+        <v>386</v>
       </c>
       <c r="B39" t="s">
-        <v>313</v>
+        <v>387</v>
       </c>
       <c r="C39" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -4384,10 +5441,10 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="B40" t="s">
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="E40" s="1">
         <v>20000</v>
@@ -4421,7 +5478,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>238</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -4433,21 +5490,21 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>239</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>25</v>
+      <c r="A2" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>314</v>
+        <v>388</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -4455,13 +5512,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>315</v>
+        <v>389</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -4469,10 +5526,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>206</v>
+        <v>286</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -4480,27 +5537,27 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>316</v>
+        <v>390</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>317</v>
+      <c r="A6" s="4" t="s">
+        <v>391</v>
       </c>
       <c r="B6" t="s">
-        <v>318</v>
+        <v>392</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -4508,13 +5565,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -4525,10 +5582,10 @@
         <v>61032421821</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>319</v>
+        <v>393</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -4539,10 +5596,10 @@
         <v>61030821821</v>
       </c>
       <c r="B9" t="s">
-        <v>320</v>
+        <v>394</v>
       </c>
       <c r="C9" t="s">
-        <v>321</v>
+        <v>395</v>
       </c>
       <c r="D9">
         <v>16</v>
@@ -4553,10 +5610,10 @@
         <v>61032021821</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>322</v>
+        <v>396</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -4567,10 +5624,10 @@
         <v>61002421121</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="C11" t="s">
-        <v>323</v>
+        <v>397</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -4581,10 +5638,10 @@
         <v>61032021121</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="C12" t="s">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -4595,10 +5652,10 @@
         <v>61300311121</v>
       </c>
       <c r="B13" t="s">
-        <v>324</v>
+        <v>398</v>
       </c>
       <c r="C13" t="s">
-        <v>325</v>
+        <v>399</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -4606,41 +5663,41 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="B14" t="s">
-        <v>224</v>
+        <v>302</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>232</v>
+      <c r="A15" s="4" t="s">
+        <v>176</v>
       </c>
       <c r="B15" t="s">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="C15" t="s">
-        <v>326</v>
+        <v>400</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>131</v>
+      <c r="A16" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="B16" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="C16" t="s">
-        <v>327</v>
+        <v>401</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -4648,10 +5705,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="C17" t="s">
-        <v>138</v>
+        <v>202</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -4659,10 +5716,10 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="B18" t="s">
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -4673,6 +5730,165 @@
       <c r="F18" s="1">
         <f>E18*D18</f>
         <v>132000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="18.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="14.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="10.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="15.4444444444444" customWidth="1"/>
+    <col min="6" max="6" width="47.2222222222222" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C3" s="1">
+        <v>26400</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1">
+        <f>D3*C3</f>
+        <v>132000</v>
+      </c>
+      <c r="F3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B4" t="s">
+        <v>408</v>
+      </c>
+      <c r="C4" s="1">
+        <v>62000</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1">
+        <f>D4*C4</f>
+        <v>310000</v>
+      </c>
+      <c r="F4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+      <c r="C5" s="1">
+        <v>62000</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1">
+        <f>D5*C5</f>
+        <v>310000</v>
+      </c>
+      <c r="F5" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>411</v>
+      </c>
+      <c r="B6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C6" s="1">
+        <v>20000</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <f>D6*C6</f>
+        <v>100000</v>
+      </c>
+      <c r="F6" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>414</v>
+      </c>
+      <c r="B7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26400</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1">
+        <f>D7*C7</f>
+        <v>132000</v>
+      </c>
+      <c r="F7" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5">
+      <c r="D8" t="s">
+        <v>416</v>
+      </c>
+      <c r="E8" s="1">
+        <f>SUM(E3:E7)-E5</f>
+        <v>674000</v>
       </c>
     </row>
   </sheetData>

--- a/2.Hardware/1.PCB/BOMTotal.xlsx
+++ b/2.Hardware/1.PCB/BOMTotal.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8280"/>
   </bookViews>
   <sheets>
     <sheet name="MainBoard" sheetId="7" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="462">
   <si>
     <t>Name</t>
   </si>
@@ -745,7 +745,7 @@
     <t>https://shopee.vn/S%E1%BA%A3n-xu%E1%BA%A5t-PCB-ch%E1%BA%A5t-l%C6%B0%E1%BB%A3ng-cao-%E2%80%93-MOQ-5-T%C3%B9y-ch%E1%BB%89nh-m%C3%A0u-mi%E1%BB%85n-ph%C3%AD-B%E1%BA%A3ng-%C4%91%C6%A1n-%C4%91%C3%B4i-v%C3%A0-nhi%E1%BB%81u-l%E1%BB%9Bp-i.1135296432.28315488514</t>
   </si>
   <si>
-    <t>Tổng tiền</t>
+    <t>Total</t>
   </si>
   <si>
     <t>Type</t>
@@ -763,7 +763,7 @@
     <t>C1, C2</t>
   </si>
   <si>
-    <t>0108051031050</t>
+    <t>https://www.thegioiic.com/tu-gom-0603-22uf-10v</t>
   </si>
   <si>
     <t>CAP, size 0805, 10 nF, 50 VDC</t>
@@ -772,10 +772,19 @@
     <t>C3</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/tu-gom-0805-10nf-50v</t>
+  </si>
+  <si>
+    <t>Diode 1N5819W</t>
+  </si>
+  <si>
+    <t>1N5819W Diode Schottky 1A 40V SOD-123</t>
+  </si>
+  <si>
     <t>D1, D2</t>
   </si>
   <si>
-    <t>160603GreenClear</t>
+    <t>LED xanh lá</t>
   </si>
   <si>
     <t>WL-SMCW SMT Mono-color Chip LED Waterclear, size 0603, Green, 3.2V, 140deg</t>
@@ -784,46 +793,73 @@
     <t>D3</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/led-xanh-la-0603-dan-smd-trong-suot</t>
+  </si>
+  <si>
+    <t>LED xanh dương</t>
+  </si>
+  <si>
     <t>D4</t>
   </si>
   <si>
-    <t>KF120-2</t>
+    <t>KF301-2-V Domino 2 Chân Thẳng 5.08mm 300V 10A Hàn PCB</t>
   </si>
   <si>
     <t>2.54mm Terminal</t>
   </si>
   <si>
+    <t>KF120-2-V Domino 2 Chân Thẳng 2.54mm 150V 6A Hàn PCB</t>
+  </si>
+  <si>
     <t>J2, J3</t>
   </si>
   <si>
-    <t>90StraightHeader</t>
+    <t>https://www.thegioiic.com/kf120-2-v-domino-2-chan-thang-2-54mm-150v-6a-han-pcb</t>
+  </si>
+  <si>
+    <t>Hàng Rào Đực Đôi 2.54mm</t>
+  </si>
+  <si>
+    <t>Hàng Rào Đực Đôi 2.54mm 80 Chân 2 Hàng Cao 21mm Xuyên Lỗ</t>
   </si>
   <si>
     <t>J4</t>
   </si>
   <si>
-    <t>IRLR7843TRPBF</t>
-  </si>
-  <si>
-    <t>RoHS Compliant</t>
+    <t>https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-cao-21mm-xuyen-lo</t>
+  </si>
+  <si>
+    <t>IRLR7843</t>
+  </si>
+  <si>
+    <t>IRLR7843 MOSFET Kênh N 30V 161A TO-252-3</t>
   </si>
   <si>
     <t>Q1, Q2, Q3, Q4</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/irlr7843-mosfet-kenh-n-30v-161a-to-252-3</t>
+  </si>
+  <si>
     <t>R1, R4, R5, R6, R9, R10</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/dien-tro-100-ohm-0603-1-</t>
+  </si>
+  <si>
     <t>R2, R3, R13</t>
   </si>
   <si>
     <t>R7, R8, R11, R12</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/dien-tro-10-kohm-0603-5-</t>
+  </si>
+  <si>
     <t>Scr1</t>
   </si>
   <si>
-    <t>PC817X2NIP1B</t>
+    <t>PC817X2NIPW</t>
   </si>
   <si>
     <t>Optocoupler DC-IN 1-CH Transistor DC-OUT 4-Pin DIP SMD T/R</t>
@@ -832,6 +868,9 @@
     <t>U1, U4</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/pc817x2nipw-optoisolator-transistor-output-5000vrms-1-channel-sop-4</t>
+  </si>
+  <si>
     <t>IR2104SPBF</t>
   </si>
   <si>
@@ -841,6 +880,9 @@
     <t>U2, U3</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/ir2104spbf-mosfet-2-ngo-ra-360-ma-20v-8-soic</t>
+  </si>
+  <si>
     <t>PCB-Pannel</t>
   </si>
   <si>
@@ -850,28 +892,25 @@
     <t>C2</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/tu-gom-0603-10uf-25v</t>
+  </si>
+  <si>
     <t>C3, C9</t>
   </si>
   <si>
-    <t>0106030600550</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 6 pF, 50 VDC</t>
+    <t>CAP, size 0603, 8 pF, 50 VDC</t>
   </si>
   <si>
     <t>C11, C12</t>
   </si>
   <si>
-    <t>0106033300550</t>
-  </si>
-  <si>
     <t>CAP, size 0603, 33 pF, 50 VDC</t>
   </si>
   <si>
     <t>C13, C14</t>
   </si>
   <si>
-    <t>865080340003</t>
+    <t>https://www.thegioiic.com/tu-gom-0603-33pf-50v</t>
   </si>
   <si>
     <t>V-Chip, D4 x H5.5mm, 22uF, 16V</t>
@@ -883,28 +922,34 @@
     <t>C17, C18</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/led-xanh-duong-0805-dan-smd-trong-suot</t>
+  </si>
+  <si>
+    <t>LED đỏ</t>
+  </si>
+  <si>
     <t>D3, D7</t>
   </si>
   <si>
+    <t>LED trắng</t>
+  </si>
+  <si>
     <t>D5, D6</t>
   </si>
   <si>
     <t>D8, D10, D12, D14</t>
   </si>
   <si>
-    <t>Schottky-Diode</t>
+    <t>Diode Zener 18V</t>
   </si>
   <si>
     <t>D9, D11, D13, D15</t>
   </si>
   <si>
-    <t>0605201000250F</t>
-  </si>
-  <si>
     <t>Glass Fuse, Size 0520, 250 VAC, 10A, F</t>
   </si>
   <si>
-    <t>061812110024</t>
+    <t>https://www.thegioiic.com/cau-chi-ong-thuy-tinh-10a-5x20mm-toc-do-f</t>
   </si>
   <si>
     <t>Resettable Fuse, Size 1812, 24V, 1.1A</t>
@@ -913,393 +958,500 @@
     <t>F2, F3</t>
   </si>
   <si>
-    <t>796683-3</t>
+    <t>https://www.thegioiic.com/mf-msmf110-24x-2-cau-chi-tu-phuc-hoi-1812-24v-1-1a</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/mf-msmf020-2-cau-chi-tu-phuc-hoi-1812-0-20a-30v</t>
+  </si>
+  <si>
+    <t>KF301-3-V Domino 3 Chân Thẳng 5.08mm 300V 10A Hàn PCB</t>
   </si>
   <si>
     <t>Wire to Board 3 Position 5 mm Pitch 30-12 AWG Euro Style Terminal Block</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/kf301-3-v-domino-3-chan-thang-5-08mm-300v-10a-han-pcb</t>
+  </si>
+  <si>
+    <t>Hàng Rào Cái Đôi 2.54mm 12 Chân 2 Hàng SMD</t>
+  </si>
+  <si>
     <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 12p</t>
   </si>
   <si>
     <t>J3_U_MotorDriverConnector1, J3_U_MotorDriverConnector2, J3_U_MotorDriverConnector3, J3_U_MotorDriverConnector4</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-12-chan-2-hang-smd</t>
+  </si>
+  <si>
+    <t>Đầu SH1.0mm 3 Chân Dán SMD Thẳng Đứng</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dau-sh1-0mm-3-chan-dan-smd-thang-dung</t>
+  </si>
+  <si>
+    <t>Hàng Rào Đực Đơn 2.54mm 40 Chân Cong 1 Hàng Cao 6mm Xuyên Lỗ</t>
+  </si>
+  <si>
     <t>WR-PHD Pin Header, THT, pitch 2.54mm, Single Row, Angled, 4p</t>
   </si>
   <si>
     <t>P2</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/hang-rao-duc-don-2-54mm-40-chan-cong-1-hang-cao-6mm-xuyen-lo</t>
+  </si>
+  <si>
+    <t>Đầu SH1.0mm 4 Chân Dán SMD Thẳng Đứng</t>
+  </si>
+  <si>
     <t>P3</t>
   </si>
   <si>
+    <t>Hàng Rào Đực Đôi 2.54mm 80 Chân 2 Hàng SMD</t>
+  </si>
+  <si>
     <t>P4</t>
   </si>
   <si>
+    <t>AO3407A MOSFET Kênh P 30V 4.3A SOT-23-3</t>
+  </si>
+  <si>
+    <t>AOD4185 MOSFET Kênh P 40V 40A TO-252-2 DPAK</t>
+  </si>
+  <si>
+    <t>P-Channel 40V 40A (Tc) 2.5W (Ta), 62.5W (Tc) Surface Mount TO-252, (D-Pak)</t>
+  </si>
+  <si>
+    <t>Q4, Q5, Q6</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/aod4185-mosfet-kenh-p-40v-40a-to-252-2-dpak</t>
+  </si>
+  <si>
+    <t>R1, R2, R3, R15</t>
+  </si>
+  <si>
+    <t>R4, R8, R12, R14</t>
+  </si>
+  <si>
+    <t>R5, R6, R7, R9, R10, R11_U_MotorDriverConnector1, R11_U_MotorDriverConnector2, R11_U_MotorDriverConnector3, R11_U_MotorDriverConnector4</t>
+  </si>
+  <si>
+    <t>RES, size 0603, 120 Ohm, 1/4 W</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-120-ohm-0603-1-</t>
+  </si>
+  <si>
+    <t>RES, size 0805, 10 KOhm, 1/8 W</t>
+  </si>
+  <si>
+    <t>R16, R17, R18, R19, R20, R21</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-10-kohm-0805-1-</t>
+  </si>
+  <si>
+    <t>Nút Nhấn 3x6mm Cao 2.5mm 2 Chân SMD Đầu Đỏ</t>
+  </si>
+  <si>
+    <t>WS-TASV SMT Tact Switch, L6 x W3.5 x H4.3mm, 260g, SPST-NO, 12V, 50mA</t>
+  </si>
+  <si>
+    <t>SW1, SW2_U_MotorDriverConnector1, SW2_U_MotorDriverConnector2, SW2_U_MotorDriverConnector3, SW2_U_MotorDriverConnector4</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/nut-nhan-3x6mm-cao-2-5mm-2-chan-smd-dau-do</t>
+  </si>
+  <si>
+    <t>STM32F103RCT6</t>
+  </si>
+  <si>
+    <t>ARMÂ® CortexÂ®-M3 STM32F1 Microcontroller IC 32-Bit 72MHz 256KB (256K x 8) FLASH 64-LQFP (10x10)</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/stm32f103rct6-64-lqfp-32-bit-arm-cortex-m3-microcontroller-72mhz-256kb-flash</t>
+  </si>
+  <si>
+    <t>TJA1050T IC CAN Transceiver 8-SOIC</t>
+  </si>
+  <si>
+    <t>1/1 Transceiver Half CANbus 8-SO</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tja1050t-ic-can-transceiver-8-soic</t>
+  </si>
+  <si>
+    <t>AMS1117-3.3V IC Ổn Áp 3.3V 1A SOT-223</t>
+  </si>
+  <si>
+    <t>Thạch Anh 8MHz 3225 4 Chân SMD</t>
+  </si>
+  <si>
+    <t>CRYSTAL 8.000MHZ 8PF SMD</t>
+  </si>
+  <si>
+    <t>C0603C200J5GACTU</t>
+  </si>
+  <si>
+    <t>100nF 0603</t>
+  </si>
+  <si>
+    <t>C1_DS1, C1_DS2, C1_DS3, C1_DS4, C2_DS1, C2_DS2, C2_DS3, C2_DS4, C3_DS1, C3_DS2, C3_DS3, C3_DS4, C4_DS1, C4_DS2, C4_DS3, C4_DS4, C6_LS1, C6_LS2, C6_LS3, C6_LS4, C6_LS5, C7_LS1, C7_LS2, C7_LS3, C7_LS4, C7_LS5, C8_LS1, C8_LS2, C8_LS3, C8_LS4, C8_LS5, C9_LS1, C9_LS2, C9_LS3, C9_LS4, C9_LS5</t>
+  </si>
+  <si>
+    <t>GRM155R71C104KA88D</t>
+  </si>
+  <si>
+    <t>100NF 0402</t>
+  </si>
+  <si>
+    <t>C5_DS1, C5_DS2, C5_DS3, C5_DS4, C10_LS1, C10_LS2, C10_LS3, C10_LS4, C10_LS5</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-gom-0402-100nf-0-1uf-50v</t>
+  </si>
+  <si>
+    <t>100 nF</t>
+  </si>
+  <si>
+    <t>C16, C18, C19, C20, C21, C22, C23, C24, C26, C27, C28, C38</t>
+  </si>
+  <si>
+    <t>10 uF</t>
+  </si>
+  <si>
+    <t>C17, C31, C34</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 100 nF</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>10 nF</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>1 uF</t>
+  </si>
+  <si>
+    <t>C30, C32, C33</t>
+  </si>
+  <si>
+    <t>22 pF</t>
+  </si>
+  <si>
+    <t>CAP, size 0603, 22 pF, 50 VDC</t>
+  </si>
+  <si>
+    <t>C35, C37</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-gom-0603-22pf-50v</t>
+  </si>
+  <si>
+    <t>C36</t>
+  </si>
+  <si>
+    <t>30 pF</t>
+  </si>
+  <si>
+    <t>C39, C40</t>
+  </si>
+  <si>
+    <t>WP7113SRC/DU</t>
+  </si>
+  <si>
+    <t>Red 640nm LED Indication - Discrete 1.85V Radial</t>
+  </si>
+  <si>
+    <t>D1_DS1, D1_DS2, D1_DS3, D1_DS4</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/cap-led-5mm-thu-phat-hong-ngoai-940nm</t>
+  </si>
+  <si>
+    <t>D2_LS1, D2_LS2, D2_LS3, D2_LS4, D2_LS5</t>
+  </si>
+  <si>
+    <t>Red, 2V</t>
+  </si>
+  <si>
+    <t>HSMW-C191</t>
+  </si>
+  <si>
+    <t>LED Uni-Color White, 78 mW, 20 mA, -40 to 85 degC, 2-Pin SMD, RoHS, Tape and Reel</t>
+  </si>
+  <si>
+    <t>DS1_LS1, DS1_LS2, DS1_LS3, DS1_LS4, DS1_LS5</t>
+  </si>
+  <si>
+    <t>BLM21AG121SN1D</t>
+  </si>
+  <si>
+    <t>FERRITE BEAD 120 OHM 0805 1LN</t>
+  </si>
+  <si>
+    <t>B2B-XH-A</t>
+  </si>
+  <si>
+    <t>WR-WTB SMT Male Vertical Shrouded Header, pitch 2.54mm, 4p</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dau-xh2-54mm-2-chan-thang-xuyen-lo</t>
+  </si>
+  <si>
+    <t>WR-PHD Pin Header, THT, pitch 2.54mm, Dual Row, Vertical, 6p</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/hang-rao-duc-don-2-54mm-40-chan-1-hang-cao-11-2mm-xuyen-lo</t>
+  </si>
+  <si>
+    <t>WR-PHD Pin Header, THT, pitch 2.54mm, Single Row, Vertical, 4p</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>SFH_313_FA-3/4</t>
+  </si>
+  <si>
+    <t>Phototransistors 870nm Top View Radial - 2 Leads</t>
+  </si>
+  <si>
+    <t>Q1_DS1, Q1_DS2, Q1_DS3, Q1_DS4</t>
+  </si>
+  <si>
+    <t>BC817-16LT1G</t>
+  </si>
+  <si>
+    <t>General Purpose Transistor, NPN Silicon, 3-Pin SOT-23, Pb-Free, Tape and Reel</t>
+  </si>
+  <si>
+    <t>Q2_DS1, Q2_DS2, Q2_DS3, Q2_DS4, Q4_LS1, Q4_LS2, Q4_LS3, Q4_LS4, Q4_LS5</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/bc817-transistor-npn-45v-0-5a-3-chan-sot-23</t>
+  </si>
+  <si>
+    <t>Q3_LS1, Q3_LS2, Q3_LS3, Q3_LS4, Q3_LS5</t>
+  </si>
+  <si>
+    <t>75 Ohm</t>
+  </si>
+  <si>
+    <t>RES, size 0603, 75 Ohm, 1/4 W</t>
+  </si>
+  <si>
+    <t>R1_DS1, R1_DS2, R1_DS3, R1_DS4, R4_LS1, R4_LS2, R4_LS3, R4_LS4, R4_LS5</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-75-ohm-0603-5-</t>
+  </si>
+  <si>
+    <t>1 kOhm</t>
+  </si>
+  <si>
+    <t>R2_DS1, R2_DS2, R2_DS3, R2_DS4, R3_DS1, R3_DS2, R3_DS3, R3_DS4, R5_LS1, R5_LS2, R5_LS3, R5_LS4, R5_LS5, R6_LS1, R6_LS2, R6_LS3, R6_LS4, R6_LS5, R7_LS1, R7_LS2, R7_LS3, R7_LS4, R7_LS5</t>
+  </si>
+  <si>
+    <t>100 kOhm</t>
+  </si>
+  <si>
+    <t>R14, R15</t>
+  </si>
+  <si>
+    <t>R16, R17</t>
+  </si>
+  <si>
+    <t>10 kOhm</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>1 MOhm</t>
+  </si>
+  <si>
+    <t>RES, size 0603, 1 MOhm, 1/4 W</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-1-mohm-0603-5-</t>
+  </si>
+  <si>
+    <t>0 Ohm</t>
+  </si>
+  <si>
+    <t>R20, R22</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-0-ohm-0603-5-</t>
+  </si>
+  <si>
+    <t>120 Ohm</t>
+  </si>
+  <si>
+    <t>R21</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/dien-tro-120-ohm-0603-5-</t>
+  </si>
+  <si>
+    <t>1k Ohm</t>
+  </si>
+  <si>
+    <t>R23, R24</t>
+  </si>
+  <si>
+    <t>M3Screw</t>
+  </si>
+  <si>
+    <t>430152043826</t>
+  </si>
+  <si>
+    <t>WS-TASV SMT Tact Switch, L6 x W6 x H4.3mm, 260g, SPST-NO, 12V, 50mA</t>
+  </si>
+  <si>
+    <t>3.3V, 1A</t>
+  </si>
+  <si>
+    <t>TJA1050T</t>
+  </si>
+  <si>
+    <t>ABM8AIG-8.000MHZ-8-V1R-T</t>
+  </si>
+  <si>
+    <t>8 MHz Â±10ppm Crystal 8pF 500 Ohms 4-SMD, No Lead</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/tu-gom-0805-100nf-0-1uf-50v</t>
+  </si>
+  <si>
+    <t>D1, D3</t>
+  </si>
+  <si>
+    <t>18V Zener diode</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>0605201000250</t>
+  </si>
+  <si>
+    <t>Ceramic Fuse, Size 0520, 250 VAC, 10A</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/cau-chi-ong-thuy-tinh-30a-5x20mm-toc-do-f</t>
+  </si>
+  <si>
+    <t>J2, J3, J5</t>
+  </si>
+  <si>
+    <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 8p</t>
+  </si>
+  <si>
+    <t>J4, J7</t>
+  </si>
+  <si>
+    <t>J6</t>
+  </si>
+  <si>
+    <t>P1, P2, P3</t>
+  </si>
+  <si>
+    <t>WR-PHD Pin Header, THT, pitch 2.54mm, Single Row, Vertical, 3p</t>
+  </si>
+  <si>
+    <t>P5, P6, P7, P8, P9, P10, P11, P12, P13, P14, P15, P16, P17, P18, P19, P20</t>
+  </si>
+  <si>
     <t>AOD4185</t>
   </si>
   <si>
-    <t>P-Channel 40V 40A (Tc) 2.5W (Ta), 62.5W (Tc) Surface Mount TO-252, (D-Pak)</t>
-  </si>
-  <si>
-    <t>Q4, Q5, Q6</t>
-  </si>
-  <si>
-    <t>R1, R2, R3, R15</t>
-  </si>
-  <si>
-    <t>R4, R8, R12, R14</t>
-  </si>
-  <si>
-    <t>R5, R6, R7, R9, R10, R11_U_MotorDriverConnector1, R11_U_MotorDriverConnector2, R11_U_MotorDriverConnector3, R11_U_MotorDriverConnector4</t>
-  </si>
-  <si>
-    <t>0006031211</t>
-  </si>
-  <si>
-    <t>RES, size 0603, 120 Ohm, 1/4 W</t>
-  </si>
-  <si>
-    <t>R13</t>
-  </si>
-  <si>
-    <t>R16, R17, R18, R19, R20, R21</t>
-  </si>
-  <si>
-    <t>434111043826</t>
-  </si>
-  <si>
-    <t>WS-TASV SMT Tact Switch, L6 x W3.5 x H4.3mm, 260g, SPST-NO, 12V, 50mA</t>
-  </si>
-  <si>
-    <t>SW1, SW2_U_MotorDriverConnector1, SW2_U_MotorDriverConnector2, SW2_U_MotorDriverConnector3, SW2_U_MotorDriverConnector4</t>
-  </si>
-  <si>
-    <t>STM32F103RCT6</t>
-  </si>
-  <si>
-    <t>ARMÂ® CortexÂ®-M3 STM32F1 Microcontroller IC 32-Bit 72MHz 256KB (256K x 8) FLASH 64-LQFP (10x10)</t>
-  </si>
-  <si>
-    <t>TJA1050</t>
-  </si>
-  <si>
-    <t>1/1 Transceiver Half CANbus 8-SO</t>
-  </si>
-  <si>
-    <t>C0603C200J5GACTU</t>
-  </si>
-  <si>
-    <t>CAP CER 20PF 50V 5% NP0 0603</t>
-  </si>
-  <si>
-    <t>C1_DS1, C1_DS2, C1_DS3, C1_DS4, C2_DS1, C2_DS2, C2_DS3, C2_DS4, C3_DS1, C3_DS2, C3_DS3, C3_DS4, C4_DS1, C4_DS2, C4_DS3, C4_DS4, C6_LS1, C6_LS2, C6_LS3, C6_LS4, C6_LS5, C7_LS1, C7_LS2, C7_LS3, C7_LS4, C7_LS5, C8_LS1, C8_LS2, C8_LS3, C8_LS4, C8_LS5, C9_LS1, C9_LS2, C9_LS3, C9_LS4, C9_LS5</t>
-  </si>
-  <si>
-    <t>GRM155R71C104KA88D</t>
-  </si>
-  <si>
-    <t>CAP CER 0.1UF 16V X7R 0402</t>
-  </si>
-  <si>
-    <t>C5_DS1, C5_DS2, C5_DS3, C5_DS4, C10_LS1, C10_LS2, C10_LS3, C10_LS4, C10_LS5</t>
-  </si>
-  <si>
-    <t>100 nF</t>
-  </si>
-  <si>
-    <t>C16, C18, C19, C20, C21, C22, C23, C24, C26, C27, C28, C38</t>
-  </si>
-  <si>
-    <t>10 uF</t>
-  </si>
-  <si>
-    <t>C17, C31, C34</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 100 nF</t>
-  </si>
-  <si>
-    <t>C25</t>
-  </si>
-  <si>
-    <t>10 nF</t>
-  </si>
-  <si>
-    <t>C29</t>
-  </si>
-  <si>
-    <t>1 uF</t>
-  </si>
-  <si>
-    <t>C30, C32, C33</t>
-  </si>
-  <si>
-    <t>22 pF</t>
-  </si>
-  <si>
-    <t>CAP, size 0603, 22 pF, 50 VDC</t>
-  </si>
-  <si>
-    <t>C35, C37</t>
-  </si>
-  <si>
-    <t>C36</t>
-  </si>
-  <si>
-    <t>30 pF</t>
-  </si>
-  <si>
-    <t>C39, C40</t>
-  </si>
-  <si>
-    <t>WP7113SRC/DU</t>
-  </si>
-  <si>
-    <t>Red 640nm LED Indication - Discrete 1.85V Radial</t>
-  </si>
-  <si>
-    <t>D1_DS1, D1_DS2, D1_DS3, D1_DS4</t>
-  </si>
-  <si>
-    <t>D2_LS1, D2_LS2, D2_LS3, D2_LS4, D2_LS5</t>
-  </si>
-  <si>
-    <t>Red, 2V</t>
-  </si>
-  <si>
-    <t>HSMW-C191</t>
-  </si>
-  <si>
-    <t>LED Uni-Color White, 78 mW, 20 mA, -40 to 85 degC, 2-Pin SMD, RoHS, Tape and Reel</t>
-  </si>
-  <si>
-    <t>DS1_LS1, DS1_LS2, DS1_LS3, DS1_LS4, DS1_LS5</t>
-  </si>
-  <si>
-    <t>BLM21AG121SN1D</t>
-  </si>
-  <si>
-    <t>FERRITE BEAD 120 OHM 0805 1LN</t>
-  </si>
-  <si>
-    <t>B2B-XH-A</t>
-  </si>
-  <si>
-    <t>WR-PHD Pin Header, THT, pitch 2.54mm, Dual Row, Vertical, 6p</t>
-  </si>
-  <si>
-    <t>WR-PHD Pin Header, THT, pitch 2.54mm, Single Row, Vertical, 4p</t>
-  </si>
-  <si>
-    <t>SFH_313_FA-3/4</t>
-  </si>
-  <si>
-    <t>Phototransistors 870nm Top View Radial - 2 Leads</t>
-  </si>
-  <si>
-    <t>Q1_DS1, Q1_DS2, Q1_DS3, Q1_DS4</t>
-  </si>
-  <si>
-    <t>BC817-16LT1G</t>
-  </si>
-  <si>
-    <t>General Purpose Transistor, NPN Silicon, 3-Pin SOT-23, Pb-Free, Tape and Reel</t>
-  </si>
-  <si>
-    <t>Q2_DS1, Q2_DS2, Q2_DS3, Q2_DS4, Q4_LS1, Q4_LS2, Q4_LS3, Q4_LS4, Q4_LS5</t>
-  </si>
-  <si>
-    <t>Q3_LS1, Q3_LS2, Q3_LS3, Q3_LS4, Q3_LS5</t>
-  </si>
-  <si>
-    <t>RC0603FR-072K2L</t>
-  </si>
-  <si>
-    <t>Thick Film Resistor, 2.2 KOhm, 100 mW, 50 V, +/- 1%, -55 to 155 degC, 2-Pin SMD (0603), RoHS, Tape and Reel</t>
-  </si>
-  <si>
-    <t>R1_DS1, R1_DS2, R1_DS3, R1_DS4, R4_LS1, R4_LS2, R4_LS3, R4_LS4, R4_LS5</t>
-  </si>
-  <si>
-    <t>ERJ2GE0R00X</t>
-  </si>
-  <si>
-    <t>Chip Resistor, 0 Ohm, 0.1 W, -55 to 155 degC, 0402 (1005 Metric), RoHS, Tape and Reel</t>
-  </si>
-  <si>
-    <t>R2_DS1, R2_DS2, R2_DS3, R2_DS4, R3_DS1, R3_DS2, R3_DS3, R3_DS4, R5_LS1, R5_LS2, R5_LS3, R5_LS4, R5_LS5, R6_LS1, R6_LS2, R6_LS3, R6_LS4, R6_LS5, R7_LS1, R7_LS2, R7_LS3, R7_LS4, R7_LS5</t>
-  </si>
-  <si>
-    <t>100 kOhm</t>
-  </si>
-  <si>
-    <t>R14, R15</t>
-  </si>
-  <si>
-    <t>1 kOhm</t>
-  </si>
-  <si>
-    <t>R16, R17</t>
-  </si>
-  <si>
-    <t>10 kOhm</t>
-  </si>
-  <si>
-    <t>R18</t>
-  </si>
-  <si>
-    <t>1 MOhm</t>
-  </si>
-  <si>
-    <t>RES, size 0603, 1 MOhm, 1/4 W</t>
-  </si>
-  <si>
-    <t>R19</t>
-  </si>
-  <si>
-    <t>0 Ohm</t>
-  </si>
-  <si>
-    <t>R20, R22</t>
-  </si>
-  <si>
-    <t>120 Ohm</t>
-  </si>
-  <si>
-    <t>R21</t>
-  </si>
-  <si>
-    <t>1k Ohm</t>
-  </si>
-  <si>
-    <t>R23, R24</t>
-  </si>
-  <si>
-    <t>M3Screw</t>
-  </si>
-  <si>
-    <t>430152043826</t>
-  </si>
-  <si>
-    <t>WS-TASV SMT Tact Switch, L6 x W6 x H4.3mm, 260g, SPST-NO, 12V, 50mA</t>
-  </si>
-  <si>
-    <t>3.3V, 1A</t>
-  </si>
-  <si>
-    <t>TJA1050T</t>
-  </si>
-  <si>
-    <t>ABM8AIG-8.000MHZ-8-V1R-T</t>
-  </si>
-  <si>
-    <t>8 MHz Â±10ppm Crystal 8pF 500 Ohms 4-SMD, No Lead</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>D1, D3</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t>0605201000250</t>
-  </si>
-  <si>
-    <t>Ceramic Fuse, Size 0520, 250 VAC, 10A</t>
-  </si>
-  <si>
-    <t>J2, J3, J5</t>
-  </si>
-  <si>
-    <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 8p</t>
-  </si>
-  <si>
-    <t>J4, J7</t>
-  </si>
-  <si>
-    <t>J6</t>
-  </si>
-  <si>
-    <t>P1, P2, P3</t>
-  </si>
-  <si>
-    <t>WR-PHD Pin Header, THT, pitch 2.54mm, Single Row, Vertical, 3p</t>
-  </si>
-  <si>
-    <t>P5, P6, P7, P8, P9, P10, P11, P12, P13, P14, P15, P16, P17, P18, P19, P20</t>
-  </si>
-  <si>
     <t>R1, R2, R3</t>
   </si>
   <si>
     <t>R4</t>
   </si>
   <si>
+    <t>Total PCB Price in 1 Set</t>
+  </si>
+  <si>
+    <t>PCB Name</t>
+  </si>
+  <si>
     <t>PCB Price</t>
   </si>
   <si>
-    <t>Project related</t>
-  </si>
-  <si>
-    <t>Note</t>
+    <t>Quantity 1 Set</t>
+  </si>
+  <si>
+    <t>PCB Price Total</t>
   </si>
   <si>
     <t>MainBoard</t>
   </si>
   <si>
-    <t>Shopee , 6 - 8 days shipping</t>
-  </si>
-  <si>
-    <t>HBridge-MCU</t>
-  </si>
-  <si>
-    <t>HBridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CXT , 12 - 14 days shipping , PCB Pannel </t>
-  </si>
-  <si>
-    <t>HBridge-Driver</t>
+    <t>HBridgeDriver</t>
+  </si>
+  <si>
+    <t>HBridgeMCU</t>
   </si>
   <si>
     <t>MainSensor</t>
   </si>
   <si>
-    <t>Sensor</t>
-  </si>
-  <si>
-    <t>CXT , 12 - 14 days shipping</t>
-  </si>
-  <si>
     <t>ServoShield</t>
-  </si>
-  <si>
-    <t>MainBoard Sheild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total: </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="[$VND]\ #,##0.00;[$VND]\ \-#,##0.00"/>
+    <numFmt numFmtId="179" formatCode="_ [$VND]\ * #,##0.00_ ;_ [$VND]\ * \-#,##0.00_ ;_ [$VND]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1316,6 +1468,54 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF467886"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF467886"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1769,149 +1969,191 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -2462,30 +2704,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="24" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
@@ -2497,19 +2739,19 @@
       <c r="D2">
         <v>9</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>190</v>
       </c>
-      <c r="F2" s="1">
-        <f t="shared" ref="F2:F11" si="0">E2*D2</f>
+      <c r="F2" s="2">
+        <f t="shared" ref="F2:F12" si="0">E2*D2</f>
         <v>1710</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="24" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
@@ -2521,19 +2763,19 @@
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>400</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="24" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
@@ -2545,19 +2787,19 @@
       <c r="D4">
         <v>2</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>1500</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="24" t="s">
         <v>19</v>
       </c>
       <c r="B5" t="s">
@@ -2569,19 +2811,19 @@
       <c r="D5">
         <v>3</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>190</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <f t="shared" si="0"/>
         <v>570</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="24" t="s">
         <v>23</v>
       </c>
       <c r="B6" t="s">
@@ -2593,19 +2835,19 @@
       <c r="D6">
         <v>2</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>350</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="24" t="s">
         <v>27</v>
       </c>
       <c r="B7" t="s">
@@ -2617,19 +2859,19 @@
       <c r="D7">
         <v>6</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>190</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <f t="shared" si="0"/>
         <v>1140</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="24" t="s">
         <v>31</v>
       </c>
       <c r="B8" t="s">
@@ -2641,19 +2883,19 @@
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>190</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <f t="shared" si="0"/>
         <v>190</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="24" t="s">
         <v>35</v>
       </c>
       <c r="B9" t="s">
@@ -2665,19 +2907,19 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>500</v>
       </c>
-      <c r="F9" s="1">
-        <f>E9*D9</f>
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="24" t="s">
         <v>39</v>
       </c>
       <c r="B10" t="s">
@@ -2689,19 +2931,19 @@
       <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10" s="1">
-        <v>192</v>
-      </c>
-      <c r="F10" s="1">
-        <f t="shared" si="0"/>
-        <v>768</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="E10" s="2">
+        <v>190</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="24" t="s">
         <v>42</v>
       </c>
       <c r="B11" t="s">
@@ -2713,19 +2955,19 @@
       <c r="D11">
         <v>1</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>800</v>
       </c>
-      <c r="F11" s="1">
-        <f>E11*D11</f>
+      <c r="F11" s="2">
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="24" t="s">
         <v>46</v>
       </c>
       <c r="B12" t="s">
@@ -2737,19 +2979,19 @@
       <c r="D12">
         <v>1</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>800</v>
       </c>
-      <c r="F12" s="1">
-        <f>E12*D12</f>
+      <c r="F12" s="2">
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B13" t="s">
@@ -2761,19 +3003,19 @@
       <c r="D13">
         <v>6</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>600</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="2">
         <f>E13*D9</f>
         <v>600</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="24" t="s">
         <v>54</v>
       </c>
       <c r="B14" t="s">
@@ -2785,14 +3027,14 @@
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>400</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="2">
         <f>E14*D11</f>
         <v>400</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="6" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2809,14 +3051,14 @@
       <c r="D15">
         <v>4</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
         <v>180</v>
       </c>
-      <c r="F15" s="1">
-        <f t="shared" ref="F15:F47" si="1">E15*D15</f>
+      <c r="F15" s="2">
+        <f t="shared" ref="F15:F52" si="1">E15*D15</f>
         <v>720</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="6" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2833,14 +3075,14 @@
       <c r="D16">
         <v>2</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="2">
         <v>500</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="2">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="6" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2857,14 +3099,14 @@
       <c r="D17">
         <v>2</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="2">
         <v>200</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="2">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="6" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2881,14 +3123,14 @@
       <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="2">
         <v>600</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="2">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="6" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2905,14 +3147,14 @@
       <c r="D19">
         <v>2</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="2">
         <v>350</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="2">
         <f t="shared" si="1"/>
         <v>700</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="6" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2929,14 +3171,14 @@
       <c r="D20">
         <v>1</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="2">
         <v>170</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="2">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="6" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2953,14 +3195,14 @@
       <c r="D21">
         <v>1</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="2">
         <v>210</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="2">
         <f t="shared" si="1"/>
         <v>210</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="6" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2977,19 +3219,19 @@
       <c r="D22">
         <v>1</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="2">
         <v>180</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="2">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="6" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="24" t="s">
         <v>89</v>
       </c>
       <c r="B23" t="s">
@@ -3001,19 +3243,19 @@
       <c r="D23">
         <v>1</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="2">
         <v>1500</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="2">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="24" t="s">
         <v>93</v>
       </c>
       <c r="B24" t="s">
@@ -3025,19 +3267,19 @@
       <c r="D24">
         <v>1</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="2">
         <v>1700</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="2">
         <f t="shared" si="1"/>
         <v>1700</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="6" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="24" t="s">
         <v>97</v>
       </c>
       <c r="B25" t="s">
@@ -3049,19 +3291,19 @@
       <c r="D25">
         <v>1</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="2">
         <v>1500</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="2">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="6" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="24" t="s">
         <v>101</v>
       </c>
       <c r="B26" t="s">
@@ -3073,14 +3315,14 @@
       <c r="D26">
         <v>1</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="2">
         <v>3000</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="2">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="6" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3097,14 +3339,14 @@
       <c r="D27">
         <v>1</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="2">
         <v>600</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="2">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="6" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3121,14 +3363,14 @@
       <c r="D28">
         <v>1</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="2">
         <v>1500</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="2">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="6" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3145,14 +3387,14 @@
       <c r="D29">
         <v>1</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="2">
         <v>3000</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="2">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="6" t="s">
         <v>116</v>
       </c>
     </row>
@@ -3169,14 +3411,14 @@
       <c r="D30">
         <v>3</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="2">
         <v>4200</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="2">
         <f t="shared" si="1"/>
         <v>12600</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="6" t="s">
         <v>119</v>
       </c>
     </row>
@@ -3193,14 +3435,14 @@
       <c r="D31">
         <v>1</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="2">
         <v>3500</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="2">
         <f t="shared" si="1"/>
         <v>3500</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="6" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3217,14 +3459,14 @@
       <c r="D32">
         <v>1</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="2">
         <v>3700</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="2">
         <f t="shared" si="1"/>
         <v>3700</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="6" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3241,14 +3483,14 @@
       <c r="D33">
         <v>1</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="2">
         <v>800</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="2">
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="6" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3265,14 +3507,14 @@
       <c r="D34">
         <v>2</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="2">
         <v>1200</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="2">
         <f t="shared" si="1"/>
         <v>2400</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="6" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3289,14 +3531,14 @@
       <c r="D35">
         <v>1</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="2">
         <v>4500</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="2">
         <f t="shared" si="1"/>
         <v>4500</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="7" t="s">
         <v>135</v>
       </c>
     </row>
@@ -3313,14 +3555,14 @@
       <c r="D36">
         <v>1</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="2">
         <v>1300</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="2">
         <f t="shared" si="1"/>
         <v>1300</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="6" t="s">
         <v>138</v>
       </c>
     </row>
@@ -3337,14 +3579,14 @@
       <c r="D37">
         <v>1</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="2">
         <v>4500</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="2">
         <f t="shared" si="1"/>
         <v>4500</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="7" t="s">
         <v>135</v>
       </c>
     </row>
@@ -3361,19 +3603,19 @@
       <c r="D38">
         <v>3</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="2">
         <v>1200</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="2">
         <f t="shared" si="1"/>
         <v>3600</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="24" t="s">
         <v>143</v>
       </c>
       <c r="B39" t="s">
@@ -3385,19 +3627,19 @@
       <c r="D39">
         <v>3</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="2">
         <v>900</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="2">
         <f t="shared" si="1"/>
         <v>2700</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="24" t="s">
         <v>147</v>
       </c>
       <c r="B40" t="s">
@@ -3409,19 +3651,19 @@
       <c r="D40">
         <v>3</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="2">
         <v>1200</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="2">
         <f t="shared" si="1"/>
         <v>3600</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="24" t="s">
         <v>151</v>
       </c>
       <c r="B41" t="s">
@@ -3433,14 +3675,14 @@
       <c r="D41">
         <v>5</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="2">
         <v>680</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="2">
         <f t="shared" si="1"/>
         <v>3400</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="6" t="s">
         <v>154</v>
       </c>
     </row>
@@ -3457,14 +3699,14 @@
       <c r="D42">
         <v>1</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="2">
         <v>4500</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="2">
         <f t="shared" si="1"/>
         <v>4500</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="6" t="s">
         <v>135</v>
       </c>
     </row>
@@ -3481,14 +3723,14 @@
       <c r="D43">
         <v>2</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="2">
         <v>1500</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="2">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="6" t="s">
         <v>159</v>
       </c>
     </row>
@@ -3505,19 +3747,19 @@
       <c r="D44">
         <v>3</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="2">
         <v>2000</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="2">
         <f t="shared" si="1"/>
         <v>6000</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="24" t="s">
         <v>164</v>
       </c>
       <c r="B45" t="s">
@@ -3529,19 +3771,19 @@
       <c r="D45">
         <v>18</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="2">
         <v>38</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="2">
         <f t="shared" si="1"/>
         <v>684</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="6" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="24" t="s">
         <v>168</v>
       </c>
       <c r="B46" t="s">
@@ -3553,19 +3795,19 @@
       <c r="D46">
         <v>5</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="2">
         <v>38</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="2">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="6" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="24" t="s">
         <v>172</v>
       </c>
       <c r="B47" t="s">
@@ -3577,19 +3819,19 @@
       <c r="D47">
         <v>7</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="2">
         <v>38</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="2">
         <f t="shared" si="1"/>
         <v>266</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="24" t="s">
         <v>176</v>
       </c>
       <c r="B48" t="s">
@@ -3601,19 +3843,19 @@
       <c r="D48">
         <v>3</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="2">
         <v>50</v>
       </c>
-      <c r="F48" s="1">
-        <f>E48*D48</f>
+      <c r="F48" s="2">
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="24" t="s">
         <v>180</v>
       </c>
       <c r="B49" t="s">
@@ -3625,19 +3867,19 @@
       <c r="D49">
         <v>1</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="2">
         <v>32</v>
       </c>
-      <c r="F49" s="1">
-        <f>E49*D49</f>
+      <c r="F49" s="2">
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="24" t="s">
         <v>184</v>
       </c>
       <c r="B50" t="s">
@@ -3649,19 +3891,19 @@
       <c r="D50">
         <v>1</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="2">
         <v>38</v>
       </c>
-      <c r="F50" s="1">
-        <f>E50*D50</f>
+      <c r="F50" s="2">
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" s="6" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="24" t="s">
         <v>188</v>
       </c>
       <c r="B51" t="s">
@@ -3673,19 +3915,19 @@
       <c r="D51">
         <v>1</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="2">
         <v>32</v>
       </c>
-      <c r="F51" s="1">
-        <f>E51*D51</f>
+      <c r="F51" s="2">
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G51" s="6" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="24" t="s">
         <v>192</v>
       </c>
       <c r="B52" t="s">
@@ -3697,19 +3939,19 @@
       <c r="D52">
         <v>2</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52" s="2">
         <v>32</v>
       </c>
-      <c r="F52" s="1">
-        <f>E52*D52</f>
+      <c r="F52" s="2">
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="6" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="24" t="s">
         <v>196</v>
       </c>
       <c r="B53" t="s">
@@ -3721,14 +3963,14 @@
       <c r="D53">
         <v>3</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="2">
         <v>32</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="2">
         <f t="shared" ref="F53:F62" si="2">E53*D53</f>
         <v>96</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="6" t="s">
         <v>199</v>
       </c>
     </row>
@@ -3745,19 +3987,19 @@
       <c r="D54">
         <v>4</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54" s="2">
         <v>380</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="2">
         <f t="shared" si="2"/>
         <v>1520</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" s="6" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="24" t="s">
         <v>204</v>
       </c>
       <c r="B55" t="s">
@@ -3769,14 +4011,14 @@
       <c r="D55">
         <v>3</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="2">
         <v>500</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="2">
         <f t="shared" si="2"/>
         <v>1500</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="6" t="s">
         <v>207</v>
       </c>
     </row>
@@ -3793,14 +4035,14 @@
       <c r="D56">
         <v>1</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="2">
         <v>85000</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="2">
         <f t="shared" si="2"/>
         <v>85000</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G56" s="6" t="s">
         <v>211</v>
       </c>
     </row>
@@ -3817,14 +4059,14 @@
       <c r="D57">
         <v>1</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="2">
         <v>13000</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="2">
         <f t="shared" si="2"/>
         <v>13000</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="6" t="s">
         <v>215</v>
       </c>
     </row>
@@ -3841,14 +4083,14 @@
       <c r="D58">
         <v>1</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58" s="2">
         <v>3500</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="2">
         <f t="shared" si="2"/>
         <v>3500</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G58" s="6" t="s">
         <v>219</v>
       </c>
     </row>
@@ -3865,14 +4107,14 @@
       <c r="D59">
         <v>1</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="2">
         <v>33000</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="2">
         <f t="shared" si="2"/>
         <v>33000</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" s="7" t="s">
         <v>223</v>
       </c>
     </row>
@@ -3889,14 +4131,14 @@
       <c r="D60">
         <v>2</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="2">
         <v>4000</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="2">
         <f t="shared" si="2"/>
         <v>8000</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="6" t="s">
         <v>227</v>
       </c>
     </row>
@@ -3910,14 +4152,14 @@
       <c r="D61">
         <v>1</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61" s="2">
         <v>4000</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="2">
         <f>E61*D62</f>
         <v>4000</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="6" t="s">
         <v>230</v>
       </c>
     </row>
@@ -3934,14 +4176,14 @@
       <c r="D62">
         <v>1</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E62" s="2">
         <v>4000</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="2">
         <f>E62*D62</f>
         <v>4000</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="7" t="s">
         <v>234</v>
       </c>
     </row>
@@ -3955,24 +4197,24 @@
       <c r="D63">
         <v>5</v>
       </c>
-      <c r="E63" s="1">
-        <v>26400</v>
-      </c>
-      <c r="F63" s="1">
+      <c r="E63" s="2">
+        <v>20000</v>
+      </c>
+      <c r="F63" s="2">
         <f>E63*D63</f>
-        <v>132000</v>
-      </c>
-      <c r="G63" s="2" t="s">
+        <v>100000</v>
+      </c>
+      <c r="G63" s="6" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="64" spans="5:6">
-      <c r="E64" t="s">
+      <c r="E64" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="F64" s="1">
-        <f>SUM(F2:F63)</f>
-        <v>375530</v>
+      <c r="F64" s="5">
+        <f>SUM(F2:F63)-4*E63</f>
+        <v>263522</v>
       </c>
     </row>
   </sheetData>
@@ -4041,6 +4283,7 @@
     <hyperlink ref="G63" r:id="rId57" display="https://shopee.vn/S%E1%BA%A3n-xu%E1%BA%A5t-PCB-ch%E1%BA%A5t-l%C6%B0%E1%BB%A3ng-cao-%E2%80%93-MOQ-5-T%C3%B9y-ch%E1%BB%89nh-m%C3%A0u-mi%E1%BB%85n-ph%C3%AD-B%E1%BA%A3ng-%C4%91%C6%A1n-%C4%91%C3%B4i-v%C3%A0-nhi%E1%BB%81u-l%E1%BB%9Bp-i.1135296432.28315488514"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -4048,275 +4291,419 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="17.6666666666667" customWidth="1"/>
     <col min="2" max="2" width="74.4444444444444" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="5" max="5" width="14.2222222222222"/>
+    <col min="5" max="5" width="15.2222222222222"/>
     <col min="6" max="6" width="15.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>10603226106.3</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="20">
         <v>2</v>
       </c>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="E2" s="21">
+        <v>550</v>
+      </c>
+      <c r="F2" s="22">
+        <v>5500</v>
+      </c>
+      <c r="G2" s="23" t="s">
         <v>243</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="20"/>
+      <c r="C3" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D3" s="20">
+        <v>1</v>
+      </c>
+      <c r="E3" s="21">
+        <v>190</v>
+      </c>
+      <c r="F3" s="22">
+        <v>1900</v>
+      </c>
+      <c r="G3" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="D4">
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="D4" s="20">
         <v>2</v>
       </c>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C5" t="s">
-        <v>249</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="E4" s="21">
+        <v>350</v>
+      </c>
+      <c r="F4" s="22">
+        <v>3500</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="20">
+        <v>1</v>
+      </c>
+      <c r="E5" s="21">
+        <v>190</v>
+      </c>
+      <c r="F5" s="22">
+        <v>190</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C6" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="D6" s="20">
+        <v>1</v>
+      </c>
+      <c r="E6" s="21">
+        <v>170</v>
+      </c>
+      <c r="F6" s="22">
+        <v>170</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>251</v>
-      </c>
-      <c r="B8" t="s">
-        <v>252</v>
-      </c>
-      <c r="C8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D8">
+      <c r="D7" s="20">
+        <v>1</v>
+      </c>
+      <c r="E7" s="21">
+        <v>1500</v>
+      </c>
+      <c r="F7" s="22">
+        <v>1500</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="20">
         <v>2</v>
       </c>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>254</v>
-      </c>
-      <c r="C9" t="s">
-        <v>255</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>256</v>
-      </c>
-      <c r="B10" t="s">
-        <v>257</v>
-      </c>
-      <c r="C10" t="s">
-        <v>258</v>
-      </c>
-      <c r="D10">
+      <c r="E8" s="21">
+        <v>1500</v>
+      </c>
+      <c r="F8" s="22">
+        <v>3000</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="D9" s="20">
+        <v>1</v>
+      </c>
+      <c r="E9" s="21">
+        <v>4000</v>
+      </c>
+      <c r="F9" s="22">
+        <v>4000</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" s="20">
         <v>4</v>
       </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="E10" s="21">
+        <v>3000</v>
+      </c>
+      <c r="F10" s="22">
+        <v>12000</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="C11" t="s">
-        <v>259</v>
-      </c>
-      <c r="D11">
+      <c r="B11" s="20"/>
+      <c r="C11" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="D11" s="20">
         <v>6</v>
       </c>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="E11" s="21">
+        <v>38</v>
+      </c>
+      <c r="F11" s="22">
+        <v>1900</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="C12" t="s">
-        <v>260</v>
-      </c>
-      <c r="D12">
+      <c r="B12" s="20"/>
+      <c r="C12" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="D12" s="20">
         <v>3</v>
       </c>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="E12" s="21">
+        <v>32</v>
+      </c>
+      <c r="F12" s="22">
+        <v>1600</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="C13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D13">
+      <c r="B13" s="20"/>
+      <c r="C13" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="D13" s="20">
         <v>4</v>
       </c>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="E13" s="21">
+        <v>3</v>
+      </c>
+      <c r="F13" s="22">
+        <v>1600</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>200</v>
       </c>
       <c r="C14" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>263</v>
-      </c>
-      <c r="B15" t="s">
-        <v>264</v>
-      </c>
-      <c r="C15" t="s">
-        <v>265</v>
-      </c>
-      <c r="D15">
+      <c r="E14" s="3">
+        <v>380</v>
+      </c>
+      <c r="F14" s="3">
+        <f>E14*D14</f>
+        <v>380</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="D15" s="20">
         <v>2</v>
       </c>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>266</v>
-      </c>
-      <c r="B16" t="s">
-        <v>267</v>
-      </c>
-      <c r="C16" t="s">
-        <v>268</v>
-      </c>
-      <c r="D16">
+      <c r="E15" s="21">
+        <v>2800</v>
+      </c>
+      <c r="F15" s="22">
+        <v>5600</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="D16" s="20">
         <v>2</v>
       </c>
-      <c r="E16" s="1"/>
+      <c r="E16" s="21">
+        <v>15000</v>
+      </c>
+      <c r="F16" s="22">
+        <v>30000</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>235</v>
       </c>
       <c r="B17" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="D17">
         <v>5</v>
       </c>
-      <c r="E17" s="1">
-        <v>62000</v>
-      </c>
-      <c r="F17" s="1">
+      <c r="E17" s="2">
+        <v>20</v>
+      </c>
+      <c r="F17" s="2">
         <f>E17*D17</f>
-        <v>310000</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="5:6">
+      <c r="E18" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F18" s="18">
+        <f>SUM(F2:F17)-4*E17</f>
+        <v>72860</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="https://www.thegioiic.com/tu-gom-0603-22uf-10v" tooltip="https://www.thegioiic.com/tu-gom-0603-22uf-10v"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://www.thegioiic.com/tu-gom-0805-10nf-50v" tooltip="https://www.thegioiic.com/tu-gom-0805-10nf-50v"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://www.thegioiic.com/1n5819w-diode-schottky-1a-40v-sod-123" tooltip="https://www.thegioiic.com/1n5819w-diode-schottky-1a-40v-sod-123"/>
+    <hyperlink ref="G5" r:id="rId4" display="https://www.thegioiic.com/led-xanh-la-0603-dan-smd-trong-suot" tooltip="https://www.thegioiic.com/led-xanh-la-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G6" r:id="rId5" display="https://www.thegioiic.com/led-xanh-duong-0603-dan-smd-trong-suot" tooltip="https://www.thegioiic.com/led-xanh-duong-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G7" r:id="rId6" display="https://www.thegioiic.com/kf301-2-v-domino-2-chan-thang-5-08mm-300v-10a-han-pcb" tooltip="https://www.thegioiic.com/kf301-2-v-domino-2-chan-thang-5-08mm-300v-10a-han-pcb"/>
+    <hyperlink ref="G8" r:id="rId7" display="https://www.thegioiic.com/kf120-2-v-domino-2-chan-thang-2-54mm-150v-6a-han-pcb" tooltip="https://www.thegioiic.com/kf120-2-v-domino-2-chan-thang-2-54mm-150v-6a-han-pcb"/>
+    <hyperlink ref="G9" r:id="rId8" display="https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-cao-21mm-xuyen-lo" tooltip="https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-cao-21mm-xuyen-lo"/>
+    <hyperlink ref="G10" r:id="rId9" display="https://www.thegioiic.com/irlr7843-mosfet-kenh-n-30v-161a-to-252-3" tooltip="https://www.thegioiic.com/irlr7843-mosfet-kenh-n-30v-161a-to-252-3"/>
+    <hyperlink ref="G11" r:id="rId10" display="https://www.thegioiic.com/dien-tro-100-ohm-0603-1-" tooltip="https://www.thegioiic.com/dien-tro-100-ohm-0603-1-"/>
+    <hyperlink ref="G12" r:id="rId11" display="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-" tooltip="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-"/>
+    <hyperlink ref="G13" r:id="rId12" display="https://www.thegioiic.com/dien-tro-10-kohm-0603-5-" tooltip="https://www.thegioiic.com/dien-tro-10-kohm-0603-5-"/>
+    <hyperlink ref="G15" r:id="rId13" display="https://www.thegioiic.com/pc817x2nipw-optoisolator-transistor-output-5000vrms-1-channel-sop-4" tooltip="https://www.thegioiic.com/pc817x2nipw-optoisolator-transistor-output-5000vrms-1-channel-sop-4"/>
+    <hyperlink ref="G16" r:id="rId14" display="https://www.thegioiic.com/ir2104spbf-mosfet-2-ngo-ra-360-ma-20v-8-soic" tooltip="https://www.thegioiic.com/ir2104spbf-mosfet-2-ngo-ra-360-ma-20v-8-soic"/>
+    <hyperlink ref="G14" r:id="rId15" display="https://www.thegioiic.com/vit-nhua-m3-dai-5mm"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -4324,554 +4711,941 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="21.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="96.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="72.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="109.555555555556" customWidth="1"/>
     <col min="3" max="3" width="139.111111111111" customWidth="1"/>
-    <col min="5" max="5" width="14.2222222222222" customWidth="1"/>
-    <col min="6" max="6" width="15.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="17.7777777777778" customWidth="1"/>
+    <col min="6" max="6" width="18.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>239</v>
-      </c>
-      <c r="G1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D2">
+      <c r="B2" s="10"/>
+      <c r="C2" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D2" s="10">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E2" s="11">
+        <v>190</v>
+      </c>
+      <c r="F2" s="11">
+        <f>D2*E2</f>
+        <v>1330</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C3" t="s">
-        <v>271</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D3" s="10">
+        <v>1</v>
+      </c>
+      <c r="E3" s="11">
+        <v>700</v>
+      </c>
+      <c r="F3" s="11">
+        <f t="shared" ref="F3:F36" si="0">D3*E3</f>
+        <v>700</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D4">
+      <c r="B4" s="10"/>
+      <c r="C4" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D4" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="4" t="s">
+      <c r="E4" s="11">
+        <v>400</v>
+      </c>
+      <c r="F4" s="11">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="11">
+        <v>190</v>
+      </c>
+      <c r="F5" s="11">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="D6" s="10">
+        <v>2</v>
+      </c>
+      <c r="E6" s="11">
+        <v>250</v>
+      </c>
+      <c r="F6" s="11">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D7" s="10">
+        <v>2</v>
+      </c>
+      <c r="E7" s="11">
+        <v>800</v>
+      </c>
+      <c r="F7" s="11">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2</v>
+      </c>
+      <c r="E8" s="11">
+        <v>190</v>
+      </c>
+      <c r="F8" s="11">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="D9" s="10">
+        <v>2</v>
+      </c>
+      <c r="E9" s="11">
+        <v>230</v>
+      </c>
+      <c r="F9" s="11">
+        <f t="shared" si="0"/>
+        <v>460</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="D10" s="10">
+        <v>2</v>
+      </c>
+      <c r="E10" s="11">
+        <v>180</v>
+      </c>
+      <c r="F10" s="11">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D11" s="10">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11">
+        <v>210</v>
+      </c>
+      <c r="F11" s="11">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D12" s="10">
+        <v>2</v>
+      </c>
+      <c r="E12" s="11">
+        <v>350</v>
+      </c>
+      <c r="F12" s="11">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D13" s="10">
+        <v>4</v>
+      </c>
+      <c r="E13" s="11">
+        <v>500</v>
+      </c>
+      <c r="F13" s="11">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="D14" s="10">
+        <v>4</v>
+      </c>
+      <c r="E14" s="11">
+        <v>200</v>
+      </c>
+      <c r="F14" s="11">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1</v>
+      </c>
+      <c r="E15" s="11">
+        <v>500</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="D16" s="10">
+        <v>2</v>
+      </c>
+      <c r="E16" s="11">
+        <v>2500</v>
+      </c>
+      <c r="F16" s="11">
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="10">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11">
+        <v>1500</v>
+      </c>
+      <c r="F17" s="11">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="10">
+        <v>1</v>
+      </c>
+      <c r="E18" s="11">
+        <v>1500</v>
+      </c>
+      <c r="F18" s="11">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="10">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11">
+        <v>2500</v>
+      </c>
+      <c r="F19" s="11">
+        <f t="shared" si="0"/>
+        <v>2500</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="D20" s="10">
+        <v>4</v>
+      </c>
+      <c r="E20" s="11">
+        <v>2200</v>
+      </c>
+      <c r="F20" s="11">
+        <f t="shared" si="0"/>
+        <v>8800</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="10">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11">
+        <v>800</v>
+      </c>
+      <c r="F21" s="11">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="D22" s="10">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11">
+        <v>900</v>
+      </c>
+      <c r="F22" s="11">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="D23" s="10">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11">
+        <v>900</v>
+      </c>
+      <c r="F23" s="11">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="D24" s="10">
+        <v>1</v>
+      </c>
+      <c r="E24" s="11">
+        <v>4500</v>
+      </c>
+      <c r="F24" s="11">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="10">
+        <v>3</v>
+      </c>
+      <c r="E25" s="11">
+        <v>2000</v>
+      </c>
+      <c r="F25" s="11">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="D26" s="10">
+        <v>3</v>
+      </c>
+      <c r="E26" s="11">
+        <v>8000</v>
+      </c>
+      <c r="F26" s="11">
+        <f t="shared" si="0"/>
+        <v>24000</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="D27" s="10">
+        <v>4</v>
+      </c>
+      <c r="E27" s="11">
+        <v>32</v>
+      </c>
+      <c r="F27" s="11">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="D28" s="10">
+        <v>4</v>
+      </c>
+      <c r="E28" s="11">
+        <v>38</v>
+      </c>
+      <c r="F28" s="11">
+        <f t="shared" si="0"/>
+        <v>152</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B29" s="10"/>
+      <c r="C29" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="D29" s="10">
+        <v>9</v>
+      </c>
+      <c r="E29" s="11">
+        <v>32</v>
+      </c>
+      <c r="F29" s="11">
+        <f t="shared" si="0"/>
+        <v>288</v>
+      </c>
+      <c r="G29" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="B5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B6" t="s">
-        <v>277</v>
-      </c>
-      <c r="C6" t="s">
-        <v>278</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C7" t="s">
-        <v>281</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>282</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>246</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="B30" s="10"/>
+      <c r="C30" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="D30" s="10">
+        <v>1</v>
+      </c>
+      <c r="E30" s="11">
+        <v>38</v>
+      </c>
+      <c r="F30" s="11">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="B31" s="10"/>
+      <c r="C31" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="D31" s="10">
+        <v>6</v>
+      </c>
+      <c r="E31" s="11">
+        <v>56</v>
+      </c>
+      <c r="F31" s="11">
+        <f t="shared" si="0"/>
+        <v>336</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B32" s="10"/>
+      <c r="C32" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D32" s="10">
+        <v>4</v>
+      </c>
+      <c r="E32" s="13">
+        <v>380</v>
+      </c>
+      <c r="F32" s="14">
+        <f>E32*D32</f>
+        <v>1520</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="D33" s="10">
+        <v>5</v>
+      </c>
+      <c r="E33" s="11">
+        <v>400</v>
+      </c>
+      <c r="F33" s="11">
+        <f>D33*E33</f>
+        <v>2000</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" s="10">
+        <v>1</v>
+      </c>
+      <c r="E34" s="11">
+        <v>44000</v>
+      </c>
+      <c r="F34" s="11">
+        <f>D34*E34</f>
+        <v>44000</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="10">
+        <v>1</v>
+      </c>
+      <c r="E35" s="11">
+        <v>20000</v>
+      </c>
+      <c r="F35" s="11">
+        <f>D35*E35</f>
+        <v>20000</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D36" s="10">
+        <v>1</v>
+      </c>
+      <c r="E36" s="11">
+        <v>3500</v>
+      </c>
+      <c r="F36" s="11">
+        <f>D36*E36</f>
+        <v>3500</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D37" s="10">
+        <v>1</v>
+      </c>
+      <c r="E37" s="11">
+        <v>4000</v>
+      </c>
+      <c r="F37" s="11">
+        <f>D37*E37</f>
+        <v>4000</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B38" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>250</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>285</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>286</v>
-      </c>
-      <c r="C14" t="s">
-        <v>287</v>
-      </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>288</v>
-      </c>
-      <c r="B15" t="s">
-        <v>289</v>
-      </c>
-      <c r="C15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B16" t="s">
-        <v>291</v>
-      </c>
-      <c r="C16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>109</v>
-      </c>
-      <c r="B18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>293</v>
-      </c>
-      <c r="B19" t="s">
-        <v>294</v>
-      </c>
-      <c r="C19" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20">
-        <v>61031221821</v>
-      </c>
-      <c r="B20" t="s">
-        <v>295</v>
-      </c>
-      <c r="C20" t="s">
-        <v>296</v>
-      </c>
-      <c r="D20">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B21" t="s">
-        <v>152</v>
-      </c>
-      <c r="C21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22">
-        <v>61300411021</v>
-      </c>
-      <c r="B22" t="s">
-        <v>297</v>
-      </c>
-      <c r="C22" t="s">
-        <v>298</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B23" t="s">
-        <v>144</v>
-      </c>
-      <c r="C23" t="s">
-        <v>299</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24">
-        <v>61030621121</v>
-      </c>
-      <c r="B24" t="s">
-        <v>139</v>
-      </c>
-      <c r="C24" t="s">
-        <v>300</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>160</v>
-      </c>
-      <c r="B25" t="s">
-        <v>161</v>
-      </c>
-      <c r="C25" t="s">
-        <v>162</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>301</v>
-      </c>
-      <c r="B26" t="s">
-        <v>302</v>
-      </c>
-      <c r="C26" t="s">
-        <v>303</v>
-      </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C27" t="s">
-        <v>304</v>
-      </c>
-      <c r="D27">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28" t="s">
-        <v>305</v>
-      </c>
-      <c r="D28">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B29" t="s">
-        <v>165</v>
-      </c>
-      <c r="C29" t="s">
-        <v>306</v>
-      </c>
-      <c r="D29">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B30" t="s">
-        <v>308</v>
-      </c>
-      <c r="C30" t="s">
-        <v>309</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B31" t="s">
-        <v>177</v>
-      </c>
-      <c r="C31" t="s">
-        <v>310</v>
-      </c>
-      <c r="D31">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>200</v>
-      </c>
-      <c r="C32" t="s">
-        <v>202</v>
-      </c>
-      <c r="D32">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B33" t="s">
-        <v>312</v>
-      </c>
-      <c r="C33" t="s">
-        <v>313</v>
-      </c>
-      <c r="D33">
+      <c r="C38" s="17"/>
+      <c r="D38" s="17">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>314</v>
-      </c>
-      <c r="B34" t="s">
-        <v>315</v>
-      </c>
-      <c r="C34" t="s">
-        <v>210</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" t="s">
-        <v>316</v>
-      </c>
-      <c r="B35" t="s">
-        <v>317</v>
-      </c>
-      <c r="C35" t="s">
-        <v>214</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>216</v>
-      </c>
-      <c r="B36" t="s">
-        <v>217</v>
-      </c>
-      <c r="C36" t="s">
-        <v>218</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" t="s">
-        <v>224</v>
-      </c>
-      <c r="B37" t="s">
-        <v>225</v>
-      </c>
-      <c r="C37" t="s">
-        <v>226</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
-        <v>235</v>
-      </c>
-      <c r="B38" t="s">
-        <v>269</v>
-      </c>
-      <c r="D38">
-        <v>5</v>
-      </c>
-      <c r="E38" s="1">
-        <v>62000</v>
-      </c>
-      <c r="F38" s="1">
-        <f>E38*D38</f>
-        <v>310000</v>
+      <c r="E38" s="14">
+        <v>20000</v>
+      </c>
+      <c r="F38" s="11">
+        <f>D38*E38</f>
+        <v>100000</v>
+      </c>
+      <c r="G38" s="17"/>
+    </row>
+    <row r="39" spans="5:6">
+      <c r="E39" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F39" s="18">
+        <f>SUM(F2:F38)-4*E38</f>
+        <v>163082</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G3" r:id="rId1" display="https://www.thegioiic.com/tu-gom-0603-10uf-25v" tooltip="https://www.thegioiic.com/tu-gom-0603-10uf-25v"/>
+    <hyperlink ref="G4" r:id="rId2" display="https://www.thegioiic.com/tu-gom-0603-1uf-25v" tooltip="https://www.thegioiic.com/tu-gom-0603-1uf-25v"/>
+    <hyperlink ref="G5" r:id="rId3" display="https://www.thegioiic.com/tu-gom-0603-8pf-50v" tooltip="https://www.thegioiic.com/tu-gom-0603-8pf-50v"/>
+    <hyperlink ref="G6" r:id="rId4" display="https://www.thegioiic.com/tu-gom-0603-33pf-50v" tooltip="https://www.thegioiic.com/tu-gom-0603-33pf-50v"/>
+    <hyperlink ref="G7" r:id="rId5" display="https://www.thegioiic.com/tu-nhom-smd-22uf-16v-4x5-4mm" tooltip="https://www.thegioiic.com/tu-nhom-smd-22uf-16v-4x5-4mm"/>
+    <hyperlink ref="G8" r:id="rId6" display="https://www.thegioiic.com/tu-gom-0603-100pf-50v" tooltip="https://www.thegioiic.com/tu-gom-0603-100pf-50v"/>
+    <hyperlink ref="G9" r:id="rId7" display="https://www.thegioiic.com/led-xanh-duong-0805-dan-smd-trong-suot" tooltip="https://www.thegioiic.com/led-xanh-duong-0805-dan-smd-trong-suot"/>
+    <hyperlink ref="G10" r:id="rId8" display="https://www.thegioiic.com/led-do-0603-dan-smd-trong-suot" tooltip="https://www.thegioiic.com/led-do-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G11" r:id="rId9" display="https://www.thegioiic.com/led-trang-0603-dan-smd-trong-suot" tooltip="https://www.thegioiic.com/led-trang-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G12" r:id="rId10" display="https://www.thegioiic.com/1n5819w-diode-schottky-1a-40v-sod-123" tooltip="https://www.thegioiic.com/1n5819w-diode-schottky-1a-40v-sod-123"/>
+    <hyperlink ref="G13" r:id="rId11" display="https://www.thegioiic.com/smaj18a" tooltip="https://www.thegioiic.com/smaj18a"/>
+    <hyperlink ref="G14" r:id="rId12" display="https://www.thegioiic.com/zmm18-diode-zener-18v-500mw-smd" tooltip="https://www.thegioiic.com/zmm18-diode-zener-18v-500mw-smd"/>
+    <hyperlink ref="G15" r:id="rId13" display="https://www.thegioiic.com/cau-chi-ong-thuy-tinh-10a-5x20mm-toc-do-f" tooltip="https://www.thegioiic.com/cau-chi-ong-thuy-tinh-10a-5x20mm-toc-do-f"/>
+    <hyperlink ref="G16" r:id="rId14" display="https://www.thegioiic.com/mf-msmf110-24x-2-cau-chi-tu-phuc-hoi-1812-24v-1-1a" tooltip="https://www.thegioiic.com/mf-msmf110-24x-2-cau-chi-tu-phuc-hoi-1812-24v-1-1a"/>
+    <hyperlink ref="G17" r:id="rId15" display="https://www.thegioiic.com/mf-msmf020-2-cau-chi-tu-phuc-hoi-1812-0-20a-30v" tooltip="https://www.thegioiic.com/mf-msmf020-2-cau-chi-tu-phuc-hoi-1812-0-20a-30v"/>
+    <hyperlink ref="G18" r:id="rId16" display="https://www.thegioiic.com/kf301-2-v-domino-2-chan-thang-5-08mm-300v-10a-han-pcb" tooltip="https://www.thegioiic.com/kf301-2-v-domino-2-chan-thang-5-08mm-300v-10a-han-pcb"/>
+    <hyperlink ref="G19" r:id="rId17" display="https://www.thegioiic.com/kf301-3-v-domino-3-chan-thang-5-08mm-300v-10a-han-pcb" tooltip="https://www.thegioiic.com/kf301-3-v-domino-3-chan-thang-5-08mm-300v-10a-han-pcb"/>
+    <hyperlink ref="G20" r:id="rId18" display="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-12-chan-2-hang-smd" tooltip="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-12-chan-2-hang-smd"/>
+    <hyperlink ref="G21" r:id="rId19" display="https://www.thegioiic.com/dau-sh1-0mm-3-chan-dan-smd-thang-dung" tooltip="https://www.thegioiic.com/dau-sh1-0mm-3-chan-dan-smd-thang-dung"/>
+    <hyperlink ref="G22" r:id="rId20" display="https://www.thegioiic.com/hang-rao-duc-don-2-54mm-40-chan-cong-1-hang-cao-6mm-xuyen-lo" tooltip="https://www.thegioiic.com/hang-rao-duc-don-2-54mm-40-chan-cong-1-hang-cao-6mm-xuyen-lo"/>
+    <hyperlink ref="G23" r:id="rId21" display="https://www.thegioiic.com/dau-sh1-0mm-4-chan-dan-smd-thang-dung" tooltip="https://www.thegioiic.com/dau-sh1-0mm-4-chan-dan-smd-thang-dung"/>
+    <hyperlink ref="G24" r:id="rId22" display="https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-smd" tooltip="https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-smd"/>
+    <hyperlink ref="G25" r:id="rId23" display="https://www.thegioiic.com/ao3407a-mosfet-kenh-p-30v-4-3a-sot-23-3" tooltip="https://www.thegioiic.com/ao3407a-mosfet-kenh-p-30v-4-3a-sot-23-3"/>
+    <hyperlink ref="G26" r:id="rId24" display="https://www.thegioiic.com/aod4185-mosfet-kenh-p-40v-40a-to-252-2-dpak" tooltip="https://www.thegioiic.com/aod4185-mosfet-kenh-p-40v-40a-to-252-2-dpak"/>
+    <hyperlink ref="G27" r:id="rId25" display="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-" tooltip="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-"/>
+    <hyperlink ref="G28" r:id="rId26" display="https://www.thegioiic.com/dien-tro-0-ohm-0603-1-" tooltip="https://www.thegioiic.com/dien-tro-0-ohm-0603-1-"/>
+    <hyperlink ref="G29" r:id="rId27" display="https://www.thegioiic.com/dien-tro-10-kohm-0603-5-" tooltip="https://www.thegioiic.com/dien-tro-10-kohm-0603-5-"/>
+    <hyperlink ref="G30" r:id="rId28" display="https://www.thegioiic.com/dien-tro-120-ohm-0603-1-" tooltip="https://www.thegioiic.com/dien-tro-120-ohm-0603-1-"/>
+    <hyperlink ref="G31" r:id="rId29" display="https://www.thegioiic.com/dien-tro-10-kohm-0805-1-" tooltip="https://www.thegioiic.com/dien-tro-10-kohm-0805-1-"/>
+    <hyperlink ref="G33" r:id="rId30" display="https://www.thegioiic.com/nut-nhan-3x6mm-cao-2-5mm-2-chan-smd-dau-do" tooltip="https://www.thegioiic.com/nut-nhan-3x6mm-cao-2-5mm-2-chan-smd-dau-do"/>
+    <hyperlink ref="G34" r:id="rId31" display="https://www.thegioiic.com/stm32f103rct6-64-lqfp-32-bit-arm-cortex-m3-microcontroller-72mhz-256kb-flash" tooltip="https://www.thegioiic.com/stm32f103rct6-64-lqfp-32-bit-arm-cortex-m3-microcontroller-72mhz-256kb-flash"/>
+    <hyperlink ref="G35" r:id="rId32" display="https://www.thegioiic.com/tja1050t-ic-can-transceiver-8-soic" tooltip="https://www.thegioiic.com/tja1050t-ic-can-transceiver-8-soic"/>
+    <hyperlink ref="G36" r:id="rId33" display="https://www.thegioiic.com/ams1117-3-3v-ic-on-ap-3-3v-1a-sot-223" tooltip="https://www.thegioiic.com/ams1117-3-3v-ic-on-ap-3-3v-1a-sot-223"/>
+    <hyperlink ref="G37" r:id="rId34" display="https://www.thegioiic.com/thach-anh-8mhz-3225-4-chan-smd" tooltip="https://www.thegioiic.com/thach-anh-8mhz-3225-4-chan-smd"/>
+    <hyperlink ref="G2" r:id="rId35" display="https://www.thegioiic.com/tu-gom-0603-100nf-0-1uf-50v" tooltip="https://www.thegioiic.com/tu-gom-0603-100nf-0-1uf-50v"/>
+    <hyperlink ref="G32" r:id="rId36" display="https://www.thegioiic.com/vit-nhua-m3-dai-5mm"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -4879,242 +5653,382 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="27.6666666666667" customWidth="1"/>
     <col min="2" max="2" width="99.7777777777778" customWidth="1"/>
     <col min="3" max="3" width="255.777777777778" customWidth="1"/>
     <col min="5" max="5" width="15.4444444444444"/>
     <col min="6" max="6" width="17.1111111111111" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="7" max="7" width="87.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="B2" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="C2" t="s">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="D2">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="3">
+        <v>190</v>
+      </c>
+      <c r="F2" s="3">
+        <f>D2*E2</f>
+        <v>6840</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="B3" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="C3" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
       <c r="D3">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="3">
+        <v>250</v>
+      </c>
+      <c r="F3" s="3">
+        <f t="shared" ref="F3:F39" si="0">D3*E3</f>
+        <v>2250</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>324</v>
+        <v>361</v>
       </c>
       <c r="B4" t="s">
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="D4">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="3">
+        <v>190</v>
+      </c>
+      <c r="F4" s="3">
+        <f t="shared" si="0"/>
+        <v>2280</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>326</v>
+        <v>363</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="3">
+        <v>700</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>324</v>
+        <v>361</v>
       </c>
       <c r="B6" t="s">
-        <v>328</v>
+        <v>365</v>
       </c>
       <c r="C6" t="s">
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="3">
+        <v>190</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>331</v>
+        <v>368</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="3">
+        <v>190</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="B8" t="s">
         <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>333</v>
+        <v>370</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="3">
+        <v>350</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="B9" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="C9" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="3">
+        <v>190</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="3">
+        <v>350</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="B11" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="C11" t="s">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="3">
+        <v>250</v>
+      </c>
+      <c r="F11" s="3">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="B12" t="s">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="C12" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="D12">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="B13" t="s">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="C13" t="s">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="D13">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F13" s="3">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>344</v>
+        <v>383</v>
       </c>
       <c r="B14" t="s">
         <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="3">
+        <v>180</v>
+      </c>
+      <c r="F14" s="3">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>345</v>
+        <v>384</v>
       </c>
       <c r="B15" t="s">
-        <v>346</v>
+        <v>385</v>
       </c>
       <c r="C15" t="s">
-        <v>347</v>
+        <v>386</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="3">
+        <v>210</v>
+      </c>
+      <c r="F15" s="3">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>348</v>
+        <v>387</v>
       </c>
       <c r="B16" t="s">
-        <v>349</v>
+        <v>388</v>
       </c>
       <c r="C16" t="s">
         <v>107</v>
@@ -5122,10 +6036,23 @@
       <c r="D16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="3">
+        <v>600</v>
+      </c>
+      <c r="F16" s="3">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>350</v>
+        <v>389</v>
+      </c>
+      <c r="B17" t="s">
+        <v>390</v>
       </c>
       <c r="C17" t="s">
         <v>115</v>
@@ -5133,13 +6060,23 @@
       <c r="D17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="3">
+        <v>170</v>
+      </c>
+      <c r="F17" s="3">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>61300621121</v>
       </c>
       <c r="B18" t="s">
-        <v>351</v>
+        <v>392</v>
       </c>
       <c r="C18" t="s">
         <v>140</v>
@@ -5147,220 +6084,386 @@
       <c r="D18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="3">
+        <v>700</v>
+      </c>
+      <c r="F18" s="3">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>61300411121</v>
       </c>
       <c r="B19" t="s">
-        <v>352</v>
+        <v>394</v>
       </c>
       <c r="C19" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="4" t="s">
+      <c r="E19" s="3">
+        <v>700</v>
+      </c>
+      <c r="F19" s="3">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="K19" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="24" t="s">
         <v>151</v>
       </c>
       <c r="B20" t="s">
         <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="4" t="s">
+      <c r="E20" s="3">
+        <v>800</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="24" t="s">
         <v>143</v>
       </c>
       <c r="B21" t="s">
         <v>144</v>
       </c>
       <c r="C21" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="3">
+        <v>900</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="B22" t="s">
-        <v>354</v>
+        <v>397</v>
       </c>
       <c r="C22" t="s">
-        <v>355</v>
+        <v>398</v>
       </c>
       <c r="D22">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F22" s="3">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="B23" t="s">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="C23" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="D23">
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" s="3">
+        <v>400</v>
+      </c>
+      <c r="F23" s="3">
+        <f t="shared" si="0"/>
+        <v>3600</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="B24" t="s">
-        <v>354</v>
+        <v>397</v>
       </c>
       <c r="C24" t="s">
-        <v>359</v>
+        <v>403</v>
       </c>
       <c r="D24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F24" s="3">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>360</v>
+        <v>404</v>
       </c>
       <c r="B25" t="s">
-        <v>361</v>
+        <v>405</v>
       </c>
       <c r="C25" t="s">
-        <v>362</v>
+        <v>406</v>
       </c>
       <c r="D25">
         <v>9</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" s="3">
+        <v>32</v>
+      </c>
+      <c r="F25" s="3">
+        <f t="shared" si="0"/>
+        <v>288</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="B26" t="s">
-        <v>364</v>
+        <v>197</v>
       </c>
       <c r="C26" t="s">
-        <v>365</v>
+        <v>409</v>
       </c>
       <c r="D26">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26" s="3">
+        <v>32</v>
+      </c>
+      <c r="F26" s="3">
+        <f t="shared" si="0"/>
+        <v>736</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>366</v>
+        <v>410</v>
       </c>
       <c r="B27" t="s">
         <v>181</v>
       </c>
       <c r="C27" t="s">
-        <v>367</v>
+        <v>411</v>
       </c>
       <c r="D27">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27" s="3">
+        <v>32</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="B28" t="s">
         <v>197</v>
       </c>
       <c r="C28" t="s">
-        <v>369</v>
+        <v>412</v>
       </c>
       <c r="D28">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28" s="3">
+        <v>32</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>370</v>
+        <v>413</v>
       </c>
       <c r="B29" t="s">
         <v>165</v>
       </c>
       <c r="C29" t="s">
-        <v>371</v>
+        <v>414</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29" s="3">
+        <v>32</v>
+      </c>
+      <c r="F29" s="3">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>372</v>
+        <v>415</v>
       </c>
       <c r="B30" t="s">
-        <v>373</v>
+        <v>416</v>
       </c>
       <c r="C30" t="s">
-        <v>374</v>
+        <v>417</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30" s="3">
+        <v>32</v>
+      </c>
+      <c r="F30" s="3">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>375</v>
+        <v>419</v>
       </c>
       <c r="B31" t="s">
         <v>173</v>
       </c>
       <c r="C31" t="s">
-        <v>376</v>
+        <v>420</v>
       </c>
       <c r="D31">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31" s="3">
+        <v>32</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="B32" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="C32" t="s">
-        <v>378</v>
+        <v>423</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32" s="3">
+        <v>32</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>379</v>
+        <v>425</v>
       </c>
       <c r="B33" t="s">
         <v>197</v>
       </c>
       <c r="C33" t="s">
-        <v>380</v>
+        <v>426</v>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33" s="3">
+        <v>32</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>381</v>
+        <v>427</v>
+      </c>
+      <c r="B34" t="s">
+        <v>201</v>
       </c>
       <c r="C34" t="s">
         <v>202</v>
@@ -5368,13 +6471,23 @@
       <c r="D34">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
-        <v>382</v>
+      <c r="E34" s="3">
+        <v>380</v>
+      </c>
+      <c r="F34" s="3">
+        <f t="shared" si="0"/>
+        <v>1520</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="24" t="s">
+        <v>428</v>
       </c>
       <c r="B35" t="s">
-        <v>383</v>
+        <v>429</v>
       </c>
       <c r="C35" t="s">
         <v>206</v>
@@ -5382,8 +6495,18 @@
       <c r="D35">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35" s="3">
+        <v>500</v>
+      </c>
+      <c r="F35" s="3">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>220</v>
       </c>
@@ -5396,10 +6519,20 @@
       <c r="D36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F36" s="3">
+        <f t="shared" si="0"/>
+        <v>33000</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>384</v>
+        <v>430</v>
       </c>
       <c r="B37" t="s">
         <v>217</v>
@@ -5410,13 +6543,23 @@
       <c r="D37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F37" s="3">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>385</v>
+        <v>431</v>
       </c>
       <c r="B38" t="s">
-        <v>317</v>
+        <v>349</v>
       </c>
       <c r="C38" t="s">
         <v>222</v>
@@ -5424,19 +6567,39 @@
       <c r="D38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F38" s="3">
+        <f t="shared" si="0"/>
+        <v>20000</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>386</v>
+        <v>432</v>
       </c>
       <c r="B39" t="s">
-        <v>387</v>
+        <v>433</v>
       </c>
       <c r="C39" t="s">
         <v>226</v>
       </c>
       <c r="D39">
         <v>1</v>
+      </c>
+      <c r="E39" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F39" s="3">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -5446,16 +6609,69 @@
       <c r="B40" t="s">
         <v>235</v>
       </c>
-      <c r="E40" s="1">
+      <c r="D40">
+        <v>5</v>
+      </c>
+      <c r="E40" s="2">
         <v>20000</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="2">
         <f>E40*D40</f>
-        <v>0</v>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="41" spans="5:6">
+      <c r="E41" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F41" s="5">
+        <f>SUM(F2:F40)-4*E40</f>
+        <v>145906</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="https://www.thegioiic.com/tu-gom-0603-100nf-0-1uf-50v"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://www.thegioiic.com/tu-gom-0402-100nf-0-1uf-50v"/>
+    <hyperlink ref="G4" r:id="rId1" display="https://www.thegioiic.com/tu-gom-0603-100nf-0-1uf-50v"/>
+    <hyperlink ref="G6" r:id="rId1" display="https://www.thegioiic.com/tu-gom-0603-100nf-0-1uf-50v"/>
+    <hyperlink ref="G5" r:id="rId3" display="https://www.thegioiic.com/tu-gom-0603-10uf-25v"/>
+    <hyperlink ref="G7" r:id="rId4" display="https://www.thegioiic.com/tu-gom-0603-10nf-50v"/>
+    <hyperlink ref="G8" r:id="rId5" display="https://www.thegioiic.com/tu-gom-0603-1uf-50v"/>
+    <hyperlink ref="G9" r:id="rId6" display="https://www.thegioiic.com/tu-gom-0603-22pf-50v"/>
+    <hyperlink ref="G10" r:id="rId5" display="https://www.thegioiic.com/tu-gom-0603-1uf-50v"/>
+    <hyperlink ref="G11" r:id="rId7" display="https://www.thegioiic.com/tu-gom-0603-33pf-50v"/>
+    <hyperlink ref="G12" r:id="rId8" display="https://www.thegioiic.com/cap-led-5mm-thu-phat-hong-ngoai-940nm"/>
+    <hyperlink ref="G22" r:id="rId8" display="https://www.thegioiic.com/cap-led-5mm-thu-phat-hong-ngoai-940nm"/>
+    <hyperlink ref="G13" r:id="rId8" display="https://www.thegioiic.com/cap-led-5mm-thu-phat-hong-ngoai-940nm"/>
+    <hyperlink ref="G24" r:id="rId8" display="https://www.thegioiic.com/cap-led-5mm-thu-phat-hong-ngoai-940nm"/>
+    <hyperlink ref="G14" r:id="rId9" display="https://www.thegioiic.com/led-do-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G15" r:id="rId10" display="https://www.thegioiic.com/led-trang-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G16" r:id="rId11" display="https://www.thegioiic.com/cbw201209u121t-ferrite-beads-2a-120-ohm-0805"/>
+    <hyperlink ref="G17" r:id="rId12" display="https://www.thegioiic.com/dau-xh2-54mm-2-chan-thang-xuyen-lo"/>
+    <hyperlink ref="G18" r:id="rId13" display="https://www.thegioiic.com/hang-rao-duc-don-2-54mm-40-chan-1-hang-cao-11-2mm-xuyen-lo"/>
+    <hyperlink ref="G19" r:id="rId13" display="https://www.thegioiic.com/hang-rao-duc-don-2-54mm-40-chan-1-hang-cao-11-2mm-xuyen-lo"/>
+    <hyperlink ref="G20" r:id="rId14" display="https://www.thegioiic.com/dau-sh1-0mm-3-chan-dan-smd-thang-dung"/>
+    <hyperlink ref="G21" r:id="rId15" display="https://www.thegioiic.com/dau-sh1-0mm-4-chan-dan-smd-thang-dung"/>
+    <hyperlink ref="G23" r:id="rId16" display="https://www.thegioiic.com/bc817-transistor-npn-45v-0-5a-3-chan-sot-23"/>
+    <hyperlink ref="G25" r:id="rId17" display="https://www.thegioiic.com/dien-tro-75-ohm-0603-5-"/>
+    <hyperlink ref="G26" r:id="rId18" display="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-" tooltip="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-"/>
+    <hyperlink ref="G27" r:id="rId19" display="https://www.thegioiic.com/dien-tro-100-kohm-0603-5-" tooltip="https://www.thegioiic.com/dien-tro-100-kohm-0603-5-"/>
+    <hyperlink ref="G28" r:id="rId18" display="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-" tooltip="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-"/>
+    <hyperlink ref="G29" r:id="rId20" display="https://www.thegioiic.com/dien-tro-10-kohm-0603-5-"/>
+    <hyperlink ref="G30" r:id="rId21" display="https://www.thegioiic.com/dien-tro-1-mohm-0603-5-"/>
+    <hyperlink ref="G31" r:id="rId22" display="https://www.thegioiic.com/dien-tro-0-ohm-0603-5-"/>
+    <hyperlink ref="G32" r:id="rId23" display="https://www.thegioiic.com/dien-tro-120-ohm-0603-5-"/>
+    <hyperlink ref="G33" r:id="rId18" display="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-" tooltip="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-"/>
+    <hyperlink ref="G34" r:id="rId24" display="https://www.thegioiic.com/vit-nhua-m3-dai-5mm"/>
+    <hyperlink ref="G35" r:id="rId25" display="https://www.thegioiic.com/nut-nhan-3x6mm-cao-5mm-2-chan-smd-dau-trang"/>
+    <hyperlink ref="G36" r:id="rId26" display="https://www.thegioiic.com/stm32f103c8t6-32-bit-arm-cortex-m3-microcontroller-72mhz-64kb-flash-48-lqfp"/>
+    <hyperlink ref="G37" r:id="rId27" display="https://www.thegioiic.com/ams1117-3-3v-ic-on-ap-3-3v-1a-sot-223"/>
+    <hyperlink ref="G38" r:id="rId28" display="https://www.thegioiic.com/tja1050t-ic-can-transceiver-8-soic"/>
+    <hyperlink ref="G39" r:id="rId29" display="https://www.thegioiic.com/thach-anh-8mhz-3225-4-chan-smd"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -5463,7 +6679,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.2222222222222" customWidth="1"/>
@@ -5474,43 +6690,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="24" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>388</v>
+        <v>434</v>
       </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>190</v>
+      </c>
+      <c r="F2" s="2">
+        <f t="shared" ref="F2:F17" si="0">E2*D2</f>
+        <v>190</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -5518,24 +6744,47 @@
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>389</v>
+        <v>436</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="3">
+        <v>500</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>286</v>
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
+        <v>437</v>
       </c>
       <c r="C4" t="s">
         <v>64</v>
       </c>
       <c r="D4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>200</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>86</v>
       </c>
@@ -5543,27 +6792,47 @@
         <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>390</v>
+        <v>438</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="4" t="s">
-        <v>391</v>
+      <c r="E5" s="3">
+        <v>180</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="B6" t="s">
-        <v>392</v>
+        <v>440</v>
       </c>
       <c r="C6" t="s">
         <v>91</v>
       </c>
       <c r="D6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>500</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>109</v>
       </c>
@@ -5576,8 +6845,18 @@
       <c r="D7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>61032421821</v>
       </c>
@@ -5585,27 +6864,47 @@
         <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>393</v>
+        <v>442</v>
       </c>
       <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="0"/>
+        <v>12600</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>61030821821</v>
       </c>
       <c r="B9" t="s">
-        <v>394</v>
+        <v>443</v>
       </c>
       <c r="C9" t="s">
-        <v>395</v>
+        <v>444</v>
       </c>
       <c r="D9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>61032021821</v>
       </c>
@@ -5613,13 +6912,23 @@
         <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>396</v>
+        <v>445</v>
       </c>
       <c r="D10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="0"/>
+        <v>3700</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>61002421121</v>
       </c>
@@ -5627,13 +6936,23 @@
         <v>141</v>
       </c>
       <c r="C11" t="s">
-        <v>397</v>
+        <v>446</v>
       </c>
       <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="0"/>
+        <v>13500</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>61032021121</v>
       </c>
@@ -5641,32 +6960,52 @@
         <v>155</v>
       </c>
       <c r="C12" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>61300311121</v>
       </c>
       <c r="B13" t="s">
-        <v>398</v>
+        <v>447</v>
       </c>
       <c r="C13" t="s">
-        <v>399</v>
+        <v>448</v>
       </c>
       <c r="D13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E13" s="3">
+        <v>700</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" si="0"/>
+        <v>11200</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>301</v>
+        <v>449</v>
       </c>
       <c r="B14" t="s">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="C14" t="s">
         <v>162</v>
@@ -5674,36 +7013,66 @@
       <c r="D14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="4" t="s">
+      <c r="E14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="24" t="s">
         <v>176</v>
       </c>
       <c r="B15" t="s">
         <v>177</v>
       </c>
       <c r="C15" t="s">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="4" t="s">
+      <c r="E15" s="3">
+        <v>50</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="24" t="s">
         <v>196</v>
       </c>
       <c r="B16" t="s">
         <v>197</v>
       </c>
       <c r="C16" t="s">
-        <v>401</v>
+        <v>451</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="3">
+        <v>32</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>200</v>
       </c>
@@ -5711,7 +7080,17 @@
         <v>202</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="E17" s="3">
+        <v>380</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="0"/>
+        <v>1520</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5724,16 +7103,44 @@
       <c r="D18">
         <v>5</v>
       </c>
-      <c r="E18" s="1">
-        <v>26400</v>
-      </c>
-      <c r="F18" s="1">
+      <c r="E18" s="2">
+        <v>20000</v>
+      </c>
+      <c r="F18" s="2">
         <f>E18*D18</f>
-        <v>132000</v>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19" spans="5:6">
+      <c r="E19" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F19" s="5">
+        <f>SUM(F2:F18)-4*E18</f>
+        <v>79972</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="https://www.thegioiic.com/tu-gom-0805-100nf-0-1uf-50v"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://www.thegioiic.com/smaj18a"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://www.thegioiic.com/zmm18-diode-zener-18v-500mw-smd"/>
+    <hyperlink ref="G5" r:id="rId4" display="https://www.thegioiic.com/led-do-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G6" r:id="rId5" display="https://www.thegioiic.com/cau-chi-ong-thuy-tinh-30a-5x20mm-toc-do-f"/>
+    <hyperlink ref="G7" r:id="rId6" display="https://www.thegioiic.com/kf301-2-v-domino-2-chan-thang-5-08mm-300v-10a-han-pcb"/>
+    <hyperlink ref="G11" r:id="rId7" display="https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-smd"/>
+    <hyperlink ref="G12" r:id="rId7" display="https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-smd"/>
+    <hyperlink ref="G13" r:id="rId8" display="https://www.thegioiic.com/hang-rao-duc-don-2-54mm-40-chan-1-hang-cao-11-2mm-xuyen-lo"/>
+    <hyperlink ref="G8" r:id="rId9" display="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-24-chan-2-hang-smd"/>
+    <hyperlink ref="G10" r:id="rId10" display="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-20-chan-2-hang-smd"/>
+    <hyperlink ref="G9" r:id="rId11" display="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-8-chan-2-hang-smd"/>
+    <hyperlink ref="G14" r:id="rId12" display="https://www.thegioiic.com/ao3407a-mosfet-kenh-p-30v-4-3a-sot-23-3"/>
+    <hyperlink ref="G15" r:id="rId13" display="https://www.thegioiic.com/dien-tro-15-kohm-0805-5-"/>
+    <hyperlink ref="G16" r:id="rId14" display="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-"/>
+    <hyperlink ref="G17" r:id="rId15" display="https://www.thegioiic.com/vit-nhua-m3-dai-5mm"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -5741,158 +7148,137 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="18.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="14.2222222222222" customWidth="1"/>
-    <col min="4" max="4" width="10.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="16.2222222222222" customWidth="1"/>
     <col min="5" max="5" width="15.4444444444444" customWidth="1"/>
     <col min="6" max="6" width="47.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>457</v>
+      </c>
+      <c r="B3" s="2">
+        <f>MainBoard!F64</f>
+        <v>263522</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <f>B3*C3</f>
+        <v>263522</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>458</v>
+      </c>
+      <c r="B4" s="3">
+        <f>HBridgeDriver!F18</f>
+        <v>72860</v>
+      </c>
+      <c r="C4">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>239</v>
-      </c>
-      <c r="F2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>405</v>
-      </c>
-      <c r="B3" t="s">
-        <v>405</v>
-      </c>
-      <c r="C3" s="1">
-        <v>26400</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1">
-        <f>D3*C3</f>
-        <v>132000</v>
-      </c>
-      <c r="F3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>407</v>
-      </c>
-      <c r="B4" t="s">
-        <v>408</v>
-      </c>
-      <c r="C4" s="1">
-        <v>62000</v>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1">
-        <f>D4*C4</f>
-        <v>310000</v>
-      </c>
-      <c r="F4" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="D4" s="2">
+        <f>B4*C4</f>
+        <v>291440</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>410</v>
-      </c>
-      <c r="B5" t="s">
-        <v>408</v>
-      </c>
-      <c r="C5" s="1">
-        <v>62000</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5" s="1">
-        <f>D5*C5</f>
-        <v>310000</v>
-      </c>
-      <c r="F5" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>459</v>
+      </c>
+      <c r="B5" s="3">
+        <f>HBridgeMCU!F39</f>
+        <v>163082</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <f>B5*C5</f>
+        <v>163082</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>411</v>
-      </c>
-      <c r="B6" t="s">
-        <v>412</v>
-      </c>
-      <c r="C6" s="1">
-        <v>20000</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1">
-        <f>D6*C6</f>
-        <v>100000</v>
-      </c>
-      <c r="F6" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>460</v>
+      </c>
+      <c r="B6" s="2">
+        <f>MainSensor!F41</f>
+        <v>145906</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <f>B6*C6</f>
+        <v>145906</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>414</v>
-      </c>
-      <c r="B7" t="s">
-        <v>415</v>
-      </c>
-      <c r="C7" s="1">
-        <v>26400</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7" s="1">
-        <f>D7*C7</f>
-        <v>132000</v>
-      </c>
-      <c r="F7" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="8" spans="4:5">
-      <c r="D8" t="s">
-        <v>416</v>
-      </c>
-      <c r="E8" s="1">
-        <f>SUM(E3:E7)-E5</f>
-        <v>674000</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="B7" s="2">
+        <f>ServoShield!F19</f>
+        <v>79972</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <f>B7*C7</f>
+        <v>79972</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="3:5">
+      <c r="C8" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" s="5">
+        <f>SUM(D3:D7)</f>
+        <v>943922</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="5:5">
+      <c r="E9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/2.Hardware/1.PCB/BOMTotal.xlsx
+++ b/2.Hardware/1.PCB/BOMTotal.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="MainBoard" sheetId="7" r:id="rId1"/>
@@ -2099,7 +2099,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2128,7 +2128,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -2143,15 +2142,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
@@ -2727,7 +2721,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="20" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
@@ -2751,7 +2745,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="20" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
@@ -2775,7 +2769,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
@@ -2799,7 +2793,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="20" t="s">
         <v>19</v>
       </c>
       <c r="B5" t="s">
@@ -2823,7 +2817,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="20" t="s">
         <v>23</v>
       </c>
       <c r="B6" t="s">
@@ -2847,7 +2841,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="20" t="s">
         <v>27</v>
       </c>
       <c r="B7" t="s">
@@ -2871,7 +2865,7 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="20" t="s">
         <v>31</v>
       </c>
       <c r="B8" t="s">
@@ -2895,7 +2889,7 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="20" t="s">
         <v>35</v>
       </c>
       <c r="B9" t="s">
@@ -2919,7 +2913,7 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="20" t="s">
         <v>39</v>
       </c>
       <c r="B10" t="s">
@@ -2943,7 +2937,7 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="20" t="s">
         <v>42</v>
       </c>
       <c r="B11" t="s">
@@ -2967,7 +2961,7 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="20" t="s">
         <v>46</v>
       </c>
       <c r="B12" t="s">
@@ -2991,7 +2985,7 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="20" t="s">
         <v>50</v>
       </c>
       <c r="B13" t="s">
@@ -3015,7 +3009,7 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="20" t="s">
         <v>54</v>
       </c>
       <c r="B14" t="s">
@@ -3231,7 +3225,7 @@
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="20" t="s">
         <v>89</v>
       </c>
       <c r="B23" t="s">
@@ -3255,7 +3249,7 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="20" t="s">
         <v>93</v>
       </c>
       <c r="B24" t="s">
@@ -3279,7 +3273,7 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="20" t="s">
         <v>97</v>
       </c>
       <c r="B25" t="s">
@@ -3303,7 +3297,7 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="20" t="s">
         <v>101</v>
       </c>
       <c r="B26" t="s">
@@ -3615,7 +3609,7 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="20" t="s">
         <v>143</v>
       </c>
       <c r="B39" t="s">
@@ -3639,7 +3633,7 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="20" t="s">
         <v>147</v>
       </c>
       <c r="B40" t="s">
@@ -3663,7 +3657,7 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="24" t="s">
+      <c r="A41" s="20" t="s">
         <v>151</v>
       </c>
       <c r="B41" t="s">
@@ -3759,7 +3753,7 @@
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="24" t="s">
+      <c r="A45" s="20" t="s">
         <v>164</v>
       </c>
       <c r="B45" t="s">
@@ -3783,7 +3777,7 @@
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="24" t="s">
+      <c r="A46" s="20" t="s">
         <v>168</v>
       </c>
       <c r="B46" t="s">
@@ -3807,7 +3801,7 @@
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="24" t="s">
+      <c r="A47" s="20" t="s">
         <v>172</v>
       </c>
       <c r="B47" t="s">
@@ -3831,7 +3825,7 @@
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="24" t="s">
+      <c r="A48" s="20" t="s">
         <v>176</v>
       </c>
       <c r="B48" t="s">
@@ -3855,7 +3849,7 @@
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="24" t="s">
+      <c r="A49" s="20" t="s">
         <v>180</v>
       </c>
       <c r="B49" t="s">
@@ -3879,7 +3873,7 @@
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="24" t="s">
+      <c r="A50" s="20" t="s">
         <v>184</v>
       </c>
       <c r="B50" t="s">
@@ -3903,7 +3897,7 @@
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="24" t="s">
+      <c r="A51" s="20" t="s">
         <v>188</v>
       </c>
       <c r="B51" t="s">
@@ -3927,7 +3921,7 @@
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="24" t="s">
+      <c r="A52" s="20" t="s">
         <v>192</v>
       </c>
       <c r="B52" t="s">
@@ -3951,7 +3945,7 @@
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="24" t="s">
+      <c r="A53" s="20" t="s">
         <v>196</v>
       </c>
       <c r="B53" t="s">
@@ -3999,7 +3993,7 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="24" t="s">
+      <c r="A55" s="20" t="s">
         <v>204</v>
       </c>
       <c r="B55" t="s">
@@ -4325,268 +4319,268 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="19" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="17">
         <v>2</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="18">
         <v>550</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="18">
         <v>5500</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="19" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="19" t="s">
+      <c r="B3" s="17"/>
+      <c r="C3" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="D3" s="20">
-        <v>1</v>
-      </c>
-      <c r="E3" s="21">
+      <c r="D3" s="17">
+        <v>1</v>
+      </c>
+      <c r="E3" s="18">
         <v>190</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="18">
         <v>1900</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="19" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="17">
         <v>2</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="18">
         <v>350</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="18">
         <v>3500</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="19" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="D5" s="20">
-        <v>1</v>
-      </c>
-      <c r="E5" s="21">
+      <c r="D5" s="17">
+        <v>1</v>
+      </c>
+      <c r="E5" s="18">
         <v>190</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="18">
         <v>190</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="19" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="D6" s="20">
-        <v>1</v>
-      </c>
-      <c r="E6" s="21">
+      <c r="D6" s="17">
+        <v>1</v>
+      </c>
+      <c r="E6" s="18">
         <v>170</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="18">
         <v>170</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="19" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="20">
-        <v>1</v>
-      </c>
-      <c r="E7" s="21">
+      <c r="D7" s="17">
+        <v>1</v>
+      </c>
+      <c r="E7" s="18">
         <v>1500</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="18">
         <v>1500</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="19" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="17">
         <v>2</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="18">
         <v>1500</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="18">
         <v>3000</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="19" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="D9" s="20">
-        <v>1</v>
-      </c>
-      <c r="E9" s="21">
+      <c r="D9" s="17">
+        <v>1</v>
+      </c>
+      <c r="E9" s="18">
         <v>4000</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="18">
         <v>4000</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="19" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="17">
         <v>4</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="18">
         <v>3000</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="18">
         <v>12000</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="19" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="19" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="17">
         <v>6</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="18">
         <v>38</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="18">
         <v>1900</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="G11" s="19" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="19" t="s">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="17">
         <v>3</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="18">
         <v>32</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="18">
         <v>1600</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G12" s="19" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="19" t="s">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="17">
         <v>4</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="18">
         <v>3</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="18">
         <v>1600</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="G13" s="19" t="s">
         <v>273</v>
       </c>
     </row>
@@ -4612,48 +4606,48 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="17">
         <v>2</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="18">
         <v>2800</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="18">
         <v>5600</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="19" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="17" t="s">
         <v>281</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="17">
         <v>2</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="18">
         <v>15000</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="18">
         <v>30000</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="G16" s="19" t="s">
         <v>282</v>
       </c>
     </row>
@@ -4679,7 +4673,7 @@
       <c r="E18" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="16">
         <f>SUM(F2:F17)-4*E17</f>
         <v>72860</v>
       </c>
@@ -4748,21 +4742,21 @@
       <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10"/>
+      <c r="B2" s="9"/>
       <c r="C2" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <v>7</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="10">
         <v>190</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <f>D2*E2</f>
         <v>1330</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4770,21 +4764,21 @@
       <c r="A3" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="10"/>
+      <c r="B3" s="9"/>
       <c r="C3" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="D3" s="10">
-        <v>1</v>
-      </c>
-      <c r="E3" s="11">
+      <c r="D3" s="9">
+        <v>1</v>
+      </c>
+      <c r="E3" s="10">
         <v>700</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="10">
         <f t="shared" ref="F3:F36" si="0">D3*E3</f>
         <v>700</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>286</v>
       </c>
     </row>
@@ -4792,21 +4786,21 @@
       <c r="A4" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="10"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>2</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="10">
         <v>400</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4814,21 +4808,21 @@
       <c r="A5" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="B5" s="10"/>
+      <c r="B5" s="9"/>
       <c r="C5" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>2</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <v>190</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <f t="shared" si="0"/>
         <v>380</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="11" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4836,21 +4830,21 @@
       <c r="A6" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="B6" s="10"/>
+      <c r="B6" s="9"/>
       <c r="C6" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>2</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <v>250</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>292</v>
       </c>
     </row>
@@ -4858,21 +4852,21 @@
       <c r="A7" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="B7" s="10"/>
+      <c r="B7" s="9"/>
       <c r="C7" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>2</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <v>800</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="11" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4880,21 +4874,21 @@
       <c r="A8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="10"/>
+      <c r="B8" s="9"/>
       <c r="C8" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>2</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <v>190</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <f t="shared" si="0"/>
         <v>380</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="11" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4908,17 +4902,17 @@
       <c r="C9" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>2</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <v>230</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <f t="shared" si="0"/>
         <v>460</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="11" t="s">
         <v>296</v>
       </c>
     </row>
@@ -4932,17 +4926,17 @@
       <c r="C10" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>2</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <v>180</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="11" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4956,17 +4950,17 @@
       <c r="C11" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="D11" s="10">
-        <v>1</v>
-      </c>
-      <c r="E11" s="11">
+      <c r="D11" s="9">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10">
         <v>210</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="11" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4980,17 +4974,17 @@
       <c r="C12" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>2</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="10">
         <v>350</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="11" t="s">
         <v>77</v>
       </c>
     </row>
@@ -5004,17 +4998,17 @@
       <c r="C13" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>4</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="10">
         <v>500</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="10">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="11" t="s">
         <v>65</v>
       </c>
     </row>
@@ -5028,17 +5022,17 @@
       <c r="C14" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>4</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="10">
         <v>200</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="10">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="11" t="s">
         <v>69</v>
       </c>
     </row>
@@ -5046,21 +5040,21 @@
       <c r="A15" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="B15" s="10"/>
+      <c r="B15" s="9"/>
       <c r="C15" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="10">
-        <v>1</v>
-      </c>
-      <c r="E15" s="11">
+      <c r="D15" s="9">
+        <v>1</v>
+      </c>
+      <c r="E15" s="10">
         <v>500</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="10">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="11" t="s">
         <v>305</v>
       </c>
     </row>
@@ -5068,21 +5062,21 @@
       <c r="A16" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="B16" s="10"/>
+      <c r="B16" s="9"/>
       <c r="C16" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>2</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="10">
         <v>2500</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="11" t="s">
         <v>308</v>
       </c>
     </row>
@@ -5090,21 +5084,21 @@
       <c r="A17" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="10"/>
+      <c r="B17" s="9"/>
       <c r="C17" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="D17" s="10">
-        <v>1</v>
-      </c>
-      <c r="E17" s="11">
+      <c r="D17" s="9">
+        <v>1</v>
+      </c>
+      <c r="E17" s="10">
         <v>1500</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="10">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="11" t="s">
         <v>309</v>
       </c>
     </row>
@@ -5118,17 +5112,17 @@
       <c r="C18" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="D18" s="10">
-        <v>1</v>
-      </c>
-      <c r="E18" s="11">
+      <c r="D18" s="9">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10">
         <v>1500</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="10">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="11" t="s">
         <v>112</v>
       </c>
     </row>
@@ -5142,17 +5136,17 @@
       <c r="C19" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="10">
-        <v>1</v>
-      </c>
-      <c r="E19" s="11">
+      <c r="D19" s="9">
+        <v>1</v>
+      </c>
+      <c r="E19" s="10">
         <v>2500</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="10">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="11" t="s">
         <v>312</v>
       </c>
     </row>
@@ -5166,17 +5160,17 @@
       <c r="C20" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>4</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="10">
         <v>2200</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="10">
         <f t="shared" si="0"/>
         <v>8800</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="11" t="s">
         <v>316</v>
       </c>
     </row>
@@ -5190,17 +5184,17 @@
       <c r="C21" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="10">
-        <v>1</v>
-      </c>
-      <c r="E21" s="11">
+      <c r="D21" s="9">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10">
         <v>800</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="10">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="11" t="s">
         <v>318</v>
       </c>
     </row>
@@ -5214,17 +5208,17 @@
       <c r="C22" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="D22" s="10">
-        <v>1</v>
-      </c>
-      <c r="E22" s="11">
+      <c r="D22" s="9">
+        <v>1</v>
+      </c>
+      <c r="E22" s="10">
         <v>900</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="10">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="11" t="s">
         <v>322</v>
       </c>
     </row>
@@ -5238,17 +5232,17 @@
       <c r="C23" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="D23" s="10">
-        <v>1</v>
-      </c>
-      <c r="E23" s="11">
+      <c r="D23" s="9">
+        <v>1</v>
+      </c>
+      <c r="E23" s="10">
         <v>900</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="10">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="11" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5262,17 +5256,17 @@
       <c r="C24" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="D24" s="10">
-        <v>1</v>
-      </c>
-      <c r="E24" s="11">
+      <c r="D24" s="9">
+        <v>1</v>
+      </c>
+      <c r="E24" s="10">
         <v>4500</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="10">
         <f t="shared" si="0"/>
         <v>4500</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="11" t="s">
         <v>135</v>
       </c>
     </row>
@@ -5286,17 +5280,17 @@
       <c r="C25" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>3</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="10">
         <v>2000</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="10">
         <f t="shared" si="0"/>
         <v>6000</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G25" s="11" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5310,17 +5304,17 @@
       <c r="C26" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <v>3</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="10">
         <v>8000</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="10">
         <f t="shared" si="0"/>
         <v>24000</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="11" t="s">
         <v>331</v>
       </c>
     </row>
@@ -5328,21 +5322,21 @@
       <c r="A27" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B27" s="10"/>
+      <c r="B27" s="9"/>
       <c r="C27" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="9">
         <v>4</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="10">
         <v>32</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="10">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="11" t="s">
         <v>199</v>
       </c>
     </row>
@@ -5350,21 +5344,21 @@
       <c r="A28" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B28" s="10"/>
+      <c r="B28" s="9"/>
       <c r="C28" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="9">
         <v>4</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="10">
         <v>38</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="10">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="11" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5372,21 +5366,21 @@
       <c r="A29" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B29" s="10"/>
+      <c r="B29" s="9"/>
       <c r="C29" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="9">
         <v>9</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="10">
         <v>32</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="10">
         <f t="shared" si="0"/>
         <v>288</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="G29" s="11" t="s">
         <v>273</v>
       </c>
     </row>
@@ -5394,21 +5388,21 @@
       <c r="A30" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="B30" s="10"/>
+      <c r="B30" s="9"/>
       <c r="C30" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="D30" s="10">
-        <v>1</v>
-      </c>
-      <c r="E30" s="11">
+      <c r="D30" s="9">
+        <v>1</v>
+      </c>
+      <c r="E30" s="10">
         <v>38</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="10">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="11" t="s">
         <v>337</v>
       </c>
     </row>
@@ -5416,21 +5410,21 @@
       <c r="A31" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="B31" s="10"/>
+      <c r="B31" s="9"/>
       <c r="C31" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <v>6</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="10">
         <v>56</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="10">
         <f t="shared" si="0"/>
         <v>336</v>
       </c>
-      <c r="G31" s="12" t="s">
+      <c r="G31" s="11" t="s">
         <v>340</v>
       </c>
     </row>
@@ -5438,21 +5432,21 @@
       <c r="A32" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="B32" s="10"/>
+      <c r="B32" s="9"/>
       <c r="C32" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <v>4</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="12">
         <v>380</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="13">
         <f>E32*D32</f>
         <v>1520</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>203</v>
       </c>
     </row>
@@ -5466,17 +5460,17 @@
       <c r="C33" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="9">
         <v>5</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="10">
         <v>400</v>
       </c>
-      <c r="F33" s="11">
-        <f>D33*E33</f>
+      <c r="F33" s="10">
+        <f t="shared" ref="F33:F38" si="1">D33*E33</f>
         <v>2000</v>
       </c>
-      <c r="G33" s="12" t="s">
+      <c r="G33" s="11" t="s">
         <v>344</v>
       </c>
     </row>
@@ -5490,17 +5484,17 @@
       <c r="C34" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="D34" s="10">
-        <v>1</v>
-      </c>
-      <c r="E34" s="11">
+      <c r="D34" s="9">
+        <v>1</v>
+      </c>
+      <c r="E34" s="10">
         <v>44000</v>
       </c>
-      <c r="F34" s="11">
-        <f>D34*E34</f>
+      <c r="F34" s="10">
+        <f t="shared" si="1"/>
         <v>44000</v>
       </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="11" t="s">
         <v>347</v>
       </c>
     </row>
@@ -5514,17 +5508,17 @@
       <c r="C35" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="D35" s="10">
-        <v>1</v>
-      </c>
-      <c r="E35" s="11">
+      <c r="D35" s="9">
+        <v>1</v>
+      </c>
+      <c r="E35" s="10">
         <v>20000</v>
       </c>
-      <c r="F35" s="11">
-        <f>D35*E35</f>
+      <c r="F35" s="10">
+        <f t="shared" si="1"/>
         <v>20000</v>
       </c>
-      <c r="G35" s="12" t="s">
+      <c r="G35" s="11" t="s">
         <v>350</v>
       </c>
     </row>
@@ -5538,17 +5532,17 @@
       <c r="C36" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="D36" s="10">
-        <v>1</v>
-      </c>
-      <c r="E36" s="11">
+      <c r="D36" s="9">
+        <v>1</v>
+      </c>
+      <c r="E36" s="10">
         <v>3500</v>
       </c>
-      <c r="F36" s="11">
-        <f>D36*E36</f>
+      <c r="F36" s="10">
+        <f t="shared" si="1"/>
         <v>3500</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="11" t="s">
         <v>219</v>
       </c>
     </row>
@@ -5562,45 +5556,45 @@
       <c r="C37" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D37" s="10">
-        <v>1</v>
-      </c>
-      <c r="E37" s="11">
+      <c r="D37" s="9">
+        <v>1</v>
+      </c>
+      <c r="E37" s="10">
         <v>4000</v>
       </c>
-      <c r="F37" s="11">
-        <f>D37*E37</f>
+      <c r="F37" s="10">
+        <f t="shared" si="1"/>
         <v>4000</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="11" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17">
+      <c r="C38" s="15"/>
+      <c r="D38" s="15">
         <v>5</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="13">
         <v>20000</v>
       </c>
-      <c r="F38" s="11">
-        <f>D38*E38</f>
+      <c r="F38" s="10">
+        <f t="shared" si="1"/>
         <v>100000</v>
       </c>
-      <c r="G38" s="17"/>
+      <c r="G38" s="15"/>
     </row>
     <row r="39" spans="5:6">
       <c r="E39" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="16">
         <f>SUM(F2:F38)-4*E38</f>
         <v>163082</v>
       </c>
@@ -6123,7 +6117,7 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="20" t="s">
         <v>151</v>
       </c>
       <c r="B20" t="s">
@@ -6147,7 +6141,7 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="20" t="s">
         <v>143</v>
       </c>
       <c r="B21" t="s">
@@ -6483,7 +6477,7 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="24" t="s">
+      <c r="A35" s="20" t="s">
         <v>428</v>
       </c>
       <c r="B35" t="s">
@@ -6713,7 +6707,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="20" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
@@ -6729,7 +6723,7 @@
         <v>190</v>
       </c>
       <c r="F2" s="2">
-        <f t="shared" ref="F2:F17" si="0">E2*D2</f>
+        <f t="shared" ref="F2:F18" si="0">E2*D2</f>
         <v>190</v>
       </c>
       <c r="G2" s="6" t="s">
@@ -6809,7 +6803,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="20" t="s">
         <v>439</v>
       </c>
       <c r="B6" t="s">
@@ -7025,7 +7019,7 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="20" t="s">
         <v>176</v>
       </c>
       <c r="B15" t="s">
@@ -7049,7 +7043,7 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="20" t="s">
         <v>196</v>
       </c>
       <c r="B16" t="s">
@@ -7107,7 +7101,7 @@
         <v>20000</v>
       </c>
       <c r="F18" s="2">
-        <f>E18*D18</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
     </row>

--- a/2.Hardware/1.PCB/BOMTotal.xlsx
+++ b/2.Hardware/1.PCB/BOMTotal.xlsx
@@ -6672,7 +6672,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
@@ -7134,7 +7136,7 @@
     <hyperlink ref="G17" r:id="rId15" display="https://www.thegioiic.com/vit-nhua-m3-dai-5mm"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageSetup paperSize="1" scale="45" fitToHeight="0" orientation="landscape"/>
   <headerFooter/>
 </worksheet>
 </file>
